--- a/shared-templates/team_skill_register.xlsx
+++ b/shared-templates/team_skill_register.xlsx
@@ -2933,17 +2933,17 @@
       </c>
       <c r="K6" s="24" t="inlineStr">
         <is>
-          <t>产品解读、行业配置变化、净值走势、客户沟通要点</t>
+          <t>产品解读、净值归因、风险提示、客户沟通话术</t>
         </is>
       </c>
       <c r="L6" s="24" t="inlineStr">
         <is>
-          <t>规划</t>
+          <t>已制作Demo</t>
         </is>
       </c>
       <c r="M6" s="24" t="inlineStr">
         <is>
-          <t>catalog</t>
+          <t>demo</t>
         </is>
       </c>
       <c r="N6" s="24" t="inlineStr">
@@ -2958,26 +2958,30 @@
       </c>
       <c r="P6" s="24" t="inlineStr">
         <is>
-          <t>保留为平台中立目录项；真实演示可复用 Dumate 能力，网页侧补一个轻量 Demo。</t>
-        </is>
-      </c>
-      <c r="Q6" s="24" t="str"/>
-      <c r="R6" s="24" t="str"/>
-      <c r="S6" s="24" t="str"/>
-      <c r="T6" s="24" t="str"/>
+          <t>已接入同事提供的页面 Demo；暂无真实 SKILL.md 与配套脚本，后续需补 Skill 包后再进入真实文件展示。</t>
+        </is>
+      </c>
+      <c r="Q6" s="24" t="inlineStr"/>
+      <c r="R6" s="24" t="inlineStr">
+        <is>
+          <t>presales-skill-matrix/wealth-product-net-value-analysis/wealth-product-net-value-analysis-demo.html</t>
+        </is>
+      </c>
+      <c r="S6" s="24" t="inlineStr"/>
+      <c r="T6" s="24" t="inlineStr"/>
       <c r="U6" s="24" t="inlineStr">
         <is>
-          <t>0.1.0</t>
+          <t>0.2.0-demo</t>
         </is>
       </c>
       <c r="V6" s="24" t="inlineStr">
         <is>
-          <t>财富管理,投顾,产品解读,金融数据</t>
+          <t>财富管理,投顾,产品解读,净值走势,客户沟通,Demo</t>
         </is>
       </c>
       <c r="W6" s="24" t="inlineStr">
         <is>
-          <t>来源：Dumate场景积累-2026.05.29.pdf；仅先登记名称和分类，待补 SKILL.md。</t>
+          <t>2026-06-18 接入同事提供的财富产品解读与净值走势分析页面 Demo；当前仅有 HTML demo 文件，未伪造 Skill 文件包。</t>
         </is>
       </c>
     </row>

--- a/shared-templates/team_skill_register.xlsx
+++ b/shared-templates/team_skill_register.xlsx
@@ -2918,7 +2918,7 @@
       </c>
       <c r="H6" s="24" t="inlineStr">
         <is>
-          <t>面向投顾、理财经理、客户经理，在财富营销和陪伴过程中解读基金、股票、债券等产品，并支持持仓变化和净值走势分析。</t>
+          <t>面向投顾、理财经理、客户经理，围绕基金/财富产品进行材料解读、净值走势分析、持仓识别、量化评估和客户沟通话术生成。</t>
         </is>
       </c>
       <c r="I6" s="24" t="inlineStr">
@@ -2928,17 +2928,17 @@
       </c>
       <c r="J6" s="24" t="inlineStr">
         <is>
-          <t>产品材料、持仓截图、净值数据、客户问题</t>
+          <t>产品材料、持仓截图、净值数据、客户问题、基金/经理/公司数据</t>
         </is>
       </c>
       <c r="K6" s="24" t="inlineStr">
         <is>
-          <t>产品解读、净值归因、风险提示、客户沟通话术</t>
+          <t>产品解读、净值归因、量化分析、风险提示、客户沟通话术、持仓报告</t>
         </is>
       </c>
       <c r="L6" s="24" t="inlineStr">
         <is>
-          <t>已制作Demo</t>
+          <t>已开发</t>
         </is>
       </c>
       <c r="M6" s="24" t="inlineStr">
@@ -2948,40 +2948,52 @@
       </c>
       <c r="N6" s="24" t="inlineStr">
         <is>
-          <t>同事/Dumate场景积累</t>
+          <t>同事/Fund Advisor Skill包</t>
         </is>
       </c>
       <c r="O6" s="24" t="inlineStr">
         <is>
-          <t>Dumate</t>
+          <t>Dumate/Dodo</t>
         </is>
       </c>
       <c r="P6" s="24" t="inlineStr">
         <is>
-          <t>已接入同事提供的页面 Demo；暂无真实 SKILL.md 与配套脚本，后续需补 Skill 包后再进入真实文件展示。</t>
-        </is>
-      </c>
-      <c r="Q6" s="24" t="inlineStr"/>
+          <t>已补齐 fund-advisor 真实 Skill 包；页面 Demo 与真实 SKILL.md、脚本、数据、引用文档共同展示。后续可继续做 Web UI 运行验证和真实数据接入。</t>
+        </is>
+      </c>
+      <c r="Q6" s="24" t="inlineStr">
+        <is>
+          <t>presales-skill-matrix/wealth-product-net-value-analysis/SKILL.md</t>
+        </is>
+      </c>
       <c r="R6" s="24" t="inlineStr">
         <is>
           <t>presales-skill-matrix/wealth-product-net-value-analysis/wealth-product-net-value-analysis-demo.html</t>
         </is>
       </c>
-      <c r="S6" s="24" t="inlineStr"/>
-      <c r="T6" s="24" t="inlineStr"/>
+      <c r="S6" s="24" t="inlineStr">
+        <is>
+          <t>presales-skill-matrix/wealth-product-net-value-analysis/references/</t>
+        </is>
+      </c>
+      <c r="T6" s="24" t="inlineStr">
+        <is>
+          <t>presales-skill-matrix/wealth-product-net-value-analysis/data/</t>
+        </is>
+      </c>
       <c r="U6" s="24" t="inlineStr">
         <is>
-          <t>0.2.0-demo</t>
+          <t>5.0.0</t>
         </is>
       </c>
       <c r="V6" s="24" t="inlineStr">
         <is>
-          <t>财富管理,投顾,产品解读,净值走势,客户沟通,Demo</t>
+          <t>财富管理,基金投顾,产品解读,净值走势,持仓识别,量化分析,客户沟通,已开发Skill</t>
         </is>
       </c>
       <c r="W6" s="24" t="inlineStr">
         <is>
-          <t>2026-06-18 接入同事提供的财富产品解读与净值走势分析页面 Demo；当前仅有 HTML demo 文件，未伪造 Skill 文件包。</t>
+          <t>2026-06-18 已接入 fund-advisor 完整 Skill 包；保留同事提供的财富产品解读页面 Demo。</t>
         </is>
       </c>
     </row>

--- a/shared-templates/team_skill_register.xlsx
+++ b/shared-templates/team_skill_register.xlsx
@@ -4,17 +4,20 @@
   <workbookPr/>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="场景清单" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="已制作Skill登记" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="同事填写说明" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="分类口径说明" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="已制作Skill登记" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="同事填写说明" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
-  <definedNames/>
+  <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'已制作Skill登记'!$A$1:$AA$220</definedName>
+  </definedNames>
 </workbook>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="32">
+  <fonts count="35">
     <font>
       <name val="Carlito"/>
       <sz val="11"/>
@@ -184,8 +187,21 @@
       <b val="1"/>
       <sz val="16"/>
     </font>
+    <font>
+      <b val="1"/>
+      <color rgb="00FFFFFF"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <color rgb="00FFFFFF"/>
+      <sz val="16"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <color rgb="004C1D95"/>
+    </font>
   </fonts>
-  <fills count="37">
+  <fills count="41">
     <fill>
       <patternFill/>
     </fill>
@@ -367,8 +383,28 @@
         <fgColor rgb="FFFFFFFF"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="001F4E78"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="004C1D95"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="006D28D9"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00334155"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="10">
+  <borders count="16">
     <border/>
     <border>
       <left style="thin">
@@ -461,6 +497,66 @@
       </top>
       <bottom style="double">
         <color theme="4"/>
+      </bottom>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="00D9E2F3"/>
+      </left>
+      <right style="thin">
+        <color rgb="00D9E2F3"/>
+      </right>
+      <top style="thin">
+        <color rgb="00D9E2F3"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00D9E2F3"/>
+      </bottom>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="00D9E2EC"/>
+      </left>
+      <right style="thin">
+        <color rgb="00D9E2EC"/>
+      </right>
+      <top style="thin">
+        <color rgb="00D9E2EC"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00D9E2EC"/>
+      </bottom>
+    </border>
+    <border>
+      <top style="thin">
+        <color rgb="00D9E2EC"/>
+      </top>
+    </border>
+    <border>
+      <right style="thin">
+        <color rgb="00D9E2EC"/>
+      </right>
+      <top style="thin">
+        <color rgb="00D9E2EC"/>
+      </top>
+    </border>
+    <border>
+      <top style="thin">
+        <color rgb="00D9E2EC"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00D9E2EC"/>
+      </bottom>
+    </border>
+    <border>
+      <right style="thin">
+        <color rgb="00D9E2EC"/>
+      </right>
+      <top style="thin">
+        <color rgb="00D9E2EC"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00D9E2EC"/>
       </bottom>
     </border>
   </borders>
@@ -614,7 +710,7 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="30">
+  <cellXfs count="40">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="49"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="49">
       <alignment vertical="top" wrapText="1"/>
@@ -681,6 +777,32 @@
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="32" fillId="37" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="34" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="33" fillId="38" borderId="11" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="14" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="15" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="34" fillId="0" borderId="11" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="32" fillId="39" borderId="11" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="32" fillId="40" borderId="11" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="50">
     <cellStyle name="常规" xfId="0"/>
@@ -2339,146 +2461,578 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W220"/>
+  <dimension ref="A1:E19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="12.22000026702881" customWidth="1" style="29" min="1" max="1"/>
-    <col width="20" customWidth="1" style="29" min="2" max="2"/>
-    <col width="15.5600004196167" customWidth="1" style="29" min="3" max="3"/>
+    <col width="20" customWidth="1" style="29" min="1" max="1"/>
+    <col width="28" customWidth="1" style="29" min="2" max="2"/>
+    <col width="42" customWidth="1" style="29" min="3" max="3"/>
+    <col width="70" customWidth="1" style="29" min="4" max="4"/>
+    <col width="48" customWidth="1" style="29" min="5" max="5"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="28" customHeight="1" s="29">
+      <c r="A1" s="33" t="inlineStr">
+        <is>
+          <t>FDE Skill 分类体系说明</t>
+        </is>
+      </c>
+      <c r="B1" s="34" t="n"/>
+      <c r="C1" s="34" t="n"/>
+      <c r="D1" s="34" t="n"/>
+      <c r="E1" s="35" t="n"/>
+    </row>
+    <row r="2" ht="42" customHeight="1" s="29">
+      <c r="A2" s="36" t="inlineStr">
+        <is>
+          <t>核心原则</t>
+        </is>
+      </c>
+      <c r="B2" s="37" t="inlineStr">
+        <is>
+          <t>分类不是标签堆叠；一个 Skill 至少要同时说明服务对象、业务问题、落地形态、实现模式和真实交付物。</t>
+        </is>
+      </c>
+      <c r="C2" s="34" t="n"/>
+      <c r="D2" s="34" t="n"/>
+      <c r="E2" s="35" t="n"/>
+    </row>
+    <row r="3" ht="42" customHeight="1" s="29">
+      <c r="A3" s="37" t="inlineStr"/>
+      <c r="B3" s="37" t="inlineStr"/>
+      <c r="C3" s="37" t="inlineStr"/>
+      <c r="D3" s="37" t="inlineStr"/>
+      <c r="E3" s="37" t="inlineStr"/>
+    </row>
+    <row r="4" ht="42" customHeight="1" s="29">
+      <c r="A4" s="38" t="inlineStr">
+        <is>
+          <t>字段</t>
+        </is>
+      </c>
+      <c r="B4" s="38" t="inlineStr">
+        <is>
+          <t>回答的问题</t>
+        </is>
+      </c>
+      <c r="C4" s="38" t="inlineStr">
+        <is>
+          <t>推荐取值</t>
+        </is>
+      </c>
+      <c r="D4" s="38" t="inlineStr">
+        <is>
+          <t>填写规则</t>
+        </is>
+      </c>
+      <c r="E4" s="38" t="inlineStr">
+        <is>
+          <t>示例</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="42" customHeight="1" s="29">
+      <c r="A5" s="37" t="inlineStr">
+        <is>
+          <t>场景大类</t>
+        </is>
+      </c>
+      <c r="B5" s="37" t="inlineStr">
+        <is>
+          <t>它服务谁？</t>
+        </is>
+      </c>
+      <c r="C5" s="37" t="inlineStr">
+        <is>
+          <t>客户金融场景 / SA-AI内化场景</t>
+        </is>
+      </c>
+      <c r="D5" s="37" t="inlineStr">
+        <is>
+          <t>第一步先判断服务对象。客户业务、客户共创、行业方案放客户金融场景；SA 自己的投标、方案、评估、日报、资料整理放 SA-AI内化场景。</t>
+        </is>
+      </c>
+      <c r="E5" s="37" t="inlineStr">
+        <is>
+          <t>财富产品解读=客户金融场景；团队日报汇总=SA-AI内化场景</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="42" customHeight="1" s="29">
+      <c r="A6" s="37" t="inlineStr">
+        <is>
+          <t>业务分类</t>
+        </is>
+      </c>
+      <c r="B6" s="37" t="inlineStr">
+        <is>
+          <t>它解决哪类业务问题？</t>
+        </is>
+      </c>
+      <c r="C6" s="37" t="inlineStr">
+        <is>
+          <t>风控 / 财富管理 / 投研 / 团队管理 / 投标 / 方案写作 / 技术评估 / 资料检索 / 合规 / 车险 / 客服 / 办公 / 科技</t>
+        </is>
+      </c>
+      <c r="D6" s="37" t="inlineStr">
+        <is>
+          <t>用业务语言，不用技术语言。不要填“混合型”“Agent”“RAG”；这些属于实现模式。</t>
+        </is>
+      </c>
+      <c r="E6" s="37" t="inlineStr">
+        <is>
+          <t>授信走访=风控；个股研究=投研；日报汇总=团队管理；招标红线=投标</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="42" customHeight="1" s="29">
+      <c r="A7" s="37" t="inlineStr">
+        <is>
+          <t>落地形态</t>
+        </is>
+      </c>
+      <c r="B7" s="37" t="inlineStr">
+        <is>
+          <t>它如何沉淀为工程资产？</t>
+        </is>
+      </c>
+      <c r="C7" s="37" t="inlineStr">
+        <is>
+          <t>独立 Skill / 主 Skill + L1 / Agent 编排 / L1 候选 / L3 专项候选</t>
+        </is>
+      </c>
+      <c r="D7" s="37" t="inlineStr">
+        <is>
+          <t>看工程组织方式。边界清晰填独立 Skill；需要复用企业画像、检索、报告生成等公共能力填主 Skill + L1；多角色多工具协同填 Agent 编排。</t>
+        </is>
+      </c>
+      <c r="E7" s="37" t="inlineStr">
+        <is>
+          <t>贷后风险=主 Skill + L1；个股产业链投研=Agent 编排；合同关键词检索=独立 Skill</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="42" customHeight="1" s="29">
+      <c r="A8" s="37" t="inlineStr">
+        <is>
+          <t>实现模式</t>
+        </is>
+      </c>
+      <c r="B8" s="37" t="inlineStr">
+        <is>
+          <t>主要靠什么机制完成？</t>
+        </is>
+      </c>
+      <c r="C8" s="37" t="inlineStr">
+        <is>
+          <t>规则型 / LLM生成型 / RAG知识检索型 / 数据分析型 / 工具调用型 / Agent编排型 / 混合型</t>
+        </is>
+      </c>
+      <c r="D8" s="37" t="inlineStr">
+        <is>
+          <t>填主导机制。依赖内部 API、MCP、EOP、Dodo、Dumate 工具或脚本时，优先填工具调用型；高价值金融链路多机制并用时填混合型。</t>
+        </is>
+      </c>
+      <c r="E8" s="37" t="inlineStr">
+        <is>
+          <t>废标红线=规则型；PPT文案=LLM生成型；案例素材=RAG知识检索型；日报汇总=工具调用型</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="42" customHeight="1" s="29">
+      <c r="A9" s="37" t="inlineStr">
+        <is>
+          <t>建设状态</t>
+        </is>
+      </c>
+      <c r="B9" s="37" t="inlineStr">
+        <is>
+          <t>内容做到哪一步？</t>
+        </is>
+      </c>
+      <c r="C9" s="37" t="inlineStr">
+        <is>
+          <t>规划 / 已制作 / 已开发</t>
+        </is>
+      </c>
+      <c r="D9" s="37" t="inlineStr">
+        <is>
+          <t>规划=只有方向或目录；已制作=已有 SKILL.md 或可用内容雏形；已开发=有真实 Skill 包、脚本、数据或可演示闭环。</t>
+        </is>
+      </c>
+      <c r="E9" s="37" t="inlineStr">
+        <is>
+          <t>fund-advisor 真实包接入后=已开发</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="42" customHeight="1" s="29">
+      <c r="A10" s="37" t="inlineStr">
+        <is>
+          <t>展示状态</t>
+        </is>
+      </c>
+      <c r="B10" s="37" t="inlineStr">
+        <is>
+          <t>页面如何展示？</t>
+        </is>
+      </c>
+      <c r="C10" s="37" t="inlineStr">
+        <is>
+          <t>catalog / skill / demo</t>
+        </is>
+      </c>
+      <c r="D10" s="37" t="inlineStr">
+        <is>
+          <t>catalog=目录项；skill=已有 Skill 定义但没有页面 Demo；demo=已有演示页面。</t>
+        </is>
+      </c>
+      <c r="E10" s="37" t="inlineStr">
+        <is>
+          <t>有 demo.html 填 demo</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="42" customHeight="1" s="29">
+      <c r="A11" s="37" t="inlineStr">
+        <is>
+          <t>交付真实性</t>
+        </is>
+      </c>
+      <c r="B11" s="37" t="inlineStr">
+        <is>
+          <t>仓库里到底有什么真实文件？</t>
+        </is>
+      </c>
+      <c r="C11" s="37" t="inlineStr">
+        <is>
+          <t>目录规划 / 仅Demo / 真实SKILL.md / 真实Skill包 / 真实Skill包+Demo</t>
+        </is>
+      </c>
+      <c r="D11" s="37" t="inlineStr">
+        <is>
+          <t>按仓库真实资产填写。只有页面没有 Skill 文件填仅Demo；只有 SKILL.md 填真实SKILL.md；有 SKILL.md+references/scripts/data 等填真实Skill包；再加 Demo 填真实Skill包+Demo。</t>
+        </is>
+      </c>
+      <c r="E11" s="37" t="inlineStr">
+        <is>
+          <t>财富产品解读=真实Skill包+Demo；PDF导入未拿到文件=目录规划</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="42" customHeight="1" s="29">
+      <c r="A12" s="37" t="inlineStr">
+        <is>
+          <t>Skill分类</t>
+        </is>
+      </c>
+      <c r="B12" s="37" t="inlineStr">
+        <is>
+          <t>旧字段如何处理？</t>
+        </is>
+      </c>
+      <c r="C12" s="37" t="inlineStr">
+        <is>
+          <t>自由文本</t>
+        </is>
+      </c>
+      <c r="D12" s="37" t="inlineStr">
+        <is>
+          <t>保留历史兼容，不再承担主分类职责。不要再把业务域、实现模式、标签都塞进这个字段。</t>
+        </is>
+      </c>
+      <c r="E12" s="37" t="inlineStr">
+        <is>
+          <t>混合型 Skill（规则+LLM+人工校验）</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="42" customHeight="1" s="29">
+      <c r="A13" s="37" t="inlineStr">
+        <is>
+          <t>标签</t>
+        </is>
+      </c>
+      <c r="B13" s="37" t="inlineStr">
+        <is>
+          <t>哪些词方便搜索？</t>
+        </is>
+      </c>
+      <c r="C13" s="37" t="inlineStr">
+        <is>
+          <t>自由文本</t>
+        </is>
+      </c>
+      <c r="D13" s="37" t="inlineStr">
+        <is>
+          <t>放不适合作为稳定分类的关键词、产品名、平台名、项目名、指标名。</t>
+        </is>
+      </c>
+      <c r="E13" s="37" t="inlineStr">
+        <is>
+          <t>P800,净值走势,日报,信创,投顾</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="42" customHeight="1" s="29">
+      <c r="A14" s="37" t="inlineStr"/>
+      <c r="B14" s="37" t="inlineStr"/>
+      <c r="C14" s="37" t="inlineStr"/>
+      <c r="D14" s="37" t="inlineStr"/>
+      <c r="E14" s="37" t="inlineStr"/>
+    </row>
+    <row r="15" ht="42" customHeight="1" s="29">
+      <c r="A15" s="37" t="inlineStr">
+        <is>
+          <t>常见误区</t>
+        </is>
+      </c>
+      <c r="B15" s="37" t="inlineStr">
+        <is>
+          <t>正确处理</t>
+        </is>
+      </c>
+      <c r="C15" s="37" t="inlineStr"/>
+      <c r="D15" s="37" t="inlineStr"/>
+      <c r="E15" s="37" t="inlineStr"/>
+    </row>
+    <row r="16" ht="42" customHeight="1" s="29">
+      <c r="A16" s="39" t="inlineStr">
+        <is>
+          <t>把“混合型”写到业务分类</t>
+        </is>
+      </c>
+      <c r="B16" s="39" t="inlineStr">
+        <is>
+          <t>混合型属于实现模式；业务分类应写风控、投研、财富管理、团队管理等。</t>
+        </is>
+      </c>
+      <c r="C16" s="39" t="inlineStr"/>
+      <c r="D16" s="39" t="inlineStr"/>
+      <c r="E16" s="39" t="inlineStr"/>
+    </row>
+    <row r="17" ht="42" customHeight="1" s="29">
+      <c r="A17" s="37" t="inlineStr">
+        <is>
+          <t>把 Demo 当真实 Skill 包</t>
+        </is>
+      </c>
+      <c r="B17" s="37" t="inlineStr">
+        <is>
+          <t>只有 HTML 演示页时交付真实性填仅Demo；拿到 SKILL.md 和配套文件后再改为真实Skill包或真实Skill包+Demo。</t>
+        </is>
+      </c>
+      <c r="C17" s="37" t="inlineStr"/>
+      <c r="D17" s="37" t="inlineStr"/>
+      <c r="E17" s="37" t="inlineStr"/>
+    </row>
+    <row r="18" ht="42" customHeight="1" s="29">
+      <c r="A18" s="37" t="inlineStr">
+        <is>
+          <t>为了页面好看补假 references/scripts</t>
+        </is>
+      </c>
+      <c r="B18" s="37" t="inlineStr">
+        <is>
+          <t>禁止。页面只展示仓库实际存在的文件。缺什么就标缺什么，后续补真实文件。</t>
+        </is>
+      </c>
+      <c r="C18" s="37" t="inlineStr"/>
+      <c r="D18" s="37" t="inlineStr"/>
+      <c r="E18" s="37" t="inlineStr"/>
+    </row>
+    <row r="19" ht="42" customHeight="1" s="29">
+      <c r="A19" s="37" t="inlineStr">
+        <is>
+          <t>同一个场景既像投研又像 Agent</t>
+        </is>
+      </c>
+      <c r="B19" s="37" t="inlineStr">
+        <is>
+          <t>业务分类填投研；落地形态填 Agent 编排；实现模式填 Agent编排型。不要用一个字段包办所有信息。</t>
+        </is>
+      </c>
+      <c r="C19" s="37" t="inlineStr"/>
+      <c r="D19" s="37" t="inlineStr"/>
+      <c r="E19" s="37" t="inlineStr"/>
+    </row>
+  </sheetData>
+  <mergeCells count="2">
+    <mergeCell ref="A1:E1"/>
+    <mergeCell ref="B2:E2"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:AA220"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="34" customWidth="1" style="29" min="1" max="1"/>
+    <col width="28" customWidth="1" style="29" min="2" max="2"/>
+    <col width="18" customWidth="1" style="29" min="3" max="3"/>
     <col width="10" customWidth="1" style="29" min="4" max="4"/>
     <col width="8.890000343322754" customWidth="1" style="29" min="5" max="5"/>
     <col width="10" customWidth="1" style="29" min="6" max="6"/>
     <col width="12.22000026702881" customWidth="1" style="29" min="7" max="7"/>
-    <col width="28.88999938964844" customWidth="1" style="29" min="8" max="8"/>
-    <col width="23.32999992370605" customWidth="1" style="29" min="9" max="9"/>
-    <col width="25.55999946594238" customWidth="1" style="29" min="10" max="10"/>
-    <col width="25.55999946594238" customWidth="1" style="29" min="11" max="11"/>
-    <col width="11.10999965667725" customWidth="1" style="29" min="12" max="12"/>
-    <col width="11.10999965667725" customWidth="1" style="29" min="13" max="13"/>
-    <col width="10" customWidth="1" style="29" min="14" max="14"/>
-    <col width="13.32999992370605" customWidth="1" style="29" min="15" max="15"/>
+    <col width="42" customWidth="1" style="29" min="8" max="8"/>
+    <col width="26" customWidth="1" style="29" min="9" max="9"/>
+    <col width="16" customWidth="1" style="29" min="10" max="10"/>
+    <col width="18" customWidth="1" style="29" min="11" max="11"/>
+    <col width="18" customWidth="1" style="29" min="12" max="12"/>
+    <col width="20" customWidth="1" style="29" min="13" max="13"/>
+    <col width="34" customWidth="1" style="29" min="14" max="14"/>
+    <col width="34" customWidth="1" style="29" min="15" max="15"/>
     <col width="33.33000183105469" customWidth="1" style="29" min="16" max="16"/>
     <col width="28.88999938964844" customWidth="1" style="29" min="17" max="17"/>
     <col width="26.67000007629395" customWidth="1" style="29" min="18" max="18"/>
     <col width="26.67000007629395" customWidth="1" style="29" min="19" max="19"/>
-    <col width="26.67000007629395" customWidth="1" style="29" min="20" max="20"/>
+    <col width="42" customWidth="1" style="29" min="20" max="20"/>
     <col width="8.890000343322754" customWidth="1" style="29" min="21" max="21"/>
     <col width="20" customWidth="1" style="29" min="22" max="22"/>
     <col width="31.11000061035156" customWidth="1" style="29" min="23" max="23"/>
+    <col width="30" customWidth="1" style="29" min="26" max="26"/>
+    <col width="42" customWidth="1" style="29" min="27" max="27"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="20" t="inlineStr">
+      <c r="A1" s="32" t="inlineStr">
         <is>
           <t>Skill_ID</t>
         </is>
       </c>
-      <c r="B1" s="20" t="inlineStr">
+      <c r="B1" s="32" t="inlineStr">
         <is>
           <t>Skill名称</t>
         </is>
       </c>
-      <c r="C1" s="20" t="inlineStr">
+      <c r="C1" s="32" t="inlineStr">
         <is>
           <t>场景大类</t>
         </is>
       </c>
-      <c r="D1" s="20" t="inlineStr">
+      <c r="D1" s="32" t="inlineStr">
         <is>
           <t>行业</t>
         </is>
       </c>
-      <c r="E1" s="20" t="inlineStr">
+      <c r="E1" s="32" t="inlineStr">
         <is>
           <t>所属层级</t>
         </is>
       </c>
-      <c r="F1" s="20" t="inlineStr">
+      <c r="F1" s="32" t="inlineStr">
         <is>
           <t>业务子类</t>
         </is>
       </c>
-      <c r="G1" s="20" t="inlineStr">
+      <c r="G1" s="32" t="inlineStr">
         <is>
           <t>业务环节</t>
         </is>
       </c>
-      <c r="H1" s="20" t="inlineStr">
+      <c r="H1" s="32" t="inlineStr">
         <is>
           <t>能力说明</t>
         </is>
       </c>
-      <c r="I1" s="20" t="inlineStr">
+      <c r="I1" s="32" t="inlineStr">
         <is>
           <t>Skill分类</t>
         </is>
       </c>
-      <c r="J1" s="20" t="inlineStr">
+      <c r="J1" s="32" t="inlineStr">
+        <is>
+          <t>业务分类</t>
+        </is>
+      </c>
+      <c r="K1" s="32" t="inlineStr">
+        <is>
+          <t>落地形态</t>
+        </is>
+      </c>
+      <c r="L1" s="32" t="inlineStr">
+        <is>
+          <t>实现模式</t>
+        </is>
+      </c>
+      <c r="M1" s="32" t="inlineStr">
+        <is>
+          <t>交付真实性</t>
+        </is>
+      </c>
+      <c r="N1" s="32" t="inlineStr">
         <is>
           <t>关键输入</t>
         </is>
       </c>
-      <c r="K1" s="20" t="inlineStr">
+      <c r="O1" s="32" t="inlineStr">
         <is>
           <t>关键输出</t>
         </is>
       </c>
-      <c r="L1" s="20" t="inlineStr">
+      <c r="P1" s="32" t="inlineStr">
         <is>
           <t>建设状态</t>
         </is>
       </c>
-      <c r="M1" s="20" t="inlineStr">
+      <c r="Q1" s="32" t="inlineStr">
         <is>
           <t>展示状态</t>
         </is>
       </c>
-      <c r="N1" s="20" t="inlineStr">
+      <c r="R1" s="32" t="inlineStr">
         <is>
           <t>作者</t>
         </is>
       </c>
-      <c r="O1" s="20" t="inlineStr">
+      <c r="S1" s="32" t="inlineStr">
         <is>
           <t>来源平台</t>
         </is>
       </c>
-      <c r="P1" s="20" t="inlineStr">
+      <c r="T1" s="32" t="inlineStr">
         <is>
           <t>迁移建议</t>
         </is>
       </c>
-      <c r="Q1" s="20" t="inlineStr">
+      <c r="U1" s="32" t="inlineStr">
         <is>
           <t>Skill文件路径</t>
         </is>
       </c>
-      <c r="R1" s="20" t="inlineStr">
+      <c r="V1" s="32" t="inlineStr">
         <is>
           <t>Demo页面路径</t>
         </is>
       </c>
-      <c r="S1" s="20" t="inlineStr">
+      <c r="W1" s="32" t="inlineStr">
         <is>
           <t>规则/模板路径</t>
         </is>
       </c>
-      <c r="T1" s="20" t="inlineStr">
+      <c r="X1" s="32" t="inlineStr">
         <is>
           <t>样例数据路径</t>
         </is>
       </c>
-      <c r="U1" s="20" t="inlineStr">
+      <c r="Y1" s="32" t="inlineStr">
         <is>
           <t>版本</t>
         </is>
       </c>
-      <c r="V1" s="20" t="inlineStr">
+      <c r="Z1" s="32" t="inlineStr">
         <is>
           <t>标签</t>
         </is>
       </c>
-      <c r="W1" s="20" t="inlineStr">
+      <c r="AA1" s="32" t="inlineStr">
         <is>
           <t>备注</t>
         </is>
@@ -2506,36 +3060,56 @@
       <c r="G2" s="21" t="str"/>
       <c r="H2" s="21" t="str"/>
       <c r="I2" s="21" t="str"/>
-      <c r="J2" s="21" t="str"/>
-      <c r="K2" s="21" t="str"/>
+      <c r="J2" s="21" t="inlineStr">
+        <is>
+          <t>必填：风控 / 财富管理 / 投研 / 团队管理 / 投标 / 方案写作 / 技术评估 / 资料检索 / 合规 / 车险 / 客服 / 办公 / 科技</t>
+        </is>
+      </c>
+      <c r="K2" s="21" t="inlineStr">
+        <is>
+          <t>必填：独立 Skill / 主 Skill + L1 / Agent 编排 / L1 候选 / L3 专项候选</t>
+        </is>
+      </c>
       <c r="L2" s="21" t="inlineStr">
         <is>
+          <t>必填：规则型 / LLM生成型 / RAG知识检索型 / 数据分析型 / 工具调用型 / Agent编排型 / 混合型</t>
+        </is>
+      </c>
+      <c r="M2" s="21" t="inlineStr">
+        <is>
+          <t>必填：目录规划 / 仅Demo / 真实SKILL.md / 真实Skill包 / 真实Skill包+Demo</t>
+        </is>
+      </c>
+      <c r="N2" s="21" t="str"/>
+      <c r="O2" s="21" t="str"/>
+      <c r="P2" s="21" t="inlineStr">
+        <is>
           <t>可选：规划 / 已制作 / 已完成Demo</t>
         </is>
       </c>
-      <c r="M2" s="21" t="inlineStr">
+      <c r="Q2" s="21" t="inlineStr">
         <is>
           <t>可选：catalog / skill / demo</t>
         </is>
       </c>
-      <c r="N2" s="21" t="str"/>
-      <c r="O2" s="21" t="inlineStr">
+      <c r="R2" s="21" t="str"/>
+      <c r="S2" s="21" t="inlineStr">
         <is>
           <t>可选：Dumate / Dodo / 通用</t>
         </is>
       </c>
-      <c r="P2" s="21" t="inlineStr">
+      <c r="T2" s="21" t="inlineStr">
         <is>
           <t>建议写：保留平台实现 / 可迁移 / 需重做Demo</t>
         </is>
       </c>
-      <c r="Q2" s="21" t="str"/>
-      <c r="R2" s="21" t="str"/>
-      <c r="S2" s="21" t="str"/>
-      <c r="T2" s="21" t="str"/>
       <c r="U2" s="21" t="str"/>
       <c r="V2" s="21" t="str"/>
       <c r="W2" s="21" t="str"/>
+      <c r="X2" s="21" t="str"/>
+      <c r="Y2" s="21" t="str"/>
+      <c r="Z2" s="21" t="str"/>
+      <c r="AA2" s="21" t="str"/>
     </row>
     <row r="3">
       <c r="A3" s="21" t="inlineStr">
@@ -2585,66 +3159,86 @@
       </c>
       <c r="J3" s="21" t="inlineStr">
         <is>
+          <t>合规</t>
+        </is>
+      </c>
+      <c r="K3" s="21" t="inlineStr">
+        <is>
+          <t>独立 Skill</t>
+        </is>
+      </c>
+      <c r="L3" s="21" t="inlineStr">
+        <is>
+          <t>混合型</t>
+        </is>
+      </c>
+      <c r="M3" s="21" t="inlineStr">
+        <is>
+          <t>真实SKILL.md</t>
+        </is>
+      </c>
+      <c r="N3" s="21" t="inlineStr">
+        <is>
           <t>合同文本、条款库、审核规则</t>
         </is>
       </c>
-      <c r="K3" s="21" t="inlineStr">
+      <c r="O3" s="21" t="inlineStr">
         <is>
           <t>风险条款、修改建议、审核意见</t>
         </is>
       </c>
-      <c r="L3" s="21" t="inlineStr">
+      <c r="P3" s="21" t="inlineStr">
         <is>
           <t>已制作</t>
         </is>
       </c>
-      <c r="M3" s="21" t="inlineStr">
+      <c r="Q3" s="21" t="inlineStr">
         <is>
           <t>skill</t>
         </is>
       </c>
-      <c r="N3" s="21" t="inlineStr">
+      <c r="R3" s="21" t="inlineStr">
         <is>
           <t>张三</t>
         </is>
       </c>
-      <c r="O3" s="21" t="inlineStr">
+      <c r="S3" s="21" t="inlineStr">
         <is>
           <t>通用</t>
         </is>
       </c>
-      <c r="P3" s="21" t="inlineStr">
+      <c r="T3" s="21" t="inlineStr">
         <is>
           <t>可迁移为平台中立 Skill，并按需要适配 Dumate/Dodo 或网页 Demo。</t>
         </is>
       </c>
-      <c r="Q3" s="21" t="inlineStr">
+      <c r="U3" s="21" t="inlineStr">
         <is>
           <t>skills/contract-compliance-review/SKILL.md</t>
         </is>
       </c>
-      <c r="R3" s="21" t="str"/>
-      <c r="S3" s="21" t="inlineStr">
+      <c r="V3" s="21" t="str"/>
+      <c r="W3" s="21" t="inlineStr">
         <is>
           <t>skills/contract-compliance-review/references/</t>
         </is>
       </c>
-      <c r="T3" s="21" t="inlineStr">
+      <c r="X3" s="21" t="inlineStr">
         <is>
           <t>skills/contract-compliance-review/data/</t>
         </is>
       </c>
-      <c r="U3" s="21" t="inlineStr">
+      <c r="Y3" s="21" t="inlineStr">
         <is>
           <t>1.0.0</t>
         </is>
       </c>
-      <c r="V3" s="21" t="inlineStr">
+      <c r="Z3" s="21" t="inlineStr">
         <is>
           <t>银行,合规,合同审核</t>
         </is>
       </c>
-      <c r="W3" s="21" t="inlineStr">
+      <c r="AA3" s="21" t="inlineStr">
         <is>
           <t>没有 demo 页面时展示状态填 skill；有 demo.html 时填 demo。</t>
         </is>
@@ -2698,70 +3292,90 @@
       </c>
       <c r="J4" s="21" t="inlineStr">
         <is>
+          <t>风控</t>
+        </is>
+      </c>
+      <c r="K4" s="21" t="inlineStr">
+        <is>
+          <t>主 Skill + L1</t>
+        </is>
+      </c>
+      <c r="L4" s="21" t="inlineStr">
+        <is>
+          <t>混合型</t>
+        </is>
+      </c>
+      <c r="M4" s="21" t="inlineStr">
+        <is>
+          <t>真实Skill包+Demo</t>
+        </is>
+      </c>
+      <c r="N4" s="21" t="inlineStr">
+        <is>
           <t>企业画像、财务指标、公开风险、授信背景</t>
         </is>
       </c>
-      <c r="K4" s="21" t="inlineStr">
+      <c r="O4" s="21" t="inlineStr">
         <is>
           <t>风险线索、走访问询清单、补充材料清单</t>
         </is>
       </c>
-      <c r="L4" s="21" t="inlineStr">
+      <c r="P4" s="21" t="inlineStr">
         <is>
           <t>已完成Demo</t>
         </is>
       </c>
-      <c r="M4" s="21" t="inlineStr">
+      <c r="Q4" s="21" t="inlineStr">
         <is>
           <t>demo</t>
         </is>
       </c>
-      <c r="N4" s="21" t="inlineStr">
+      <c r="R4" s="21" t="inlineStr">
         <is>
           <t>李四</t>
         </is>
       </c>
-      <c r="O4" s="21" t="inlineStr">
+      <c r="S4" s="21" t="inlineStr">
         <is>
           <t>通用</t>
         </is>
       </c>
-      <c r="P4" s="21" t="inlineStr">
+      <c r="T4" s="21" t="inlineStr">
         <is>
           <t>已有 Demo，可沉淀为售前演示仓库样板。</t>
         </is>
       </c>
-      <c r="Q4" s="21" t="inlineStr">
+      <c r="U4" s="21" t="inlineStr">
         <is>
           <t>skills/credit-risk-demo/SKILL.md</t>
         </is>
       </c>
-      <c r="R4" s="21" t="inlineStr">
+      <c r="V4" s="21" t="inlineStr">
         <is>
           <t>skills/credit-risk-demo/demo.html</t>
         </is>
       </c>
-      <c r="S4" s="21" t="inlineStr">
+      <c r="W4" s="21" t="inlineStr">
         <is>
           <t>skills/credit-risk-demo/references/</t>
         </is>
       </c>
-      <c r="T4" s="21" t="inlineStr">
+      <c r="X4" s="21" t="inlineStr">
         <is>
           <t>skills/credit-risk-demo/data/</t>
         </is>
       </c>
-      <c r="U4" s="21" t="inlineStr">
+      <c r="Y4" s="21" t="inlineStr">
         <is>
           <t>1.0.0</t>
         </is>
       </c>
-      <c r="V4" s="21" t="inlineStr">
+      <c r="Z4" s="21" t="inlineStr">
         <is>
           <t>银行,风控,授信,demo</t>
         </is>
       </c>
-      <c r="W4" s="21" t="inlineStr">
+      <c r="AA4" s="21" t="inlineStr">
         <is>
           <t>有 demo 页面时，Demo页面路径必须填写。</t>
         </is>
@@ -2815,66 +3429,86 @@
       </c>
       <c r="J5" s="21" t="inlineStr">
         <is>
+          <t>需求调研</t>
+        </is>
+      </c>
+      <c r="K5" s="21" t="inlineStr">
+        <is>
+          <t>独立 Skill</t>
+        </is>
+      </c>
+      <c r="L5" s="21" t="inlineStr">
+        <is>
+          <t>LLM生成型</t>
+        </is>
+      </c>
+      <c r="M5" s="21" t="inlineStr">
+        <is>
+          <t>真实SKILL.md</t>
+        </is>
+      </c>
+      <c r="N5" s="21" t="inlineStr">
+        <is>
           <t>会议纪要、录音转写、客户背景、项目上下文</t>
         </is>
       </c>
-      <c r="K5" s="21" t="inlineStr">
+      <c r="O5" s="21" t="inlineStr">
         <is>
           <t>结构化纪要、需求清单、风险点、下一步行动项</t>
         </is>
       </c>
-      <c r="L5" s="21" t="inlineStr">
+      <c r="P5" s="21" t="inlineStr">
         <is>
           <t>已制作</t>
         </is>
       </c>
-      <c r="M5" s="21" t="inlineStr">
+      <c r="Q5" s="21" t="inlineStr">
         <is>
           <t>skill</t>
         </is>
       </c>
-      <c r="N5" s="21" t="inlineStr">
+      <c r="R5" s="21" t="inlineStr">
         <is>
           <t>王五</t>
         </is>
       </c>
-      <c r="O5" s="21" t="inlineStr">
+      <c r="S5" s="21" t="inlineStr">
         <is>
           <t>通用</t>
         </is>
       </c>
-      <c r="P5" s="21" t="inlineStr">
+      <c r="T5" s="21" t="inlineStr">
         <is>
           <t>优先沉淀为 SA-AI 内化 Skill，后续按需要适配不同智能体平台。</t>
         </is>
       </c>
-      <c r="Q5" s="21" t="inlineStr">
+      <c r="U5" s="21" t="inlineStr">
         <is>
           <t>skills/sa-interview-briefing/SKILL.md</t>
         </is>
       </c>
-      <c r="R5" s="21" t="str"/>
-      <c r="S5" s="21" t="inlineStr">
+      <c r="V5" s="21" t="str"/>
+      <c r="W5" s="21" t="inlineStr">
         <is>
           <t>skills/sa-interview-briefing/references/</t>
         </is>
       </c>
-      <c r="T5" s="21" t="inlineStr">
+      <c r="X5" s="21" t="inlineStr">
         <is>
           <t>skills/sa-interview-briefing/examples/</t>
         </is>
       </c>
-      <c r="U5" s="21" t="inlineStr">
+      <c r="Y5" s="21" t="inlineStr">
         <is>
           <t>1.0.0</t>
         </is>
       </c>
-      <c r="V5" s="21" t="inlineStr">
+      <c r="Z5" s="21" t="inlineStr">
         <is>
           <t>SA内部,售前,会议纪要,需求调研</t>
         </is>
       </c>
-      <c r="W5" s="21" t="inlineStr">
+      <c r="AA5" s="21" t="inlineStr">
         <is>
           <t>面向 SA 日常工作的内部 AI 内化场景，不归入客户金融业务场景。</t>
         </is>
@@ -2928,70 +3562,90 @@
       </c>
       <c r="J6" s="24" t="inlineStr">
         <is>
+          <t>财富管理</t>
+        </is>
+      </c>
+      <c r="K6" s="24" t="inlineStr">
+        <is>
+          <t>独立 Skill</t>
+        </is>
+      </c>
+      <c r="L6" s="24" t="inlineStr">
+        <is>
+          <t>数据分析型</t>
+        </is>
+      </c>
+      <c r="M6" s="24" t="inlineStr">
+        <is>
+          <t>真实Skill包+Demo</t>
+        </is>
+      </c>
+      <c r="N6" s="24" t="inlineStr">
+        <is>
           <t>产品材料、持仓截图、净值数据、客户问题、基金/经理/公司数据</t>
         </is>
       </c>
-      <c r="K6" s="24" t="inlineStr">
+      <c r="O6" s="24" t="inlineStr">
         <is>
           <t>产品解读、净值归因、量化分析、风险提示、客户沟通话术、持仓报告</t>
         </is>
       </c>
-      <c r="L6" s="24" t="inlineStr">
+      <c r="P6" s="24" t="inlineStr">
         <is>
           <t>已开发</t>
         </is>
       </c>
-      <c r="M6" s="24" t="inlineStr">
+      <c r="Q6" s="24" t="inlineStr">
         <is>
           <t>demo</t>
         </is>
       </c>
-      <c r="N6" s="24" t="inlineStr">
+      <c r="R6" s="24" t="inlineStr">
         <is>
           <t>同事/Fund Advisor Skill包</t>
         </is>
       </c>
-      <c r="O6" s="24" t="inlineStr">
+      <c r="S6" s="24" t="inlineStr">
         <is>
           <t>Dumate/Dodo</t>
         </is>
       </c>
-      <c r="P6" s="24" t="inlineStr">
+      <c r="T6" s="24" t="inlineStr">
         <is>
           <t>已补齐 fund-advisor 真实 Skill 包；页面 Demo 与真实 SKILL.md、脚本、数据、引用文档共同展示。后续可继续做 Web UI 运行验证和真实数据接入。</t>
         </is>
       </c>
-      <c r="Q6" s="24" t="inlineStr">
+      <c r="U6" s="24" t="inlineStr">
         <is>
           <t>presales-skill-matrix/wealth-product-net-value-analysis/SKILL.md</t>
         </is>
       </c>
-      <c r="R6" s="24" t="inlineStr">
+      <c r="V6" s="24" t="inlineStr">
         <is>
           <t>presales-skill-matrix/wealth-product-net-value-analysis/wealth-product-net-value-analysis-demo.html</t>
         </is>
       </c>
-      <c r="S6" s="24" t="inlineStr">
+      <c r="W6" s="24" t="inlineStr">
         <is>
           <t>presales-skill-matrix/wealth-product-net-value-analysis/references/</t>
         </is>
       </c>
-      <c r="T6" s="24" t="inlineStr">
+      <c r="X6" s="24" t="inlineStr">
         <is>
           <t>presales-skill-matrix/wealth-product-net-value-analysis/data/</t>
         </is>
       </c>
-      <c r="U6" s="24" t="inlineStr">
+      <c r="Y6" s="24" t="inlineStr">
         <is>
           <t>5.0.0</t>
         </is>
       </c>
-      <c r="V6" s="24" t="inlineStr">
+      <c r="Z6" s="24" t="inlineStr">
         <is>
           <t>财富管理,基金投顾,产品解读,净值走势,持仓识别,量化分析,客户沟通,已开发Skill</t>
         </is>
       </c>
-      <c r="W6" s="24" t="inlineStr">
+      <c r="AA6" s="24" t="inlineStr">
         <is>
           <t>2026-06-18 已接入 fund-advisor 完整 Skill 包；保留同事提供的财富产品解读页面 Demo。</t>
         </is>
@@ -3045,70 +3699,90 @@
       </c>
       <c r="J7" s="24" t="inlineStr">
         <is>
+          <t>投研</t>
+        </is>
+      </c>
+      <c r="K7" s="24" t="inlineStr">
+        <is>
+          <t>Agent 编排</t>
+        </is>
+      </c>
+      <c r="L7" s="24" t="inlineStr">
+        <is>
+          <t>Agent编排型</t>
+        </is>
+      </c>
+      <c r="M7" s="24" t="inlineStr">
+        <is>
+          <t>真实Skill包+Demo</t>
+        </is>
+      </c>
+      <c r="N7" s="24" t="inlineStr">
+        <is>
           <t>股票代码、研究周期、市场行情、新闻舆情、产业链方向、持仓或研究口径</t>
         </is>
       </c>
-      <c r="K7" s="24" t="inlineStr">
+      <c r="O7" s="24" t="inlineStr">
         <is>
           <t>个股投研摘要、技术分析、产业链关注点、多维评分、风险提示、PPT/PDF报告</t>
         </is>
       </c>
-      <c r="L7" s="24" t="inlineStr">
+      <c r="P7" s="24" t="inlineStr">
         <is>
           <t>已开发</t>
         </is>
       </c>
-      <c r="M7" s="24" t="inlineStr">
+      <c r="Q7" s="24" t="inlineStr">
         <is>
           <t>demo</t>
         </is>
       </c>
-      <c r="N7" s="24" t="inlineStr">
+      <c r="R7" s="24" t="inlineStr">
         <is>
           <t>同事/Dumate场景积累</t>
         </is>
       </c>
-      <c r="O7" s="24" t="inlineStr">
+      <c r="S7" s="24" t="inlineStr">
         <is>
           <t>Dumate</t>
         </is>
       </c>
-      <c r="P7" s="24" t="inlineStr">
+      <c r="T7" s="24" t="inlineStr">
         <is>
           <t>已接收真实 ai-stock-researcher Skill 包；网页侧补同风格售前 Demo，底层实时数据和 MCP 调用可在客户环境按平台适配。</t>
         </is>
       </c>
-      <c r="Q7" s="24" t="inlineStr">
+      <c r="U7" s="24" t="inlineStr">
         <is>
           <t>presales-skill-matrix/ai-stock-researcher/SKILL.md</t>
         </is>
       </c>
-      <c r="R7" s="24" t="inlineStr">
+      <c r="V7" s="24" t="inlineStr">
         <is>
           <t>presales-skill-matrix/ai-stock-researcher/AI股票投研工作台Demo.html</t>
         </is>
       </c>
-      <c r="S7" s="24" t="inlineStr">
+      <c r="W7" s="24" t="inlineStr">
         <is>
           <t>presales-skill-matrix/ai-stock-researcher/README.md</t>
         </is>
       </c>
-      <c r="T7" s="24" t="inlineStr">
+      <c r="X7" s="24" t="inlineStr">
         <is>
           <t>presales-skill-matrix/ai-stock-researcher/templates/index.html</t>
         </is>
       </c>
-      <c r="U7" s="24" t="inlineStr">
+      <c r="Y7" s="24" t="inlineStr">
         <is>
           <t>1.0.11</t>
         </is>
       </c>
-      <c r="V7" s="24" t="inlineStr">
+      <c r="Z7" s="24" t="inlineStr">
         <is>
           <t>投研,个股分析,产业链,报告生成</t>
         </is>
       </c>
-      <c r="W7" s="24" t="inlineStr">
+      <c r="AA7" s="24" t="inlineStr">
         <is>
           <t>来源：Dumate场景积累-2026.05.29.pdf；已对齐同事提供的 aistockresearcher-1.0.11.zip，真实 Skill 包已落入仓库。</t>
         </is>
@@ -3162,54 +3836,74 @@
       </c>
       <c r="J8" s="24" t="inlineStr">
         <is>
+          <t>投研</t>
+        </is>
+      </c>
+      <c r="K8" s="24" t="inlineStr">
+        <is>
+          <t>Agent 编排</t>
+        </is>
+      </c>
+      <c r="L8" s="24" t="inlineStr">
+        <is>
+          <t>LLM生成型</t>
+        </is>
+      </c>
+      <c r="M8" s="24" t="inlineStr">
+        <is>
+          <t>目录规划</t>
+        </is>
+      </c>
+      <c r="N8" s="24" t="inlineStr">
+        <is>
           <t>资讯源、推送时间、关注市场、摘要口径</t>
         </is>
       </c>
-      <c r="K8" s="24" t="inlineStr">
+      <c r="O8" s="24" t="inlineStr">
         <is>
           <t>每日资讯摘要、重点事件、投资顾问关注提示</t>
         </is>
       </c>
-      <c r="L8" s="24" t="inlineStr">
+      <c r="P8" s="24" t="inlineStr">
         <is>
           <t>规划</t>
         </is>
       </c>
-      <c r="M8" s="24" t="inlineStr">
+      <c r="Q8" s="24" t="inlineStr">
         <is>
           <t>catalog</t>
         </is>
       </c>
-      <c r="N8" s="24" t="inlineStr">
+      <c r="R8" s="24" t="inlineStr">
         <is>
           <t>同事/Dumate场景积累</t>
         </is>
       </c>
-      <c r="O8" s="24" t="inlineStr">
+      <c r="S8" s="24" t="inlineStr">
         <is>
           <t>Dumate/Dodo</t>
         </is>
       </c>
-      <c r="P8" s="24" t="inlineStr">
+      <c r="T8" s="24" t="inlineStr">
         <is>
           <t>若依赖平台定时任务可保留 Dumate/Dodo 实现；仓库沉淀提示词、摘要模板和边界。</t>
         </is>
       </c>
-      <c r="Q8" s="24" t="str"/>
-      <c r="R8" s="24" t="str"/>
-      <c r="S8" s="24" t="str"/>
-      <c r="T8" s="24" t="str"/>
-      <c r="U8" s="24" t="inlineStr">
+      <c r="U8" s="24" t="str"/>
+      <c r="V8" s="24" t="str"/>
+      <c r="W8" s="24" t="str"/>
+      <c r="X8" s="24" t="str"/>
+      <c r="Y8" s="24" t="inlineStr">
         <is>
           <t>0.1.0</t>
         </is>
       </c>
-      <c r="V8" s="24" t="inlineStr">
+      <c r="Z8" s="24" t="inlineStr">
         <is>
           <t>投研助手,资讯推送,定时任务</t>
         </is>
       </c>
-      <c r="W8" s="24" t="inlineStr">
+      <c r="AA8" s="24" t="inlineStr">
         <is>
           <t>来源：Dumate场景积累-2026.05.29.pdf。</t>
         </is>
@@ -3263,54 +3957,74 @@
       </c>
       <c r="J9" s="24" t="inlineStr">
         <is>
+          <t>方案写作</t>
+        </is>
+      </c>
+      <c r="K9" s="24" t="inlineStr">
+        <is>
+          <t>独立 Skill</t>
+        </is>
+      </c>
+      <c r="L9" s="24" t="inlineStr">
+        <is>
+          <t>LLM生成型</t>
+        </is>
+      </c>
+      <c r="M9" s="24" t="inlineStr">
+        <is>
+          <t>目录规划</t>
+        </is>
+      </c>
+      <c r="N9" s="24" t="inlineStr">
+        <is>
           <t>PPT方案、客户类型、交流对象、Prompt</t>
         </is>
       </c>
-      <c r="K9" s="24" t="inlineStr">
+      <c r="O9" s="24" t="inlineStr">
         <is>
           <t>PPT讲解文案、重点话术、客户关注点映射</t>
         </is>
       </c>
-      <c r="L9" s="24" t="inlineStr">
+      <c r="P9" s="24" t="inlineStr">
         <is>
           <t>规划</t>
         </is>
       </c>
-      <c r="M9" s="24" t="inlineStr">
+      <c r="Q9" s="24" t="inlineStr">
         <is>
           <t>catalog</t>
         </is>
       </c>
-      <c r="N9" s="24" t="inlineStr">
+      <c r="R9" s="24" t="inlineStr">
         <is>
           <t>同事/Dumate场景积累</t>
         </is>
       </c>
-      <c r="O9" s="24" t="inlineStr">
+      <c r="S9" s="24" t="inlineStr">
         <is>
           <t>Dumate</t>
         </is>
       </c>
-      <c r="P9" s="24" t="inlineStr">
+      <c r="T9" s="24" t="inlineStr">
         <is>
           <t>优先迁移为 SA 内部 Skill；PPT备注页自动插入属于平台能力，可作为后续 Demo 优化项。</t>
         </is>
       </c>
-      <c r="Q9" s="24" t="str"/>
-      <c r="R9" s="24" t="str"/>
-      <c r="S9" s="24" t="str"/>
-      <c r="T9" s="24" t="str"/>
-      <c r="U9" s="24" t="inlineStr">
+      <c r="U9" s="24" t="str"/>
+      <c r="V9" s="24" t="str"/>
+      <c r="W9" s="24" t="str"/>
+      <c r="X9" s="24" t="str"/>
+      <c r="Y9" s="24" t="inlineStr">
         <is>
           <t>0.1.0</t>
         </is>
       </c>
-      <c r="V9" s="24" t="inlineStr">
+      <c r="Z9" s="24" t="inlineStr">
         <is>
           <t>SA内部,售前,PPT文案,客户心智</t>
         </is>
       </c>
-      <c r="W9" s="24" t="inlineStr">
+      <c r="AA9" s="24" t="inlineStr">
         <is>
           <t>来源：Dumate场景积累-2026.05.29.pdf；原文提到备注页插入仍需优化。</t>
         </is>
@@ -3364,54 +4078,74 @@
       </c>
       <c r="J10" s="24" t="inlineStr">
         <is>
+          <t>技术评估</t>
+        </is>
+      </c>
+      <c r="K10" s="24" t="inlineStr">
+        <is>
+          <t>独立 Skill</t>
+        </is>
+      </c>
+      <c r="L10" s="24" t="inlineStr">
+        <is>
+          <t>数据分析型</t>
+        </is>
+      </c>
+      <c r="M10" s="24" t="inlineStr">
+        <is>
+          <t>目录规划</t>
+        </is>
+      </c>
+      <c r="N10" s="24" t="inlineStr">
+        <is>
           <t>产品源代码、依赖文件、客户信创要求</t>
         </is>
       </c>
-      <c r="K10" s="24" t="inlineStr">
+      <c r="O10" s="24" t="inlineStr">
         <is>
           <t>数据库/中间件清单、信创适配风险、改造建议</t>
         </is>
       </c>
-      <c r="L10" s="24" t="inlineStr">
+      <c r="P10" s="24" t="inlineStr">
         <is>
           <t>规划</t>
         </is>
       </c>
-      <c r="M10" s="24" t="inlineStr">
+      <c r="Q10" s="24" t="inlineStr">
         <is>
           <t>catalog</t>
         </is>
       </c>
-      <c r="N10" s="24" t="inlineStr">
+      <c r="R10" s="24" t="inlineStr">
         <is>
           <t>同事/Dumate场景积累</t>
         </is>
       </c>
-      <c r="O10" s="24" t="inlineStr">
+      <c r="S10" s="24" t="inlineStr">
         <is>
           <t>Dumate/Dodo</t>
         </is>
       </c>
-      <c r="P10" s="24" t="inlineStr">
+      <c r="T10" s="24" t="inlineStr">
         <is>
           <t>需要评估平台代码读取能力；仓库沉淀检查清单、输出模板和安全边界。</t>
         </is>
       </c>
-      <c r="Q10" s="24" t="str"/>
-      <c r="R10" s="24" t="str"/>
-      <c r="S10" s="24" t="str"/>
-      <c r="T10" s="24" t="str"/>
-      <c r="U10" s="24" t="inlineStr">
+      <c r="U10" s="24" t="str"/>
+      <c r="V10" s="24" t="str"/>
+      <c r="W10" s="24" t="str"/>
+      <c r="X10" s="24" t="str"/>
+      <c r="Y10" s="24" t="inlineStr">
         <is>
           <t>0.1.0</t>
         </is>
       </c>
-      <c r="V10" s="24" t="inlineStr">
+      <c r="Z10" s="24" t="inlineStr">
         <is>
           <t>SA内部,信创,代码分析,技术评估</t>
         </is>
       </c>
-      <c r="W10" s="24" t="inlineStr">
+      <c r="AA10" s="24" t="inlineStr">
         <is>
           <t>来源：Dumate场景积累-2026.05.29.pdf。</t>
         </is>
@@ -3465,54 +4199,74 @@
       </c>
       <c r="J11" s="24" t="inlineStr">
         <is>
+          <t>方案写作</t>
+        </is>
+      </c>
+      <c r="K11" s="24" t="inlineStr">
+        <is>
+          <t>独立 Skill</t>
+        </is>
+      </c>
+      <c r="L11" s="24" t="inlineStr">
+        <is>
+          <t>数据分析型</t>
+        </is>
+      </c>
+      <c r="M11" s="24" t="inlineStr">
+        <is>
+          <t>目录规划</t>
+        </is>
+      </c>
+      <c r="N11" s="24" t="inlineStr">
+        <is>
           <t>客户需求、系统模块、数据流、架构约束</t>
         </is>
       </c>
-      <c r="K11" s="24" t="inlineStr">
+      <c r="O11" s="24" t="inlineStr">
         <is>
           <t>drawio架构图、数据流图、图示说明</t>
         </is>
       </c>
-      <c r="L11" s="24" t="inlineStr">
+      <c r="P11" s="24" t="inlineStr">
         <is>
           <t>规划</t>
         </is>
       </c>
-      <c r="M11" s="24" t="inlineStr">
+      <c r="Q11" s="24" t="inlineStr">
         <is>
           <t>catalog</t>
         </is>
       </c>
-      <c r="N11" s="24" t="inlineStr">
+      <c r="R11" s="24" t="inlineStr">
         <is>
           <t>同事/Dumate场景积累</t>
         </is>
       </c>
-      <c r="O11" s="24" t="inlineStr">
+      <c r="S11" s="24" t="inlineStr">
         <is>
           <t>Dumate</t>
         </is>
       </c>
-      <c r="P11" s="24" t="inlineStr">
+      <c r="T11" s="24" t="inlineStr">
         <is>
           <t>适合迁移为平台中立模板；Demo 可输出 drawio 文件而不是纯图片。</t>
         </is>
       </c>
-      <c r="Q11" s="24" t="str"/>
-      <c r="R11" s="24" t="str"/>
-      <c r="S11" s="24" t="str"/>
-      <c r="T11" s="24" t="str"/>
-      <c r="U11" s="24" t="inlineStr">
+      <c r="U11" s="24" t="str"/>
+      <c r="V11" s="24" t="str"/>
+      <c r="W11" s="24" t="str"/>
+      <c r="X11" s="24" t="str"/>
+      <c r="Y11" s="24" t="inlineStr">
         <is>
           <t>0.1.0</t>
         </is>
       </c>
-      <c r="V11" s="24" t="inlineStr">
+      <c r="Z11" s="24" t="inlineStr">
         <is>
           <t>SA内部,架构图,drawio,方案设计</t>
         </is>
       </c>
-      <c r="W11" s="24" t="inlineStr">
+      <c r="AA11" s="24" t="inlineStr">
         <is>
           <t>来源：Dumate场景积累-2026.05.29.pdf；PDF 示例含 drawio 文件。</t>
         </is>
@@ -3566,54 +4320,74 @@
       </c>
       <c r="J12" s="24" t="inlineStr">
         <is>
+          <t>投标</t>
+        </is>
+      </c>
+      <c r="K12" s="24" t="inlineStr">
+        <is>
+          <t>独立 Skill</t>
+        </is>
+      </c>
+      <c r="L12" s="24" t="inlineStr">
+        <is>
+          <t>LLM生成型</t>
+        </is>
+      </c>
+      <c r="M12" s="24" t="inlineStr">
+        <is>
+          <t>目录规划</t>
+        </is>
+      </c>
+      <c r="N12" s="24" t="inlineStr">
+        <is>
           <t>招标文件、评分表、项目需求、历史方案</t>
         </is>
       </c>
-      <c r="K12" s="24" t="inlineStr">
+      <c r="O12" s="24" t="inlineStr">
         <is>
           <t>应标目录、章节编写要点、评分点映射</t>
         </is>
       </c>
-      <c r="L12" s="24" t="inlineStr">
+      <c r="P12" s="24" t="inlineStr">
         <is>
           <t>规划</t>
         </is>
       </c>
-      <c r="M12" s="24" t="inlineStr">
+      <c r="Q12" s="24" t="inlineStr">
         <is>
           <t>catalog</t>
         </is>
       </c>
-      <c r="N12" s="24" t="inlineStr">
+      <c r="R12" s="24" t="inlineStr">
         <is>
           <t>同事/Dumate场景积累</t>
         </is>
       </c>
-      <c r="O12" s="24" t="inlineStr">
+      <c r="S12" s="24" t="inlineStr">
         <is>
           <t>Dumate</t>
         </is>
       </c>
-      <c r="P12" s="24" t="inlineStr">
+      <c r="T12" s="24" t="inlineStr">
         <is>
           <t>优先沉淀为 SA 内部高频 Skill；可后续做成可演示投标工作台。</t>
         </is>
       </c>
-      <c r="Q12" s="24" t="str"/>
-      <c r="R12" s="24" t="str"/>
-      <c r="S12" s="24" t="str"/>
-      <c r="T12" s="24" t="str"/>
-      <c r="U12" s="24" t="inlineStr">
+      <c r="U12" s="24" t="str"/>
+      <c r="V12" s="24" t="str"/>
+      <c r="W12" s="24" t="str"/>
+      <c r="X12" s="24" t="str"/>
+      <c r="Y12" s="24" t="inlineStr">
         <is>
           <t>0.1.0</t>
         </is>
       </c>
-      <c r="V12" s="24" t="inlineStr">
+      <c r="Z12" s="24" t="inlineStr">
         <is>
           <t>SA内部,投标,应标,技术方案</t>
         </is>
       </c>
-      <c r="W12" s="24" t="inlineStr">
+      <c r="AA12" s="24" t="inlineStr">
         <is>
           <t>来源：Dumate场景积累-2026.05.29.pdf。</t>
         </is>
@@ -3667,54 +4441,74 @@
       </c>
       <c r="J13" s="24" t="inlineStr">
         <is>
+          <t>投标</t>
+        </is>
+      </c>
+      <c r="K13" s="24" t="inlineStr">
+        <is>
+          <t>独立 Skill</t>
+        </is>
+      </c>
+      <c r="L13" s="24" t="inlineStr">
+        <is>
+          <t>规则型</t>
+        </is>
+      </c>
+      <c r="M13" s="24" t="inlineStr">
+        <is>
+          <t>目录规划</t>
+        </is>
+      </c>
+      <c r="N13" s="24" t="inlineStr">
+        <is>
           <t>招标文件、资格要求、评分规则</t>
         </is>
       </c>
-      <c r="K13" s="24" t="inlineStr">
+      <c r="O13" s="24" t="inlineStr">
         <is>
           <t>废标项清单、关键红线、风险提示、待确认问题</t>
         </is>
       </c>
-      <c r="L13" s="24" t="inlineStr">
+      <c r="P13" s="24" t="inlineStr">
         <is>
           <t>规划</t>
         </is>
       </c>
-      <c r="M13" s="24" t="inlineStr">
+      <c r="Q13" s="24" t="inlineStr">
         <is>
           <t>catalog</t>
         </is>
       </c>
-      <c r="N13" s="24" t="inlineStr">
+      <c r="R13" s="24" t="inlineStr">
         <is>
           <t>同事/Dumate场景积累</t>
         </is>
       </c>
-      <c r="O13" s="24" t="inlineStr">
+      <c r="S13" s="24" t="inlineStr">
         <is>
           <t>Dumate</t>
         </is>
       </c>
-      <c r="P13" s="24" t="inlineStr">
+      <c r="T13" s="24" t="inlineStr">
         <is>
           <t>非常适合做 SA-AI 内化 Demo；仓库沉淀规则模板，平台负责文档解析。</t>
         </is>
       </c>
-      <c r="Q13" s="24" t="str"/>
-      <c r="R13" s="24" t="str"/>
-      <c r="S13" s="24" t="str"/>
-      <c r="T13" s="24" t="str"/>
-      <c r="U13" s="24" t="inlineStr">
+      <c r="U13" s="24" t="str"/>
+      <c r="V13" s="24" t="str"/>
+      <c r="W13" s="24" t="str"/>
+      <c r="X13" s="24" t="str"/>
+      <c r="Y13" s="24" t="inlineStr">
         <is>
           <t>0.1.0</t>
         </is>
       </c>
-      <c r="V13" s="24" t="inlineStr">
+      <c r="Z13" s="24" t="inlineStr">
         <is>
           <t>SA内部,投标,废标项,招标文件</t>
         </is>
       </c>
-      <c r="W13" s="24" t="inlineStr">
+      <c r="AA13" s="24" t="inlineStr">
         <is>
           <t>来源：Dumate场景积累-2026.05.29.pdf；PDF 提到已有视频案例。</t>
         </is>
@@ -3768,54 +4562,74 @@
       </c>
       <c r="J14" s="24" t="inlineStr">
         <is>
+          <t>投标</t>
+        </is>
+      </c>
+      <c r="K14" s="24" t="inlineStr">
+        <is>
+          <t>独立 Skill</t>
+        </is>
+      </c>
+      <c r="L14" s="24" t="inlineStr">
+        <is>
+          <t>数据分析型</t>
+        </is>
+      </c>
+      <c r="M14" s="24" t="inlineStr">
+        <is>
+          <t>目录规划</t>
+        </is>
+      </c>
+      <c r="N14" s="24" t="inlineStr">
+        <is>
           <t>招标文件、投标文件、评分表、响应矩阵</t>
         </is>
       </c>
-      <c r="K14" s="24" t="inlineStr">
+      <c r="O14" s="24" t="inlineStr">
         <is>
           <t>应标分析报告、缺口清单、风险点、修改建议</t>
         </is>
       </c>
-      <c r="L14" s="24" t="inlineStr">
+      <c r="P14" s="24" t="inlineStr">
         <is>
           <t>规划</t>
         </is>
       </c>
-      <c r="M14" s="24" t="inlineStr">
+      <c r="Q14" s="24" t="inlineStr">
         <is>
           <t>catalog</t>
         </is>
       </c>
-      <c r="N14" s="24" t="inlineStr">
+      <c r="R14" s="24" t="inlineStr">
         <is>
           <t>同事/Dumate场景积累</t>
         </is>
       </c>
-      <c r="O14" s="24" t="inlineStr">
+      <c r="S14" s="24" t="inlineStr">
         <is>
           <t>Dumate</t>
         </is>
       </c>
-      <c r="P14" s="24" t="inlineStr">
+      <c r="T14" s="24" t="inlineStr">
         <is>
           <t>可优先做成售前内部演示；与废标项提取组成投标助手链路。</t>
         </is>
       </c>
-      <c r="Q14" s="24" t="str"/>
-      <c r="R14" s="24" t="str"/>
-      <c r="S14" s="24" t="str"/>
-      <c r="T14" s="24" t="str"/>
-      <c r="U14" s="24" t="inlineStr">
+      <c r="U14" s="24" t="str"/>
+      <c r="V14" s="24" t="str"/>
+      <c r="W14" s="24" t="str"/>
+      <c r="X14" s="24" t="str"/>
+      <c r="Y14" s="24" t="inlineStr">
         <is>
           <t>0.1.0</t>
         </is>
       </c>
-      <c r="V14" s="24" t="inlineStr">
+      <c r="Z14" s="24" t="inlineStr">
         <is>
           <t>SA内部,投标,应标分析,文档审查</t>
         </is>
       </c>
-      <c r="W14" s="24" t="inlineStr">
+      <c r="AA14" s="24" t="inlineStr">
         <is>
           <t>来源：Dumate场景积累-2026.05.29.pdf；PDF 提到已有视频案例。</t>
         </is>
@@ -3869,54 +4683,74 @@
       </c>
       <c r="J15" s="24" t="inlineStr">
         <is>
+          <t>方案写作</t>
+        </is>
+      </c>
+      <c r="K15" s="24" t="inlineStr">
+        <is>
+          <t>独立 Skill</t>
+        </is>
+      </c>
+      <c r="L15" s="24" t="inlineStr">
+        <is>
+          <t>RAG知识检索型</t>
+        </is>
+      </c>
+      <c r="M15" s="24" t="inlineStr">
+        <is>
+          <t>目录规划</t>
+        </is>
+      </c>
+      <c r="N15" s="24" t="inlineStr">
+        <is>
           <t>案例知识库、客户行业、交流目标、PPT模板</t>
         </is>
       </c>
-      <c r="K15" s="24" t="inlineStr">
+      <c r="O15" s="24" t="inlineStr">
         <is>
           <t>案例介绍方案、PPT大纲、客户化材料</t>
         </is>
       </c>
-      <c r="L15" s="24" t="inlineStr">
+      <c r="P15" s="24" t="inlineStr">
         <is>
           <t>规划</t>
         </is>
       </c>
-      <c r="M15" s="24" t="inlineStr">
+      <c r="Q15" s="24" t="inlineStr">
         <is>
           <t>catalog</t>
         </is>
       </c>
-      <c r="N15" s="24" t="inlineStr">
+      <c r="R15" s="24" t="inlineStr">
         <is>
           <t>同事/Dumate场景积累</t>
         </is>
       </c>
-      <c r="O15" s="24" t="inlineStr">
+      <c r="S15" s="24" t="inlineStr">
         <is>
           <t>Dumate</t>
         </is>
       </c>
-      <c r="P15" s="24" t="inlineStr">
+      <c r="T15" s="24" t="inlineStr">
         <is>
           <t>仓库沉淀案例结构和PPT模板；平台实现可依赖 Dumate 知识库。</t>
         </is>
       </c>
-      <c r="Q15" s="24" t="str"/>
-      <c r="R15" s="24" t="str"/>
-      <c r="S15" s="24" t="str"/>
-      <c r="T15" s="24" t="str"/>
-      <c r="U15" s="24" t="inlineStr">
+      <c r="U15" s="24" t="str"/>
+      <c r="V15" s="24" t="str"/>
+      <c r="W15" s="24" t="str"/>
+      <c r="X15" s="24" t="str"/>
+      <c r="Y15" s="24" t="inlineStr">
         <is>
           <t>0.1.0</t>
         </is>
       </c>
-      <c r="V15" s="24" t="inlineStr">
+      <c r="Z15" s="24" t="inlineStr">
         <is>
           <t>SA内部,案例库,PPT,售前方案</t>
         </is>
       </c>
-      <c r="W15" s="24" t="inlineStr">
+      <c r="AA15" s="24" t="inlineStr">
         <is>
           <t>来源：Dumate场景积累-2026.05.29.pdf。</t>
         </is>
@@ -3970,54 +4804,74 @@
       </c>
       <c r="J16" s="24" t="inlineStr">
         <is>
+          <t>资料检索</t>
+        </is>
+      </c>
+      <c r="K16" s="24" t="inlineStr">
+        <is>
+          <t>独立 Skill</t>
+        </is>
+      </c>
+      <c r="L16" s="24" t="inlineStr">
+        <is>
+          <t>RAG知识检索型</t>
+        </is>
+      </c>
+      <c r="M16" s="24" t="inlineStr">
+        <is>
+          <t>目录规划</t>
+        </is>
+      </c>
+      <c r="N16" s="24" t="inlineStr">
+        <is>
           <t>合同文件夹、关键词组合、筛选规则</t>
         </is>
       </c>
-      <c r="K16" s="24" t="inlineStr">
+      <c r="O16" s="24" t="inlineStr">
         <is>
           <t>命中合同清单、关键词证据、统计结果</t>
         </is>
       </c>
-      <c r="L16" s="24" t="inlineStr">
+      <c r="P16" s="24" t="inlineStr">
         <is>
           <t>规划</t>
         </is>
       </c>
-      <c r="M16" s="24" t="inlineStr">
+      <c r="Q16" s="24" t="inlineStr">
         <is>
           <t>catalog</t>
         </is>
       </c>
-      <c r="N16" s="24" t="inlineStr">
+      <c r="R16" s="24" t="inlineStr">
         <is>
           <t>同事/Dumate场景积累</t>
         </is>
       </c>
-      <c r="O16" s="24" t="inlineStr">
+      <c r="S16" s="24" t="inlineStr">
         <is>
           <t>Dumate/Dodo</t>
         </is>
       </c>
-      <c r="P16" s="24" t="inlineStr">
+      <c r="T16" s="24" t="inlineStr">
         <is>
           <t>如涉及本地文件夹批量读取，需看平台权限；仓库沉淀检索口径和输出模板。</t>
         </is>
       </c>
-      <c r="Q16" s="24" t="str"/>
-      <c r="R16" s="24" t="str"/>
-      <c r="S16" s="24" t="str"/>
-      <c r="T16" s="24" t="str"/>
-      <c r="U16" s="24" t="inlineStr">
+      <c r="U16" s="24" t="str"/>
+      <c r="V16" s="24" t="str"/>
+      <c r="W16" s="24" t="str"/>
+      <c r="X16" s="24" t="str"/>
+      <c r="Y16" s="24" t="inlineStr">
         <is>
           <t>0.1.0</t>
         </is>
       </c>
-      <c r="V16" s="24" t="inlineStr">
+      <c r="Z16" s="24" t="inlineStr">
         <is>
           <t>SA内部,合同检索,关键词,资料整理</t>
         </is>
       </c>
-      <c r="W16" s="24" t="inlineStr">
+      <c r="AA16" s="24" t="inlineStr">
         <is>
           <t>来源：Dumate场景积累-2026.05.29.pdf。</t>
         </is>
@@ -4071,54 +4925,74 @@
       </c>
       <c r="J17" s="24" t="inlineStr">
         <is>
+          <t>风控</t>
+        </is>
+      </c>
+      <c r="K17" s="24" t="inlineStr">
+        <is>
+          <t>主 Skill + L1</t>
+        </is>
+      </c>
+      <c r="L17" s="24" t="inlineStr">
+        <is>
+          <t>混合型</t>
+        </is>
+      </c>
+      <c r="M17" s="24" t="inlineStr">
+        <is>
+          <t>目录规划</t>
+        </is>
+      </c>
+      <c r="N17" s="24" t="inlineStr">
+        <is>
           <t>交易数据、反洗钱规则库、客户信息、审批口径</t>
         </is>
       </c>
-      <c r="K17" s="24" t="inlineStr">
+      <c r="O17" s="24" t="inlineStr">
         <is>
           <t>结构化反洗钱报告、风险盲区、新规则提案、审批卡片</t>
         </is>
       </c>
-      <c r="L17" s="24" t="inlineStr">
+      <c r="P17" s="24" t="inlineStr">
         <is>
           <t>规划</t>
         </is>
       </c>
-      <c r="M17" s="24" t="inlineStr">
+      <c r="Q17" s="24" t="inlineStr">
         <is>
           <t>catalog</t>
         </is>
       </c>
-      <c r="N17" s="24" t="inlineStr">
+      <c r="R17" s="24" t="inlineStr">
         <is>
           <t>同事/Dumate场景积累</t>
         </is>
       </c>
-      <c r="O17" s="24" t="inlineStr">
+      <c r="S17" s="24" t="inlineStr">
         <is>
           <t>Dumate/Dodo</t>
         </is>
       </c>
-      <c r="P17" s="24" t="inlineStr">
+      <c r="T17" s="24" t="inlineStr">
         <is>
           <t>可纳入客户金融场景重点候选；真实演示需模拟交易数据和规则库。</t>
         </is>
       </c>
-      <c r="Q17" s="24" t="str"/>
-      <c r="R17" s="24" t="str"/>
-      <c r="S17" s="24" t="str"/>
-      <c r="T17" s="24" t="str"/>
-      <c r="U17" s="24" t="inlineStr">
+      <c r="U17" s="24" t="str"/>
+      <c r="V17" s="24" t="str"/>
+      <c r="W17" s="24" t="str"/>
+      <c r="X17" s="24" t="str"/>
+      <c r="Y17" s="24" t="inlineStr">
         <is>
           <t>0.1.0</t>
         </is>
       </c>
-      <c r="V17" s="24" t="inlineStr">
+      <c r="Z17" s="24" t="inlineStr">
         <is>
           <t>反洗钱,交易所,规则进化,审批</t>
         </is>
       </c>
-      <c r="W17" s="24" t="inlineStr">
+      <c r="AA17" s="24" t="inlineStr">
         <is>
           <t>来源：Dumate场景积累-2026.05.29.pdf。</t>
         </is>
@@ -4172,54 +5046,74 @@
       </c>
       <c r="J18" s="24" t="inlineStr">
         <is>
+          <t>合规</t>
+        </is>
+      </c>
+      <c r="K18" s="24" t="inlineStr">
+        <is>
+          <t>独立 Skill</t>
+        </is>
+      </c>
+      <c r="L18" s="24" t="inlineStr">
+        <is>
+          <t>规则型</t>
+        </is>
+      </c>
+      <c r="M18" s="24" t="inlineStr">
+        <is>
+          <t>目录规划</t>
+        </is>
+      </c>
+      <c r="N18" s="24" t="inlineStr">
+        <is>
           <t>保险产品材料、营销文案、监管规则、审核口径</t>
         </is>
       </c>
-      <c r="K18" s="24" t="inlineStr">
+      <c r="O18" s="24" t="inlineStr">
         <is>
           <t>合规风险点、修改建议、审核结论草稿</t>
         </is>
       </c>
-      <c r="L18" s="24" t="inlineStr">
+      <c r="P18" s="24" t="inlineStr">
         <is>
           <t>规划</t>
         </is>
       </c>
-      <c r="M18" s="24" t="inlineStr">
+      <c r="Q18" s="24" t="inlineStr">
         <is>
           <t>catalog</t>
         </is>
       </c>
-      <c r="N18" s="24" t="inlineStr">
+      <c r="R18" s="24" t="inlineStr">
         <is>
           <t>同事/Dumate场景积累</t>
         </is>
       </c>
-      <c r="O18" s="24" t="inlineStr">
+      <c r="S18" s="24" t="inlineStr">
         <is>
           <t>Dumate</t>
         </is>
       </c>
-      <c r="P18" s="24" t="inlineStr">
+      <c r="T18" s="24" t="inlineStr">
         <is>
           <t>适合迁移到客户金融场景库；需补规则来源和不可替代人工审核边界。</t>
         </is>
       </c>
-      <c r="Q18" s="24" t="str"/>
-      <c r="R18" s="24" t="str"/>
-      <c r="S18" s="24" t="str"/>
-      <c r="T18" s="24" t="str"/>
-      <c r="U18" s="24" t="inlineStr">
+      <c r="U18" s="24" t="str"/>
+      <c r="V18" s="24" t="str"/>
+      <c r="W18" s="24" t="str"/>
+      <c r="X18" s="24" t="str"/>
+      <c r="Y18" s="24" t="inlineStr">
         <is>
           <t>0.1.0</t>
         </is>
       </c>
-      <c r="V18" s="24" t="inlineStr">
+      <c r="Z18" s="24" t="inlineStr">
         <is>
           <t>保险,营销合规,内容审核</t>
         </is>
       </c>
-      <c r="W18" s="24" t="inlineStr">
+      <c r="AA18" s="24" t="inlineStr">
         <is>
           <t>来源：Dumate场景积累-2026.05.29.pdf。</t>
         </is>
@@ -4273,54 +5167,74 @@
       </c>
       <c r="J19" s="24" t="inlineStr">
         <is>
+          <t>风控</t>
+        </is>
+      </c>
+      <c r="K19" s="24" t="inlineStr">
+        <is>
+          <t>主 Skill + L1</t>
+        </is>
+      </c>
+      <c r="L19" s="24" t="inlineStr">
+        <is>
+          <t>数据分析型</t>
+        </is>
+      </c>
+      <c r="M19" s="24" t="inlineStr">
+        <is>
+          <t>目录规划</t>
+        </is>
+      </c>
+      <c r="N19" s="24" t="inlineStr">
+        <is>
           <t>车辆数据、保单数据、理赔数据、外部风险信息</t>
         </is>
       </c>
-      <c r="K19" s="24" t="inlineStr">
+      <c r="O19" s="24" t="inlineStr">
         <is>
           <t>数据清单、风险特征、定价/核保/理赔分析输入</t>
         </is>
       </c>
-      <c r="L19" s="24" t="inlineStr">
+      <c r="P19" s="24" t="inlineStr">
         <is>
           <t>规划</t>
         </is>
       </c>
-      <c r="M19" s="24" t="inlineStr">
+      <c r="Q19" s="24" t="inlineStr">
         <is>
           <t>catalog</t>
         </is>
       </c>
-      <c r="N19" s="24" t="inlineStr">
+      <c r="R19" s="24" t="inlineStr">
         <is>
           <t>同事/Dumate场景积累</t>
         </is>
       </c>
-      <c r="O19" s="24" t="inlineStr">
+      <c r="S19" s="24" t="inlineStr">
         <is>
           <t>Dumate/Dodo</t>
         </is>
       </c>
-      <c r="P19" s="24" t="inlineStr">
+      <c r="T19" s="24" t="inlineStr">
         <is>
           <t>更偏数据工程与业务建模；仓库先登记场景，后续拆解可演示子任务。</t>
         </is>
       </c>
-      <c r="Q19" s="24" t="str"/>
-      <c r="R19" s="24" t="str"/>
-      <c r="S19" s="24" t="str"/>
-      <c r="T19" s="24" t="str"/>
-      <c r="U19" s="24" t="inlineStr">
+      <c r="U19" s="24" t="str"/>
+      <c r="V19" s="24" t="str"/>
+      <c r="W19" s="24" t="str"/>
+      <c r="X19" s="24" t="str"/>
+      <c r="Y19" s="24" t="inlineStr">
         <is>
           <t>0.1.0</t>
         </is>
       </c>
-      <c r="V19" s="24" t="inlineStr">
+      <c r="Z19" s="24" t="inlineStr">
         <is>
           <t>保险,车险,新能源车,核保,反欺诈</t>
         </is>
       </c>
-      <c r="W19" s="24" t="inlineStr">
+      <c r="AA19" s="24" t="inlineStr">
         <is>
           <t>来源：Dumate场景积累-2026.05.29.pdf。</t>
         </is>
@@ -4374,83 +5288,211 @@
       </c>
       <c r="J20" s="24" t="inlineStr">
         <is>
+          <t>风控</t>
+        </is>
+      </c>
+      <c r="K20" s="24" t="inlineStr">
+        <is>
+          <t>主 Skill + L1</t>
+        </is>
+      </c>
+      <c r="L20" s="24" t="inlineStr">
+        <is>
+          <t>混合型</t>
+        </is>
+      </c>
+      <c r="M20" s="24" t="inlineStr">
+        <is>
+          <t>目录规划</t>
+        </is>
+      </c>
+      <c r="N20" s="24" t="inlineStr">
+        <is>
           <t>已有风控规则、风险报告、合成测试数据</t>
         </is>
       </c>
-      <c r="K20" s="24" t="inlineStr">
+      <c r="O20" s="24" t="inlineStr">
         <is>
           <t>规则总结、新规则候选、适用条件、验证建议</t>
         </is>
       </c>
-      <c r="L20" s="24" t="inlineStr">
+      <c r="P20" s="24" t="inlineStr">
         <is>
           <t>规划</t>
         </is>
       </c>
-      <c r="M20" s="24" t="inlineStr">
+      <c r="Q20" s="24" t="inlineStr">
         <is>
           <t>catalog</t>
         </is>
       </c>
-      <c r="N20" s="24" t="inlineStr">
+      <c r="R20" s="24" t="inlineStr">
         <is>
           <t>同事/Dumate场景积累</t>
         </is>
       </c>
-      <c r="O20" s="24" t="inlineStr">
+      <c r="S20" s="24" t="inlineStr">
         <is>
           <t>Dumate/Dodo</t>
         </is>
       </c>
-      <c r="P20" s="24" t="inlineStr">
+      <c r="T20" s="24" t="inlineStr">
         <is>
           <t>适合做保险风控方向候选；需补合成数据和规则验证流程。</t>
         </is>
       </c>
-      <c r="Q20" s="24" t="str"/>
-      <c r="R20" s="24" t="str"/>
-      <c r="S20" s="24" t="str"/>
-      <c r="T20" s="24" t="str"/>
-      <c r="U20" s="24" t="inlineStr">
+      <c r="U20" s="24" t="str"/>
+      <c r="V20" s="24" t="str"/>
+      <c r="W20" s="24" t="str"/>
+      <c r="X20" s="24" t="str"/>
+      <c r="Y20" s="24" t="inlineStr">
         <is>
           <t>0.1.0</t>
         </is>
       </c>
-      <c r="V20" s="24" t="inlineStr">
+      <c r="Z20" s="24" t="inlineStr">
         <is>
           <t>保险,车险风控,规则挖掘,风险报告</t>
         </is>
       </c>
-      <c r="W20" s="24" t="inlineStr">
+      <c r="AA20" s="24" t="inlineStr">
         <is>
           <t>来源：Dumate场景积累-2026.05.29.pdf。</t>
         </is>
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="24" t="n"/>
-      <c r="B21" s="24" t="n"/>
-      <c r="C21" s="24" t="n"/>
-      <c r="D21" s="24" t="n"/>
-      <c r="E21" s="24" t="n"/>
-      <c r="F21" s="24" t="n"/>
-      <c r="G21" s="24" t="n"/>
-      <c r="H21" s="24" t="n"/>
-      <c r="I21" s="24" t="n"/>
-      <c r="J21" s="24" t="n"/>
-      <c r="K21" s="24" t="n"/>
-      <c r="L21" s="24" t="n"/>
-      <c r="M21" s="24" t="n"/>
-      <c r="N21" s="24" t="n"/>
-      <c r="O21" s="24" t="n"/>
-      <c r="P21" s="24" t="n"/>
-      <c r="Q21" s="24" t="n"/>
-      <c r="R21" s="24" t="n"/>
-      <c r="S21" s="24" t="n"/>
-      <c r="T21" s="24" t="n"/>
-      <c r="U21" s="24" t="n"/>
-      <c r="V21" s="24" t="n"/>
-      <c r="W21" s="24" t="n"/>
+      <c r="A21" s="24" t="inlineStr">
+        <is>
+          <t>eop-scene-daily-report-analyse</t>
+        </is>
+      </c>
+      <c r="B21" s="24" t="inlineStr">
+        <is>
+          <t>团队日报汇总分析</t>
+        </is>
+      </c>
+      <c r="C21" s="24" t="inlineStr">
+        <is>
+          <t>SA-AI内化场景</t>
+        </is>
+      </c>
+      <c r="D21" s="24" t="inlineStr">
+        <is>
+          <t>SA内部</t>
+        </is>
+      </c>
+      <c r="E21" s="24" t="inlineStr">
+        <is>
+          <t>内部管理</t>
+        </is>
+      </c>
+      <c r="F21" s="24" t="inlineStr">
+        <is>
+          <t>团队管理</t>
+        </is>
+      </c>
+      <c r="G21" s="24" t="inlineStr">
+        <is>
+          <t>日报/周报复盘</t>
+        </is>
+      </c>
+      <c r="H21" s="24" t="inlineStr">
+        <is>
+          <t>为团队 leader 汇总分析团队成员日报，提炼重点项目进展、日报变化、一周总结及团队风险提醒。</t>
+        </is>
+      </c>
+      <c r="I21" s="24" t="inlineStr">
+        <is>
+          <t>LLM+业务数据汇总型 Skill</t>
+        </is>
+      </c>
+      <c r="J21" s="24" t="inlineStr">
+        <is>
+          <t>团队管理</t>
+        </is>
+      </c>
+      <c r="K21" s="24" t="inlineStr">
+        <is>
+          <t>独立 Skill</t>
+        </is>
+      </c>
+      <c r="L21" s="24" t="inlineStr">
+        <is>
+          <t>工具调用型</t>
+        </is>
+      </c>
+      <c r="M21" s="24" t="inlineStr">
+        <is>
+          <t>真实Skill包+Demo</t>
+        </is>
+      </c>
+      <c r="N21" s="24" t="inlineStr">
+        <is>
+          <t>用户自然语言指令、时间范围、成员姓名/UUAP、sales_daily_report_list 返回的团队日报数据</t>
+        </is>
+      </c>
+      <c r="O21" s="24" t="inlineStr">
+        <is>
+          <t>团队日报分析报告、重点项目提炼、日报变化分析、成员周报总结、团队整体风险提醒</t>
+        </is>
+      </c>
+      <c r="P21" s="24" t="inlineStr">
+        <is>
+          <t>已开发</t>
+        </is>
+      </c>
+      <c r="Q21" s="24" t="inlineStr">
+        <is>
+          <t>demo</t>
+        </is>
+      </c>
+      <c r="R21" s="24" t="inlineStr">
+        <is>
+          <t>同事/eop-scene-daily-report-analyse Skill包</t>
+        </is>
+      </c>
+      <c r="S21" s="24" t="inlineStr">
+        <is>
+          <t>Dodo/EOP</t>
+        </is>
+      </c>
+      <c r="T21" s="24" t="inlineStr">
+        <is>
+          <t>已接入真实 Skill 包与页面 Demo；正式运行依赖 eop-core-auth-check 和 sales_daily_report_list，演示页使用脱敏样例呈现链路。</t>
+        </is>
+      </c>
+      <c r="U21" s="24" t="inlineStr">
+        <is>
+          <t>presales-skill-matrix/eop-scene-daily-report-analyse/SKILL.md</t>
+        </is>
+      </c>
+      <c r="V21" s="24" t="inlineStr">
+        <is>
+          <t>presales-skill-matrix/eop-scene-daily-report-analyse/eop-scene-daily-report-analyse-demo.html</t>
+        </is>
+      </c>
+      <c r="W21" s="24" t="inlineStr">
+        <is>
+          <t>presales-skill-matrix/eop-scene-daily-report-analyse/references/output_template.md</t>
+        </is>
+      </c>
+      <c r="X21" s="24" t="inlineStr"/>
+      <c r="Y21" s="24" t="inlineStr">
+        <is>
+          <t>1.0.0</t>
+        </is>
+      </c>
+      <c r="Z21" s="24" t="inlineStr">
+        <is>
+          <t>SA内部,团队日报,日报分析,周报总结,项目进展,风险提醒,已开发Skill</t>
+        </is>
+      </c>
+      <c r="AA21" s="24" t="inlineStr">
+        <is>
+          <t>2026-06-19 接入同事提供的 eop-scene-daily-report-analyse 真实 Skill 包；正式运行依赖 EOP/Dodo 工具调用，Demo 使用脱敏样例，不替代真实 EOP 工具查询。</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" s="24" t="n"/>
@@ -4476,6 +5518,10 @@
       <c r="U22" s="24" t="n"/>
       <c r="V22" s="24" t="n"/>
       <c r="W22" s="24" t="n"/>
+      <c r="X22" s="24" t="n"/>
+      <c r="Y22" s="24" t="n"/>
+      <c r="Z22" s="24" t="n"/>
+      <c r="AA22" s="24" t="n"/>
     </row>
     <row r="23">
       <c r="A23" s="24" t="n"/>
@@ -4501,6 +5547,10 @@
       <c r="U23" s="24" t="n"/>
       <c r="V23" s="24" t="n"/>
       <c r="W23" s="24" t="n"/>
+      <c r="X23" s="24" t="n"/>
+      <c r="Y23" s="24" t="n"/>
+      <c r="Z23" s="24" t="n"/>
+      <c r="AA23" s="24" t="n"/>
     </row>
     <row r="24">
       <c r="A24" s="24" t="n"/>
@@ -4526,6 +5576,10 @@
       <c r="U24" s="24" t="n"/>
       <c r="V24" s="24" t="n"/>
       <c r="W24" s="24" t="n"/>
+      <c r="X24" s="24" t="n"/>
+      <c r="Y24" s="24" t="n"/>
+      <c r="Z24" s="24" t="n"/>
+      <c r="AA24" s="24" t="n"/>
     </row>
     <row r="25">
       <c r="A25" s="24" t="n"/>
@@ -4551,6 +5605,10 @@
       <c r="U25" s="24" t="n"/>
       <c r="V25" s="24" t="n"/>
       <c r="W25" s="24" t="n"/>
+      <c r="X25" s="24" t="n"/>
+      <c r="Y25" s="24" t="n"/>
+      <c r="Z25" s="24" t="n"/>
+      <c r="AA25" s="24" t="n"/>
     </row>
     <row r="26">
       <c r="A26" s="24" t="n"/>
@@ -4576,6 +5634,10 @@
       <c r="U26" s="24" t="n"/>
       <c r="V26" s="24" t="n"/>
       <c r="W26" s="24" t="n"/>
+      <c r="X26" s="24" t="n"/>
+      <c r="Y26" s="24" t="n"/>
+      <c r="Z26" s="24" t="n"/>
+      <c r="AA26" s="24" t="n"/>
     </row>
     <row r="27">
       <c r="A27" s="24" t="n"/>
@@ -4601,6 +5663,10 @@
       <c r="U27" s="24" t="n"/>
       <c r="V27" s="24" t="n"/>
       <c r="W27" s="24" t="n"/>
+      <c r="X27" s="24" t="n"/>
+      <c r="Y27" s="24" t="n"/>
+      <c r="Z27" s="24" t="n"/>
+      <c r="AA27" s="24" t="n"/>
     </row>
     <row r="28">
       <c r="A28" s="24" t="n"/>
@@ -4626,6 +5692,10 @@
       <c r="U28" s="24" t="n"/>
       <c r="V28" s="24" t="n"/>
       <c r="W28" s="24" t="n"/>
+      <c r="X28" s="24" t="n"/>
+      <c r="Y28" s="24" t="n"/>
+      <c r="Z28" s="24" t="n"/>
+      <c r="AA28" s="24" t="n"/>
     </row>
     <row r="29">
       <c r="A29" s="24" t="n"/>
@@ -4651,6 +5721,10 @@
       <c r="U29" s="24" t="n"/>
       <c r="V29" s="24" t="n"/>
       <c r="W29" s="24" t="n"/>
+      <c r="X29" s="24" t="n"/>
+      <c r="Y29" s="24" t="n"/>
+      <c r="Z29" s="24" t="n"/>
+      <c r="AA29" s="24" t="n"/>
     </row>
     <row r="30">
       <c r="A30" s="24" t="n"/>
@@ -4676,6 +5750,10 @@
       <c r="U30" s="24" t="n"/>
       <c r="V30" s="24" t="n"/>
       <c r="W30" s="24" t="n"/>
+      <c r="X30" s="24" t="n"/>
+      <c r="Y30" s="24" t="n"/>
+      <c r="Z30" s="24" t="n"/>
+      <c r="AA30" s="24" t="n"/>
     </row>
     <row r="31">
       <c r="A31" s="24" t="n"/>
@@ -4701,6 +5779,10 @@
       <c r="U31" s="24" t="n"/>
       <c r="V31" s="24" t="n"/>
       <c r="W31" s="24" t="n"/>
+      <c r="X31" s="24" t="n"/>
+      <c r="Y31" s="24" t="n"/>
+      <c r="Z31" s="24" t="n"/>
+      <c r="AA31" s="24" t="n"/>
     </row>
     <row r="32">
       <c r="A32" s="24" t="n"/>
@@ -4726,6 +5808,10 @@
       <c r="U32" s="24" t="n"/>
       <c r="V32" s="24" t="n"/>
       <c r="W32" s="24" t="n"/>
+      <c r="X32" s="24" t="n"/>
+      <c r="Y32" s="24" t="n"/>
+      <c r="Z32" s="24" t="n"/>
+      <c r="AA32" s="24" t="n"/>
     </row>
     <row r="33">
       <c r="A33" s="24" t="n"/>
@@ -4751,6 +5837,10 @@
       <c r="U33" s="24" t="n"/>
       <c r="V33" s="24" t="n"/>
       <c r="W33" s="24" t="n"/>
+      <c r="X33" s="24" t="n"/>
+      <c r="Y33" s="24" t="n"/>
+      <c r="Z33" s="24" t="n"/>
+      <c r="AA33" s="24" t="n"/>
     </row>
     <row r="34">
       <c r="A34" s="24" t="n"/>
@@ -4776,6 +5866,10 @@
       <c r="U34" s="24" t="n"/>
       <c r="V34" s="24" t="n"/>
       <c r="W34" s="24" t="n"/>
+      <c r="X34" s="24" t="n"/>
+      <c r="Y34" s="24" t="n"/>
+      <c r="Z34" s="24" t="n"/>
+      <c r="AA34" s="24" t="n"/>
     </row>
     <row r="35">
       <c r="A35" s="24" t="n"/>
@@ -4801,6 +5895,10 @@
       <c r="U35" s="24" t="n"/>
       <c r="V35" s="24" t="n"/>
       <c r="W35" s="24" t="n"/>
+      <c r="X35" s="24" t="n"/>
+      <c r="Y35" s="24" t="n"/>
+      <c r="Z35" s="24" t="n"/>
+      <c r="AA35" s="24" t="n"/>
     </row>
     <row r="36">
       <c r="A36" s="24" t="n"/>
@@ -4826,6 +5924,10 @@
       <c r="U36" s="24" t="n"/>
       <c r="V36" s="24" t="n"/>
       <c r="W36" s="24" t="n"/>
+      <c r="X36" s="24" t="n"/>
+      <c r="Y36" s="24" t="n"/>
+      <c r="Z36" s="24" t="n"/>
+      <c r="AA36" s="24" t="n"/>
     </row>
     <row r="37">
       <c r="A37" s="24" t="n"/>
@@ -4851,6 +5953,10 @@
       <c r="U37" s="24" t="n"/>
       <c r="V37" s="24" t="n"/>
       <c r="W37" s="24" t="n"/>
+      <c r="X37" s="24" t="n"/>
+      <c r="Y37" s="24" t="n"/>
+      <c r="Z37" s="24" t="n"/>
+      <c r="AA37" s="24" t="n"/>
     </row>
     <row r="38">
       <c r="A38" s="24" t="n"/>
@@ -4876,6 +5982,10 @@
       <c r="U38" s="24" t="n"/>
       <c r="V38" s="24" t="n"/>
       <c r="W38" s="24" t="n"/>
+      <c r="X38" s="24" t="n"/>
+      <c r="Y38" s="24" t="n"/>
+      <c r="Z38" s="24" t="n"/>
+      <c r="AA38" s="24" t="n"/>
     </row>
     <row r="39">
       <c r="A39" s="24" t="n"/>
@@ -4901,6 +6011,10 @@
       <c r="U39" s="24" t="n"/>
       <c r="V39" s="24" t="n"/>
       <c r="W39" s="24" t="n"/>
+      <c r="X39" s="24" t="n"/>
+      <c r="Y39" s="24" t="n"/>
+      <c r="Z39" s="24" t="n"/>
+      <c r="AA39" s="24" t="n"/>
     </row>
     <row r="40">
       <c r="A40" s="24" t="n"/>
@@ -4926,6 +6040,10 @@
       <c r="U40" s="24" t="n"/>
       <c r="V40" s="24" t="n"/>
       <c r="W40" s="24" t="n"/>
+      <c r="X40" s="24" t="n"/>
+      <c r="Y40" s="24" t="n"/>
+      <c r="Z40" s="24" t="n"/>
+      <c r="AA40" s="24" t="n"/>
     </row>
     <row r="41">
       <c r="A41" s="24" t="n"/>
@@ -4951,6 +6069,10 @@
       <c r="U41" s="24" t="n"/>
       <c r="V41" s="24" t="n"/>
       <c r="W41" s="24" t="n"/>
+      <c r="X41" s="24" t="n"/>
+      <c r="Y41" s="24" t="n"/>
+      <c r="Z41" s="24" t="n"/>
+      <c r="AA41" s="24" t="n"/>
     </row>
     <row r="42">
       <c r="A42" s="24" t="n"/>
@@ -4976,6 +6098,10 @@
       <c r="U42" s="24" t="n"/>
       <c r="V42" s="24" t="n"/>
       <c r="W42" s="24" t="n"/>
+      <c r="X42" s="24" t="n"/>
+      <c r="Y42" s="24" t="n"/>
+      <c r="Z42" s="24" t="n"/>
+      <c r="AA42" s="24" t="n"/>
     </row>
     <row r="43">
       <c r="A43" s="24" t="n"/>
@@ -5001,6 +6127,10 @@
       <c r="U43" s="24" t="n"/>
       <c r="V43" s="24" t="n"/>
       <c r="W43" s="24" t="n"/>
+      <c r="X43" s="24" t="n"/>
+      <c r="Y43" s="24" t="n"/>
+      <c r="Z43" s="24" t="n"/>
+      <c r="AA43" s="24" t="n"/>
     </row>
     <row r="44">
       <c r="A44" s="24" t="n"/>
@@ -5026,6 +6156,10 @@
       <c r="U44" s="24" t="n"/>
       <c r="V44" s="24" t="n"/>
       <c r="W44" s="24" t="n"/>
+      <c r="X44" s="24" t="n"/>
+      <c r="Y44" s="24" t="n"/>
+      <c r="Z44" s="24" t="n"/>
+      <c r="AA44" s="24" t="n"/>
     </row>
     <row r="45">
       <c r="A45" s="24" t="n"/>
@@ -5051,6 +6185,10 @@
       <c r="U45" s="24" t="n"/>
       <c r="V45" s="24" t="n"/>
       <c r="W45" s="24" t="n"/>
+      <c r="X45" s="24" t="n"/>
+      <c r="Y45" s="24" t="n"/>
+      <c r="Z45" s="24" t="n"/>
+      <c r="AA45" s="24" t="n"/>
     </row>
     <row r="46">
       <c r="A46" s="24" t="n"/>
@@ -5076,6 +6214,10 @@
       <c r="U46" s="24" t="n"/>
       <c r="V46" s="24" t="n"/>
       <c r="W46" s="24" t="n"/>
+      <c r="X46" s="24" t="n"/>
+      <c r="Y46" s="24" t="n"/>
+      <c r="Z46" s="24" t="n"/>
+      <c r="AA46" s="24" t="n"/>
     </row>
     <row r="47">
       <c r="A47" s="24" t="n"/>
@@ -5101,6 +6243,10 @@
       <c r="U47" s="24" t="n"/>
       <c r="V47" s="24" t="n"/>
       <c r="W47" s="24" t="n"/>
+      <c r="X47" s="24" t="n"/>
+      <c r="Y47" s="24" t="n"/>
+      <c r="Z47" s="24" t="n"/>
+      <c r="AA47" s="24" t="n"/>
     </row>
     <row r="48">
       <c r="A48" s="24" t="n"/>
@@ -5126,6 +6272,10 @@
       <c r="U48" s="24" t="n"/>
       <c r="V48" s="24" t="n"/>
       <c r="W48" s="24" t="n"/>
+      <c r="X48" s="24" t="n"/>
+      <c r="Y48" s="24" t="n"/>
+      <c r="Z48" s="24" t="n"/>
+      <c r="AA48" s="24" t="n"/>
     </row>
     <row r="49">
       <c r="A49" s="24" t="n"/>
@@ -5151,6 +6301,10 @@
       <c r="U49" s="24" t="n"/>
       <c r="V49" s="24" t="n"/>
       <c r="W49" s="24" t="n"/>
+      <c r="X49" s="24" t="n"/>
+      <c r="Y49" s="24" t="n"/>
+      <c r="Z49" s="24" t="n"/>
+      <c r="AA49" s="24" t="n"/>
     </row>
     <row r="50">
       <c r="A50" s="24" t="n"/>
@@ -5176,6 +6330,10 @@
       <c r="U50" s="24" t="n"/>
       <c r="V50" s="24" t="n"/>
       <c r="W50" s="24" t="n"/>
+      <c r="X50" s="24" t="n"/>
+      <c r="Y50" s="24" t="n"/>
+      <c r="Z50" s="24" t="n"/>
+      <c r="AA50" s="24" t="n"/>
     </row>
     <row r="51">
       <c r="A51" s="24" t="n"/>
@@ -5201,6 +6359,10 @@
       <c r="U51" s="24" t="n"/>
       <c r="V51" s="24" t="n"/>
       <c r="W51" s="24" t="n"/>
+      <c r="X51" s="24" t="n"/>
+      <c r="Y51" s="24" t="n"/>
+      <c r="Z51" s="24" t="n"/>
+      <c r="AA51" s="24" t="n"/>
     </row>
     <row r="52">
       <c r="A52" s="24" t="n"/>
@@ -5226,6 +6388,10 @@
       <c r="U52" s="24" t="n"/>
       <c r="V52" s="24" t="n"/>
       <c r="W52" s="24" t="n"/>
+      <c r="X52" s="24" t="n"/>
+      <c r="Y52" s="24" t="n"/>
+      <c r="Z52" s="24" t="n"/>
+      <c r="AA52" s="24" t="n"/>
     </row>
     <row r="53">
       <c r="A53" s="24" t="n"/>
@@ -5251,6 +6417,10 @@
       <c r="U53" s="24" t="n"/>
       <c r="V53" s="24" t="n"/>
       <c r="W53" s="24" t="n"/>
+      <c r="X53" s="24" t="n"/>
+      <c r="Y53" s="24" t="n"/>
+      <c r="Z53" s="24" t="n"/>
+      <c r="AA53" s="24" t="n"/>
     </row>
     <row r="54">
       <c r="A54" s="24" t="n"/>
@@ -5276,6 +6446,10 @@
       <c r="U54" s="24" t="n"/>
       <c r="V54" s="24" t="n"/>
       <c r="W54" s="24" t="n"/>
+      <c r="X54" s="24" t="n"/>
+      <c r="Y54" s="24" t="n"/>
+      <c r="Z54" s="24" t="n"/>
+      <c r="AA54" s="24" t="n"/>
     </row>
     <row r="55">
       <c r="A55" s="24" t="n"/>
@@ -5301,6 +6475,10 @@
       <c r="U55" s="24" t="n"/>
       <c r="V55" s="24" t="n"/>
       <c r="W55" s="24" t="n"/>
+      <c r="X55" s="24" t="n"/>
+      <c r="Y55" s="24" t="n"/>
+      <c r="Z55" s="24" t="n"/>
+      <c r="AA55" s="24" t="n"/>
     </row>
     <row r="56">
       <c r="A56" s="24" t="n"/>
@@ -5326,6 +6504,10 @@
       <c r="U56" s="24" t="n"/>
       <c r="V56" s="24" t="n"/>
       <c r="W56" s="24" t="n"/>
+      <c r="X56" s="24" t="n"/>
+      <c r="Y56" s="24" t="n"/>
+      <c r="Z56" s="24" t="n"/>
+      <c r="AA56" s="24" t="n"/>
     </row>
     <row r="57">
       <c r="A57" s="24" t="n"/>
@@ -5351,6 +6533,10 @@
       <c r="U57" s="24" t="n"/>
       <c r="V57" s="24" t="n"/>
       <c r="W57" s="24" t="n"/>
+      <c r="X57" s="24" t="n"/>
+      <c r="Y57" s="24" t="n"/>
+      <c r="Z57" s="24" t="n"/>
+      <c r="AA57" s="24" t="n"/>
     </row>
     <row r="58">
       <c r="A58" s="24" t="n"/>
@@ -5376,6 +6562,10 @@
       <c r="U58" s="24" t="n"/>
       <c r="V58" s="24" t="n"/>
       <c r="W58" s="24" t="n"/>
+      <c r="X58" s="24" t="n"/>
+      <c r="Y58" s="24" t="n"/>
+      <c r="Z58" s="24" t="n"/>
+      <c r="AA58" s="24" t="n"/>
     </row>
     <row r="59">
       <c r="A59" s="24" t="n"/>
@@ -5401,6 +6591,10 @@
       <c r="U59" s="24" t="n"/>
       <c r="V59" s="24" t="n"/>
       <c r="W59" s="24" t="n"/>
+      <c r="X59" s="24" t="n"/>
+      <c r="Y59" s="24" t="n"/>
+      <c r="Z59" s="24" t="n"/>
+      <c r="AA59" s="24" t="n"/>
     </row>
     <row r="60">
       <c r="A60" s="24" t="n"/>
@@ -5426,6 +6620,10 @@
       <c r="U60" s="24" t="n"/>
       <c r="V60" s="24" t="n"/>
       <c r="W60" s="24" t="n"/>
+      <c r="X60" s="24" t="n"/>
+      <c r="Y60" s="24" t="n"/>
+      <c r="Z60" s="24" t="n"/>
+      <c r="AA60" s="24" t="n"/>
     </row>
     <row r="61">
       <c r="A61" s="24" t="n"/>
@@ -5451,6 +6649,10 @@
       <c r="U61" s="24" t="n"/>
       <c r="V61" s="24" t="n"/>
       <c r="W61" s="24" t="n"/>
+      <c r="X61" s="24" t="n"/>
+      <c r="Y61" s="24" t="n"/>
+      <c r="Z61" s="24" t="n"/>
+      <c r="AA61" s="24" t="n"/>
     </row>
     <row r="62">
       <c r="A62" s="24" t="n"/>
@@ -5476,6 +6678,10 @@
       <c r="U62" s="24" t="n"/>
       <c r="V62" s="24" t="n"/>
       <c r="W62" s="24" t="n"/>
+      <c r="X62" s="24" t="n"/>
+      <c r="Y62" s="24" t="n"/>
+      <c r="Z62" s="24" t="n"/>
+      <c r="AA62" s="24" t="n"/>
     </row>
     <row r="63">
       <c r="A63" s="24" t="n"/>
@@ -5501,6 +6707,10 @@
       <c r="U63" s="24" t="n"/>
       <c r="V63" s="24" t="n"/>
       <c r="W63" s="24" t="n"/>
+      <c r="X63" s="24" t="n"/>
+      <c r="Y63" s="24" t="n"/>
+      <c r="Z63" s="24" t="n"/>
+      <c r="AA63" s="24" t="n"/>
     </row>
     <row r="64">
       <c r="A64" s="24" t="n"/>
@@ -5526,6 +6736,10 @@
       <c r="U64" s="24" t="n"/>
       <c r="V64" s="24" t="n"/>
       <c r="W64" s="24" t="n"/>
+      <c r="X64" s="24" t="n"/>
+      <c r="Y64" s="24" t="n"/>
+      <c r="Z64" s="24" t="n"/>
+      <c r="AA64" s="24" t="n"/>
     </row>
     <row r="65">
       <c r="A65" s="24" t="n"/>
@@ -5551,6 +6765,10 @@
       <c r="U65" s="24" t="n"/>
       <c r="V65" s="24" t="n"/>
       <c r="W65" s="24" t="n"/>
+      <c r="X65" s="24" t="n"/>
+      <c r="Y65" s="24" t="n"/>
+      <c r="Z65" s="24" t="n"/>
+      <c r="AA65" s="24" t="n"/>
     </row>
     <row r="66">
       <c r="A66" s="24" t="n"/>
@@ -5576,6 +6794,10 @@
       <c r="U66" s="24" t="n"/>
       <c r="V66" s="24" t="n"/>
       <c r="W66" s="24" t="n"/>
+      <c r="X66" s="24" t="n"/>
+      <c r="Y66" s="24" t="n"/>
+      <c r="Z66" s="24" t="n"/>
+      <c r="AA66" s="24" t="n"/>
     </row>
     <row r="67">
       <c r="A67" s="24" t="n"/>
@@ -5601,6 +6823,10 @@
       <c r="U67" s="24" t="n"/>
       <c r="V67" s="24" t="n"/>
       <c r="W67" s="24" t="n"/>
+      <c r="X67" s="24" t="n"/>
+      <c r="Y67" s="24" t="n"/>
+      <c r="Z67" s="24" t="n"/>
+      <c r="AA67" s="24" t="n"/>
     </row>
     <row r="68">
       <c r="A68" s="24" t="n"/>
@@ -5626,6 +6852,10 @@
       <c r="U68" s="24" t="n"/>
       <c r="V68" s="24" t="n"/>
       <c r="W68" s="24" t="n"/>
+      <c r="X68" s="24" t="n"/>
+      <c r="Y68" s="24" t="n"/>
+      <c r="Z68" s="24" t="n"/>
+      <c r="AA68" s="24" t="n"/>
     </row>
     <row r="69">
       <c r="A69" s="24" t="n"/>
@@ -5651,6 +6881,10 @@
       <c r="U69" s="24" t="n"/>
       <c r="V69" s="24" t="n"/>
       <c r="W69" s="24" t="n"/>
+      <c r="X69" s="24" t="n"/>
+      <c r="Y69" s="24" t="n"/>
+      <c r="Z69" s="24" t="n"/>
+      <c r="AA69" s="24" t="n"/>
     </row>
     <row r="70">
       <c r="A70" s="24" t="n"/>
@@ -5676,6 +6910,10 @@
       <c r="U70" s="24" t="n"/>
       <c r="V70" s="24" t="n"/>
       <c r="W70" s="24" t="n"/>
+      <c r="X70" s="24" t="n"/>
+      <c r="Y70" s="24" t="n"/>
+      <c r="Z70" s="24" t="n"/>
+      <c r="AA70" s="24" t="n"/>
     </row>
     <row r="71">
       <c r="A71" s="24" t="n"/>
@@ -5701,6 +6939,10 @@
       <c r="U71" s="24" t="n"/>
       <c r="V71" s="24" t="n"/>
       <c r="W71" s="24" t="n"/>
+      <c r="X71" s="24" t="n"/>
+      <c r="Y71" s="24" t="n"/>
+      <c r="Z71" s="24" t="n"/>
+      <c r="AA71" s="24" t="n"/>
     </row>
     <row r="72">
       <c r="A72" s="24" t="n"/>
@@ -5726,6 +6968,10 @@
       <c r="U72" s="24" t="n"/>
       <c r="V72" s="24" t="n"/>
       <c r="W72" s="24" t="n"/>
+      <c r="X72" s="24" t="n"/>
+      <c r="Y72" s="24" t="n"/>
+      <c r="Z72" s="24" t="n"/>
+      <c r="AA72" s="24" t="n"/>
     </row>
     <row r="73">
       <c r="A73" s="24" t="n"/>
@@ -5751,6 +6997,10 @@
       <c r="U73" s="24" t="n"/>
       <c r="V73" s="24" t="n"/>
       <c r="W73" s="24" t="n"/>
+      <c r="X73" s="24" t="n"/>
+      <c r="Y73" s="24" t="n"/>
+      <c r="Z73" s="24" t="n"/>
+      <c r="AA73" s="24" t="n"/>
     </row>
     <row r="74">
       <c r="A74" s="24" t="n"/>
@@ -5776,6 +7026,10 @@
       <c r="U74" s="24" t="n"/>
       <c r="V74" s="24" t="n"/>
       <c r="W74" s="24" t="n"/>
+      <c r="X74" s="24" t="n"/>
+      <c r="Y74" s="24" t="n"/>
+      <c r="Z74" s="24" t="n"/>
+      <c r="AA74" s="24" t="n"/>
     </row>
     <row r="75">
       <c r="A75" s="24" t="n"/>
@@ -5801,6 +7055,10 @@
       <c r="U75" s="24" t="n"/>
       <c r="V75" s="24" t="n"/>
       <c r="W75" s="24" t="n"/>
+      <c r="X75" s="24" t="n"/>
+      <c r="Y75" s="24" t="n"/>
+      <c r="Z75" s="24" t="n"/>
+      <c r="AA75" s="24" t="n"/>
     </row>
     <row r="76">
       <c r="A76" s="24" t="n"/>
@@ -5826,6 +7084,10 @@
       <c r="U76" s="24" t="n"/>
       <c r="V76" s="24" t="n"/>
       <c r="W76" s="24" t="n"/>
+      <c r="X76" s="24" t="n"/>
+      <c r="Y76" s="24" t="n"/>
+      <c r="Z76" s="24" t="n"/>
+      <c r="AA76" s="24" t="n"/>
     </row>
     <row r="77">
       <c r="A77" s="24" t="n"/>
@@ -5851,6 +7113,10 @@
       <c r="U77" s="24" t="n"/>
       <c r="V77" s="24" t="n"/>
       <c r="W77" s="24" t="n"/>
+      <c r="X77" s="24" t="n"/>
+      <c r="Y77" s="24" t="n"/>
+      <c r="Z77" s="24" t="n"/>
+      <c r="AA77" s="24" t="n"/>
     </row>
     <row r="78">
       <c r="A78" s="24" t="n"/>
@@ -5876,6 +7142,10 @@
       <c r="U78" s="24" t="n"/>
       <c r="V78" s="24" t="n"/>
       <c r="W78" s="24" t="n"/>
+      <c r="X78" s="24" t="n"/>
+      <c r="Y78" s="24" t="n"/>
+      <c r="Z78" s="24" t="n"/>
+      <c r="AA78" s="24" t="n"/>
     </row>
     <row r="79">
       <c r="A79" s="24" t="n"/>
@@ -5901,6 +7171,10 @@
       <c r="U79" s="24" t="n"/>
       <c r="V79" s="24" t="n"/>
       <c r="W79" s="24" t="n"/>
+      <c r="X79" s="24" t="n"/>
+      <c r="Y79" s="24" t="n"/>
+      <c r="Z79" s="24" t="n"/>
+      <c r="AA79" s="24" t="n"/>
     </row>
     <row r="80">
       <c r="A80" s="24" t="n"/>
@@ -5926,6 +7200,10 @@
       <c r="U80" s="24" t="n"/>
       <c r="V80" s="24" t="n"/>
       <c r="W80" s="24" t="n"/>
+      <c r="X80" s="24" t="n"/>
+      <c r="Y80" s="24" t="n"/>
+      <c r="Z80" s="24" t="n"/>
+      <c r="AA80" s="24" t="n"/>
     </row>
     <row r="81">
       <c r="A81" s="24" t="n"/>
@@ -5951,6 +7229,10 @@
       <c r="U81" s="24" t="n"/>
       <c r="V81" s="24" t="n"/>
       <c r="W81" s="24" t="n"/>
+      <c r="X81" s="24" t="n"/>
+      <c r="Y81" s="24" t="n"/>
+      <c r="Z81" s="24" t="n"/>
+      <c r="AA81" s="24" t="n"/>
     </row>
     <row r="82">
       <c r="A82" s="24" t="n"/>
@@ -5976,6 +7258,10 @@
       <c r="U82" s="24" t="n"/>
       <c r="V82" s="24" t="n"/>
       <c r="W82" s="24" t="n"/>
+      <c r="X82" s="24" t="n"/>
+      <c r="Y82" s="24" t="n"/>
+      <c r="Z82" s="24" t="n"/>
+      <c r="AA82" s="24" t="n"/>
     </row>
     <row r="83">
       <c r="A83" s="24" t="n"/>
@@ -6001,6 +7287,10 @@
       <c r="U83" s="24" t="n"/>
       <c r="V83" s="24" t="n"/>
       <c r="W83" s="24" t="n"/>
+      <c r="X83" s="24" t="n"/>
+      <c r="Y83" s="24" t="n"/>
+      <c r="Z83" s="24" t="n"/>
+      <c r="AA83" s="24" t="n"/>
     </row>
     <row r="84">
       <c r="A84" s="24" t="n"/>
@@ -6026,6 +7316,10 @@
       <c r="U84" s="24" t="n"/>
       <c r="V84" s="24" t="n"/>
       <c r="W84" s="24" t="n"/>
+      <c r="X84" s="24" t="n"/>
+      <c r="Y84" s="24" t="n"/>
+      <c r="Z84" s="24" t="n"/>
+      <c r="AA84" s="24" t="n"/>
     </row>
     <row r="85">
       <c r="A85" s="24" t="n"/>
@@ -6051,6 +7345,10 @@
       <c r="U85" s="24" t="n"/>
       <c r="V85" s="24" t="n"/>
       <c r="W85" s="24" t="n"/>
+      <c r="X85" s="24" t="n"/>
+      <c r="Y85" s="24" t="n"/>
+      <c r="Z85" s="24" t="n"/>
+      <c r="AA85" s="24" t="n"/>
     </row>
     <row r="86">
       <c r="A86" s="24" t="n"/>
@@ -6076,6 +7374,10 @@
       <c r="U86" s="24" t="n"/>
       <c r="V86" s="24" t="n"/>
       <c r="W86" s="24" t="n"/>
+      <c r="X86" s="24" t="n"/>
+      <c r="Y86" s="24" t="n"/>
+      <c r="Z86" s="24" t="n"/>
+      <c r="AA86" s="24" t="n"/>
     </row>
     <row r="87">
       <c r="A87" s="24" t="n"/>
@@ -6101,6 +7403,10 @@
       <c r="U87" s="24" t="n"/>
       <c r="V87" s="24" t="n"/>
       <c r="W87" s="24" t="n"/>
+      <c r="X87" s="24" t="n"/>
+      <c r="Y87" s="24" t="n"/>
+      <c r="Z87" s="24" t="n"/>
+      <c r="AA87" s="24" t="n"/>
     </row>
     <row r="88">
       <c r="A88" s="24" t="n"/>
@@ -6126,6 +7432,10 @@
       <c r="U88" s="24" t="n"/>
       <c r="V88" s="24" t="n"/>
       <c r="W88" s="24" t="n"/>
+      <c r="X88" s="24" t="n"/>
+      <c r="Y88" s="24" t="n"/>
+      <c r="Z88" s="24" t="n"/>
+      <c r="AA88" s="24" t="n"/>
     </row>
     <row r="89">
       <c r="A89" s="24" t="n"/>
@@ -6151,6 +7461,10 @@
       <c r="U89" s="24" t="n"/>
       <c r="V89" s="24" t="n"/>
       <c r="W89" s="24" t="n"/>
+      <c r="X89" s="24" t="n"/>
+      <c r="Y89" s="24" t="n"/>
+      <c r="Z89" s="24" t="n"/>
+      <c r="AA89" s="24" t="n"/>
     </row>
     <row r="90">
       <c r="A90" s="24" t="n"/>
@@ -6176,6 +7490,10 @@
       <c r="U90" s="24" t="n"/>
       <c r="V90" s="24" t="n"/>
       <c r="W90" s="24" t="n"/>
+      <c r="X90" s="24" t="n"/>
+      <c r="Y90" s="24" t="n"/>
+      <c r="Z90" s="24" t="n"/>
+      <c r="AA90" s="24" t="n"/>
     </row>
     <row r="91">
       <c r="A91" s="24" t="n"/>
@@ -6201,6 +7519,10 @@
       <c r="U91" s="24" t="n"/>
       <c r="V91" s="24" t="n"/>
       <c r="W91" s="24" t="n"/>
+      <c r="X91" s="24" t="n"/>
+      <c r="Y91" s="24" t="n"/>
+      <c r="Z91" s="24" t="n"/>
+      <c r="AA91" s="24" t="n"/>
     </row>
     <row r="92">
       <c r="A92" s="24" t="n"/>
@@ -6226,6 +7548,10 @@
       <c r="U92" s="24" t="n"/>
       <c r="V92" s="24" t="n"/>
       <c r="W92" s="24" t="n"/>
+      <c r="X92" s="24" t="n"/>
+      <c r="Y92" s="24" t="n"/>
+      <c r="Z92" s="24" t="n"/>
+      <c r="AA92" s="24" t="n"/>
     </row>
     <row r="93">
       <c r="A93" s="24" t="n"/>
@@ -6251,6 +7577,10 @@
       <c r="U93" s="24" t="n"/>
       <c r="V93" s="24" t="n"/>
       <c r="W93" s="24" t="n"/>
+      <c r="X93" s="24" t="n"/>
+      <c r="Y93" s="24" t="n"/>
+      <c r="Z93" s="24" t="n"/>
+      <c r="AA93" s="24" t="n"/>
     </row>
     <row r="94">
       <c r="A94" s="24" t="n"/>
@@ -6276,6 +7606,10 @@
       <c r="U94" s="24" t="n"/>
       <c r="V94" s="24" t="n"/>
       <c r="W94" s="24" t="n"/>
+      <c r="X94" s="24" t="n"/>
+      <c r="Y94" s="24" t="n"/>
+      <c r="Z94" s="24" t="n"/>
+      <c r="AA94" s="24" t="n"/>
     </row>
     <row r="95">
       <c r="A95" s="24" t="n"/>
@@ -6301,6 +7635,10 @@
       <c r="U95" s="24" t="n"/>
       <c r="V95" s="24" t="n"/>
       <c r="W95" s="24" t="n"/>
+      <c r="X95" s="24" t="n"/>
+      <c r="Y95" s="24" t="n"/>
+      <c r="Z95" s="24" t="n"/>
+      <c r="AA95" s="24" t="n"/>
     </row>
     <row r="96">
       <c r="A96" s="24" t="n"/>
@@ -6326,6 +7664,10 @@
       <c r="U96" s="24" t="n"/>
       <c r="V96" s="24" t="n"/>
       <c r="W96" s="24" t="n"/>
+      <c r="X96" s="24" t="n"/>
+      <c r="Y96" s="24" t="n"/>
+      <c r="Z96" s="24" t="n"/>
+      <c r="AA96" s="24" t="n"/>
     </row>
     <row r="97">
       <c r="A97" s="24" t="n"/>
@@ -6351,6 +7693,10 @@
       <c r="U97" s="24" t="n"/>
       <c r="V97" s="24" t="n"/>
       <c r="W97" s="24" t="n"/>
+      <c r="X97" s="24" t="n"/>
+      <c r="Y97" s="24" t="n"/>
+      <c r="Z97" s="24" t="n"/>
+      <c r="AA97" s="24" t="n"/>
     </row>
     <row r="98">
       <c r="A98" s="24" t="n"/>
@@ -6376,6 +7722,10 @@
       <c r="U98" s="24" t="n"/>
       <c r="V98" s="24" t="n"/>
       <c r="W98" s="24" t="n"/>
+      <c r="X98" s="24" t="n"/>
+      <c r="Y98" s="24" t="n"/>
+      <c r="Z98" s="24" t="n"/>
+      <c r="AA98" s="24" t="n"/>
     </row>
     <row r="99">
       <c r="A99" s="24" t="n"/>
@@ -6401,6 +7751,10 @@
       <c r="U99" s="24" t="n"/>
       <c r="V99" s="24" t="n"/>
       <c r="W99" s="24" t="n"/>
+      <c r="X99" s="24" t="n"/>
+      <c r="Y99" s="24" t="n"/>
+      <c r="Z99" s="24" t="n"/>
+      <c r="AA99" s="24" t="n"/>
     </row>
     <row r="100">
       <c r="A100" s="24" t="n"/>
@@ -6426,6 +7780,10 @@
       <c r="U100" s="24" t="n"/>
       <c r="V100" s="24" t="n"/>
       <c r="W100" s="24" t="n"/>
+      <c r="X100" s="24" t="n"/>
+      <c r="Y100" s="24" t="n"/>
+      <c r="Z100" s="24" t="n"/>
+      <c r="AA100" s="24" t="n"/>
     </row>
     <row r="101">
       <c r="A101" s="24" t="n"/>
@@ -6451,6 +7809,10 @@
       <c r="U101" s="24" t="n"/>
       <c r="V101" s="24" t="n"/>
       <c r="W101" s="24" t="n"/>
+      <c r="X101" s="24" t="n"/>
+      <c r="Y101" s="24" t="n"/>
+      <c r="Z101" s="24" t="n"/>
+      <c r="AA101" s="24" t="n"/>
     </row>
     <row r="102">
       <c r="A102" s="24" t="n"/>
@@ -6476,6 +7838,10 @@
       <c r="U102" s="24" t="n"/>
       <c r="V102" s="24" t="n"/>
       <c r="W102" s="24" t="n"/>
+      <c r="X102" s="24" t="n"/>
+      <c r="Y102" s="24" t="n"/>
+      <c r="Z102" s="24" t="n"/>
+      <c r="AA102" s="24" t="n"/>
     </row>
     <row r="103">
       <c r="A103" s="24" t="n"/>
@@ -6501,6 +7867,10 @@
       <c r="U103" s="24" t="n"/>
       <c r="V103" s="24" t="n"/>
       <c r="W103" s="24" t="n"/>
+      <c r="X103" s="24" t="n"/>
+      <c r="Y103" s="24" t="n"/>
+      <c r="Z103" s="24" t="n"/>
+      <c r="AA103" s="24" t="n"/>
     </row>
     <row r="104">
       <c r="A104" s="24" t="n"/>
@@ -6526,6 +7896,10 @@
       <c r="U104" s="24" t="n"/>
       <c r="V104" s="24" t="n"/>
       <c r="W104" s="24" t="n"/>
+      <c r="X104" s="24" t="n"/>
+      <c r="Y104" s="24" t="n"/>
+      <c r="Z104" s="24" t="n"/>
+      <c r="AA104" s="24" t="n"/>
     </row>
     <row r="105">
       <c r="A105" s="24" t="n"/>
@@ -6551,6 +7925,10 @@
       <c r="U105" s="24" t="n"/>
       <c r="V105" s="24" t="n"/>
       <c r="W105" s="24" t="n"/>
+      <c r="X105" s="24" t="n"/>
+      <c r="Y105" s="24" t="n"/>
+      <c r="Z105" s="24" t="n"/>
+      <c r="AA105" s="24" t="n"/>
     </row>
     <row r="106">
       <c r="A106" s="24" t="n"/>
@@ -6576,6 +7954,10 @@
       <c r="U106" s="24" t="n"/>
       <c r="V106" s="24" t="n"/>
       <c r="W106" s="24" t="n"/>
+      <c r="X106" s="24" t="n"/>
+      <c r="Y106" s="24" t="n"/>
+      <c r="Z106" s="24" t="n"/>
+      <c r="AA106" s="24" t="n"/>
     </row>
     <row r="107">
       <c r="A107" s="24" t="n"/>
@@ -6601,6 +7983,10 @@
       <c r="U107" s="24" t="n"/>
       <c r="V107" s="24" t="n"/>
       <c r="W107" s="24" t="n"/>
+      <c r="X107" s="24" t="n"/>
+      <c r="Y107" s="24" t="n"/>
+      <c r="Z107" s="24" t="n"/>
+      <c r="AA107" s="24" t="n"/>
     </row>
     <row r="108">
       <c r="A108" s="24" t="n"/>
@@ -6626,6 +8012,10 @@
       <c r="U108" s="24" t="n"/>
       <c r="V108" s="24" t="n"/>
       <c r="W108" s="24" t="n"/>
+      <c r="X108" s="24" t="n"/>
+      <c r="Y108" s="24" t="n"/>
+      <c r="Z108" s="24" t="n"/>
+      <c r="AA108" s="24" t="n"/>
     </row>
     <row r="109">
       <c r="A109" s="24" t="n"/>
@@ -6651,6 +8041,10 @@
       <c r="U109" s="24" t="n"/>
       <c r="V109" s="24" t="n"/>
       <c r="W109" s="24" t="n"/>
+      <c r="X109" s="24" t="n"/>
+      <c r="Y109" s="24" t="n"/>
+      <c r="Z109" s="24" t="n"/>
+      <c r="AA109" s="24" t="n"/>
     </row>
     <row r="110">
       <c r="A110" s="24" t="n"/>
@@ -6676,6 +8070,10 @@
       <c r="U110" s="24" t="n"/>
       <c r="V110" s="24" t="n"/>
       <c r="W110" s="24" t="n"/>
+      <c r="X110" s="24" t="n"/>
+      <c r="Y110" s="24" t="n"/>
+      <c r="Z110" s="24" t="n"/>
+      <c r="AA110" s="24" t="n"/>
     </row>
     <row r="111">
       <c r="A111" s="24" t="n"/>
@@ -6701,6 +8099,10 @@
       <c r="U111" s="24" t="n"/>
       <c r="V111" s="24" t="n"/>
       <c r="W111" s="24" t="n"/>
+      <c r="X111" s="24" t="n"/>
+      <c r="Y111" s="24" t="n"/>
+      <c r="Z111" s="24" t="n"/>
+      <c r="AA111" s="24" t="n"/>
     </row>
     <row r="112">
       <c r="A112" s="24" t="n"/>
@@ -6726,6 +8128,10 @@
       <c r="U112" s="24" t="n"/>
       <c r="V112" s="24" t="n"/>
       <c r="W112" s="24" t="n"/>
+      <c r="X112" s="24" t="n"/>
+      <c r="Y112" s="24" t="n"/>
+      <c r="Z112" s="24" t="n"/>
+      <c r="AA112" s="24" t="n"/>
     </row>
     <row r="113">
       <c r="A113" s="24" t="n"/>
@@ -6751,6 +8157,10 @@
       <c r="U113" s="24" t="n"/>
       <c r="V113" s="24" t="n"/>
       <c r="W113" s="24" t="n"/>
+      <c r="X113" s="24" t="n"/>
+      <c r="Y113" s="24" t="n"/>
+      <c r="Z113" s="24" t="n"/>
+      <c r="AA113" s="24" t="n"/>
     </row>
     <row r="114">
       <c r="A114" s="24" t="n"/>
@@ -6776,6 +8186,10 @@
       <c r="U114" s="24" t="n"/>
       <c r="V114" s="24" t="n"/>
       <c r="W114" s="24" t="n"/>
+      <c r="X114" s="24" t="n"/>
+      <c r="Y114" s="24" t="n"/>
+      <c r="Z114" s="24" t="n"/>
+      <c r="AA114" s="24" t="n"/>
     </row>
     <row r="115">
       <c r="A115" s="24" t="n"/>
@@ -6801,6 +8215,10 @@
       <c r="U115" s="24" t="n"/>
       <c r="V115" s="24" t="n"/>
       <c r="W115" s="24" t="n"/>
+      <c r="X115" s="24" t="n"/>
+      <c r="Y115" s="24" t="n"/>
+      <c r="Z115" s="24" t="n"/>
+      <c r="AA115" s="24" t="n"/>
     </row>
     <row r="116">
       <c r="A116" s="24" t="n"/>
@@ -6826,6 +8244,10 @@
       <c r="U116" s="24" t="n"/>
       <c r="V116" s="24" t="n"/>
       <c r="W116" s="24" t="n"/>
+      <c r="X116" s="24" t="n"/>
+      <c r="Y116" s="24" t="n"/>
+      <c r="Z116" s="24" t="n"/>
+      <c r="AA116" s="24" t="n"/>
     </row>
     <row r="117">
       <c r="A117" s="24" t="n"/>
@@ -6851,6 +8273,10 @@
       <c r="U117" s="24" t="n"/>
       <c r="V117" s="24" t="n"/>
       <c r="W117" s="24" t="n"/>
+      <c r="X117" s="24" t="n"/>
+      <c r="Y117" s="24" t="n"/>
+      <c r="Z117" s="24" t="n"/>
+      <c r="AA117" s="24" t="n"/>
     </row>
     <row r="118">
       <c r="A118" s="24" t="n"/>
@@ -6876,6 +8302,10 @@
       <c r="U118" s="24" t="n"/>
       <c r="V118" s="24" t="n"/>
       <c r="W118" s="24" t="n"/>
+      <c r="X118" s="24" t="n"/>
+      <c r="Y118" s="24" t="n"/>
+      <c r="Z118" s="24" t="n"/>
+      <c r="AA118" s="24" t="n"/>
     </row>
     <row r="119">
       <c r="A119" s="24" t="n"/>
@@ -6901,6 +8331,10 @@
       <c r="U119" s="24" t="n"/>
       <c r="V119" s="24" t="n"/>
       <c r="W119" s="24" t="n"/>
+      <c r="X119" s="24" t="n"/>
+      <c r="Y119" s="24" t="n"/>
+      <c r="Z119" s="24" t="n"/>
+      <c r="AA119" s="24" t="n"/>
     </row>
     <row r="120">
       <c r="A120" s="24" t="n"/>
@@ -6926,6 +8360,10 @@
       <c r="U120" s="24" t="n"/>
       <c r="V120" s="24" t="n"/>
       <c r="W120" s="24" t="n"/>
+      <c r="X120" s="24" t="n"/>
+      <c r="Y120" s="24" t="n"/>
+      <c r="Z120" s="24" t="n"/>
+      <c r="AA120" s="24" t="n"/>
     </row>
     <row r="121">
       <c r="A121" s="24" t="n"/>
@@ -6951,6 +8389,10 @@
       <c r="U121" s="24" t="n"/>
       <c r="V121" s="24" t="n"/>
       <c r="W121" s="24" t="n"/>
+      <c r="X121" s="24" t="n"/>
+      <c r="Y121" s="24" t="n"/>
+      <c r="Z121" s="24" t="n"/>
+      <c r="AA121" s="24" t="n"/>
     </row>
     <row r="122">
       <c r="A122" s="24" t="n"/>
@@ -6976,6 +8418,10 @@
       <c r="U122" s="24" t="n"/>
       <c r="V122" s="24" t="n"/>
       <c r="W122" s="24" t="n"/>
+      <c r="X122" s="24" t="n"/>
+      <c r="Y122" s="24" t="n"/>
+      <c r="Z122" s="24" t="n"/>
+      <c r="AA122" s="24" t="n"/>
     </row>
     <row r="123">
       <c r="A123" s="24" t="n"/>
@@ -7001,6 +8447,10 @@
       <c r="U123" s="24" t="n"/>
       <c r="V123" s="24" t="n"/>
       <c r="W123" s="24" t="n"/>
+      <c r="X123" s="24" t="n"/>
+      <c r="Y123" s="24" t="n"/>
+      <c r="Z123" s="24" t="n"/>
+      <c r="AA123" s="24" t="n"/>
     </row>
     <row r="124">
       <c r="A124" s="24" t="n"/>
@@ -7026,6 +8476,10 @@
       <c r="U124" s="24" t="n"/>
       <c r="V124" s="24" t="n"/>
       <c r="W124" s="24" t="n"/>
+      <c r="X124" s="24" t="n"/>
+      <c r="Y124" s="24" t="n"/>
+      <c r="Z124" s="24" t="n"/>
+      <c r="AA124" s="24" t="n"/>
     </row>
     <row r="125">
       <c r="A125" s="24" t="n"/>
@@ -7051,6 +8505,10 @@
       <c r="U125" s="24" t="n"/>
       <c r="V125" s="24" t="n"/>
       <c r="W125" s="24" t="n"/>
+      <c r="X125" s="24" t="n"/>
+      <c r="Y125" s="24" t="n"/>
+      <c r="Z125" s="24" t="n"/>
+      <c r="AA125" s="24" t="n"/>
     </row>
     <row r="126">
       <c r="A126" s="24" t="n"/>
@@ -7076,6 +8534,10 @@
       <c r="U126" s="24" t="n"/>
       <c r="V126" s="24" t="n"/>
       <c r="W126" s="24" t="n"/>
+      <c r="X126" s="24" t="n"/>
+      <c r="Y126" s="24" t="n"/>
+      <c r="Z126" s="24" t="n"/>
+      <c r="AA126" s="24" t="n"/>
     </row>
     <row r="127">
       <c r="A127" s="24" t="n"/>
@@ -7101,6 +8563,10 @@
       <c r="U127" s="24" t="n"/>
       <c r="V127" s="24" t="n"/>
       <c r="W127" s="24" t="n"/>
+      <c r="X127" s="24" t="n"/>
+      <c r="Y127" s="24" t="n"/>
+      <c r="Z127" s="24" t="n"/>
+      <c r="AA127" s="24" t="n"/>
     </row>
     <row r="128">
       <c r="A128" s="24" t="n"/>
@@ -7126,6 +8592,10 @@
       <c r="U128" s="24" t="n"/>
       <c r="V128" s="24" t="n"/>
       <c r="W128" s="24" t="n"/>
+      <c r="X128" s="24" t="n"/>
+      <c r="Y128" s="24" t="n"/>
+      <c r="Z128" s="24" t="n"/>
+      <c r="AA128" s="24" t="n"/>
     </row>
     <row r="129">
       <c r="A129" s="24" t="n"/>
@@ -7151,6 +8621,10 @@
       <c r="U129" s="24" t="n"/>
       <c r="V129" s="24" t="n"/>
       <c r="W129" s="24" t="n"/>
+      <c r="X129" s="24" t="n"/>
+      <c r="Y129" s="24" t="n"/>
+      <c r="Z129" s="24" t="n"/>
+      <c r="AA129" s="24" t="n"/>
     </row>
     <row r="130">
       <c r="A130" s="24" t="n"/>
@@ -7176,6 +8650,10 @@
       <c r="U130" s="24" t="n"/>
       <c r="V130" s="24" t="n"/>
       <c r="W130" s="24" t="n"/>
+      <c r="X130" s="24" t="n"/>
+      <c r="Y130" s="24" t="n"/>
+      <c r="Z130" s="24" t="n"/>
+      <c r="AA130" s="24" t="n"/>
     </row>
     <row r="131">
       <c r="A131" s="24" t="n"/>
@@ -7201,6 +8679,10 @@
       <c r="U131" s="24" t="n"/>
       <c r="V131" s="24" t="n"/>
       <c r="W131" s="24" t="n"/>
+      <c r="X131" s="24" t="n"/>
+      <c r="Y131" s="24" t="n"/>
+      <c r="Z131" s="24" t="n"/>
+      <c r="AA131" s="24" t="n"/>
     </row>
     <row r="132">
       <c r="A132" s="24" t="n"/>
@@ -7226,6 +8708,10 @@
       <c r="U132" s="24" t="n"/>
       <c r="V132" s="24" t="n"/>
       <c r="W132" s="24" t="n"/>
+      <c r="X132" s="24" t="n"/>
+      <c r="Y132" s="24" t="n"/>
+      <c r="Z132" s="24" t="n"/>
+      <c r="AA132" s="24" t="n"/>
     </row>
     <row r="133">
       <c r="A133" s="24" t="n"/>
@@ -7251,6 +8737,10 @@
       <c r="U133" s="24" t="n"/>
       <c r="V133" s="24" t="n"/>
       <c r="W133" s="24" t="n"/>
+      <c r="X133" s="24" t="n"/>
+      <c r="Y133" s="24" t="n"/>
+      <c r="Z133" s="24" t="n"/>
+      <c r="AA133" s="24" t="n"/>
     </row>
     <row r="134">
       <c r="A134" s="24" t="n"/>
@@ -7276,6 +8766,10 @@
       <c r="U134" s="24" t="n"/>
       <c r="V134" s="24" t="n"/>
       <c r="W134" s="24" t="n"/>
+      <c r="X134" s="24" t="n"/>
+      <c r="Y134" s="24" t="n"/>
+      <c r="Z134" s="24" t="n"/>
+      <c r="AA134" s="24" t="n"/>
     </row>
     <row r="135">
       <c r="A135" s="24" t="n"/>
@@ -7301,6 +8795,10 @@
       <c r="U135" s="24" t="n"/>
       <c r="V135" s="24" t="n"/>
       <c r="W135" s="24" t="n"/>
+      <c r="X135" s="24" t="n"/>
+      <c r="Y135" s="24" t="n"/>
+      <c r="Z135" s="24" t="n"/>
+      <c r="AA135" s="24" t="n"/>
     </row>
     <row r="136">
       <c r="A136" s="24" t="n"/>
@@ -7326,6 +8824,10 @@
       <c r="U136" s="24" t="n"/>
       <c r="V136" s="24" t="n"/>
       <c r="W136" s="24" t="n"/>
+      <c r="X136" s="24" t="n"/>
+      <c r="Y136" s="24" t="n"/>
+      <c r="Z136" s="24" t="n"/>
+      <c r="AA136" s="24" t="n"/>
     </row>
     <row r="137">
       <c r="A137" s="24" t="n"/>
@@ -7351,6 +8853,10 @@
       <c r="U137" s="24" t="n"/>
       <c r="V137" s="24" t="n"/>
       <c r="W137" s="24" t="n"/>
+      <c r="X137" s="24" t="n"/>
+      <c r="Y137" s="24" t="n"/>
+      <c r="Z137" s="24" t="n"/>
+      <c r="AA137" s="24" t="n"/>
     </row>
     <row r="138">
       <c r="A138" s="24" t="n"/>
@@ -7376,6 +8882,10 @@
       <c r="U138" s="24" t="n"/>
       <c r="V138" s="24" t="n"/>
       <c r="W138" s="24" t="n"/>
+      <c r="X138" s="24" t="n"/>
+      <c r="Y138" s="24" t="n"/>
+      <c r="Z138" s="24" t="n"/>
+      <c r="AA138" s="24" t="n"/>
     </row>
     <row r="139">
       <c r="A139" s="24" t="n"/>
@@ -7401,6 +8911,10 @@
       <c r="U139" s="24" t="n"/>
       <c r="V139" s="24" t="n"/>
       <c r="W139" s="24" t="n"/>
+      <c r="X139" s="24" t="n"/>
+      <c r="Y139" s="24" t="n"/>
+      <c r="Z139" s="24" t="n"/>
+      <c r="AA139" s="24" t="n"/>
     </row>
     <row r="140">
       <c r="A140" s="24" t="n"/>
@@ -7426,6 +8940,10 @@
       <c r="U140" s="24" t="n"/>
       <c r="V140" s="24" t="n"/>
       <c r="W140" s="24" t="n"/>
+      <c r="X140" s="24" t="n"/>
+      <c r="Y140" s="24" t="n"/>
+      <c r="Z140" s="24" t="n"/>
+      <c r="AA140" s="24" t="n"/>
     </row>
     <row r="141">
       <c r="A141" s="24" t="n"/>
@@ -7451,6 +8969,10 @@
       <c r="U141" s="24" t="n"/>
       <c r="V141" s="24" t="n"/>
       <c r="W141" s="24" t="n"/>
+      <c r="X141" s="24" t="n"/>
+      <c r="Y141" s="24" t="n"/>
+      <c r="Z141" s="24" t="n"/>
+      <c r="AA141" s="24" t="n"/>
     </row>
     <row r="142">
       <c r="A142" s="24" t="n"/>
@@ -7476,6 +8998,10 @@
       <c r="U142" s="24" t="n"/>
       <c r="V142" s="24" t="n"/>
       <c r="W142" s="24" t="n"/>
+      <c r="X142" s="24" t="n"/>
+      <c r="Y142" s="24" t="n"/>
+      <c r="Z142" s="24" t="n"/>
+      <c r="AA142" s="24" t="n"/>
     </row>
     <row r="143">
       <c r="A143" s="24" t="n"/>
@@ -7501,6 +9027,10 @@
       <c r="U143" s="24" t="n"/>
       <c r="V143" s="24" t="n"/>
       <c r="W143" s="24" t="n"/>
+      <c r="X143" s="24" t="n"/>
+      <c r="Y143" s="24" t="n"/>
+      <c r="Z143" s="24" t="n"/>
+      <c r="AA143" s="24" t="n"/>
     </row>
     <row r="144">
       <c r="A144" s="24" t="n"/>
@@ -7526,6 +9056,10 @@
       <c r="U144" s="24" t="n"/>
       <c r="V144" s="24" t="n"/>
       <c r="W144" s="24" t="n"/>
+      <c r="X144" s="24" t="n"/>
+      <c r="Y144" s="24" t="n"/>
+      <c r="Z144" s="24" t="n"/>
+      <c r="AA144" s="24" t="n"/>
     </row>
     <row r="145">
       <c r="A145" s="24" t="n"/>
@@ -7551,6 +9085,10 @@
       <c r="U145" s="24" t="n"/>
       <c r="V145" s="24" t="n"/>
       <c r="W145" s="24" t="n"/>
+      <c r="X145" s="24" t="n"/>
+      <c r="Y145" s="24" t="n"/>
+      <c r="Z145" s="24" t="n"/>
+      <c r="AA145" s="24" t="n"/>
     </row>
     <row r="146">
       <c r="A146" s="24" t="n"/>
@@ -7576,6 +9114,10 @@
       <c r="U146" s="24" t="n"/>
       <c r="V146" s="24" t="n"/>
       <c r="W146" s="24" t="n"/>
+      <c r="X146" s="24" t="n"/>
+      <c r="Y146" s="24" t="n"/>
+      <c r="Z146" s="24" t="n"/>
+      <c r="AA146" s="24" t="n"/>
     </row>
     <row r="147">
       <c r="A147" s="24" t="n"/>
@@ -7601,6 +9143,10 @@
       <c r="U147" s="24" t="n"/>
       <c r="V147" s="24" t="n"/>
       <c r="W147" s="24" t="n"/>
+      <c r="X147" s="24" t="n"/>
+      <c r="Y147" s="24" t="n"/>
+      <c r="Z147" s="24" t="n"/>
+      <c r="AA147" s="24" t="n"/>
     </row>
     <row r="148">
       <c r="A148" s="24" t="n"/>
@@ -7626,6 +9172,10 @@
       <c r="U148" s="24" t="n"/>
       <c r="V148" s="24" t="n"/>
       <c r="W148" s="24" t="n"/>
+      <c r="X148" s="24" t="n"/>
+      <c r="Y148" s="24" t="n"/>
+      <c r="Z148" s="24" t="n"/>
+      <c r="AA148" s="24" t="n"/>
     </row>
     <row r="149">
       <c r="A149" s="24" t="n"/>
@@ -7651,6 +9201,10 @@
       <c r="U149" s="24" t="n"/>
       <c r="V149" s="24" t="n"/>
       <c r="W149" s="24" t="n"/>
+      <c r="X149" s="24" t="n"/>
+      <c r="Y149" s="24" t="n"/>
+      <c r="Z149" s="24" t="n"/>
+      <c r="AA149" s="24" t="n"/>
     </row>
     <row r="150">
       <c r="A150" s="24" t="n"/>
@@ -7676,6 +9230,10 @@
       <c r="U150" s="24" t="n"/>
       <c r="V150" s="24" t="n"/>
       <c r="W150" s="24" t="n"/>
+      <c r="X150" s="24" t="n"/>
+      <c r="Y150" s="24" t="n"/>
+      <c r="Z150" s="24" t="n"/>
+      <c r="AA150" s="24" t="n"/>
     </row>
     <row r="151">
       <c r="A151" s="24" t="n"/>
@@ -7701,6 +9259,10 @@
       <c r="U151" s="24" t="n"/>
       <c r="V151" s="24" t="n"/>
       <c r="W151" s="24" t="n"/>
+      <c r="X151" s="24" t="n"/>
+      <c r="Y151" s="24" t="n"/>
+      <c r="Z151" s="24" t="n"/>
+      <c r="AA151" s="24" t="n"/>
     </row>
     <row r="152">
       <c r="A152" s="24" t="n"/>
@@ -7726,6 +9288,10 @@
       <c r="U152" s="24" t="n"/>
       <c r="V152" s="24" t="n"/>
       <c r="W152" s="24" t="n"/>
+      <c r="X152" s="24" t="n"/>
+      <c r="Y152" s="24" t="n"/>
+      <c r="Z152" s="24" t="n"/>
+      <c r="AA152" s="24" t="n"/>
     </row>
     <row r="153">
       <c r="A153" s="24" t="n"/>
@@ -7751,6 +9317,10 @@
       <c r="U153" s="24" t="n"/>
       <c r="V153" s="24" t="n"/>
       <c r="W153" s="24" t="n"/>
+      <c r="X153" s="24" t="n"/>
+      <c r="Y153" s="24" t="n"/>
+      <c r="Z153" s="24" t="n"/>
+      <c r="AA153" s="24" t="n"/>
     </row>
     <row r="154">
       <c r="A154" s="24" t="n"/>
@@ -7776,6 +9346,10 @@
       <c r="U154" s="24" t="n"/>
       <c r="V154" s="24" t="n"/>
       <c r="W154" s="24" t="n"/>
+      <c r="X154" s="24" t="n"/>
+      <c r="Y154" s="24" t="n"/>
+      <c r="Z154" s="24" t="n"/>
+      <c r="AA154" s="24" t="n"/>
     </row>
     <row r="155">
       <c r="A155" s="24" t="n"/>
@@ -7801,6 +9375,10 @@
       <c r="U155" s="24" t="n"/>
       <c r="V155" s="24" t="n"/>
       <c r="W155" s="24" t="n"/>
+      <c r="X155" s="24" t="n"/>
+      <c r="Y155" s="24" t="n"/>
+      <c r="Z155" s="24" t="n"/>
+      <c r="AA155" s="24" t="n"/>
     </row>
     <row r="156">
       <c r="A156" s="24" t="n"/>
@@ -7826,6 +9404,10 @@
       <c r="U156" s="24" t="n"/>
       <c r="V156" s="24" t="n"/>
       <c r="W156" s="24" t="n"/>
+      <c r="X156" s="24" t="n"/>
+      <c r="Y156" s="24" t="n"/>
+      <c r="Z156" s="24" t="n"/>
+      <c r="AA156" s="24" t="n"/>
     </row>
     <row r="157">
       <c r="A157" s="24" t="n"/>
@@ -7851,6 +9433,10 @@
       <c r="U157" s="24" t="n"/>
       <c r="V157" s="24" t="n"/>
       <c r="W157" s="24" t="n"/>
+      <c r="X157" s="24" t="n"/>
+      <c r="Y157" s="24" t="n"/>
+      <c r="Z157" s="24" t="n"/>
+      <c r="AA157" s="24" t="n"/>
     </row>
     <row r="158">
       <c r="A158" s="24" t="n"/>
@@ -7876,6 +9462,10 @@
       <c r="U158" s="24" t="n"/>
       <c r="V158" s="24" t="n"/>
       <c r="W158" s="24" t="n"/>
+      <c r="X158" s="24" t="n"/>
+      <c r="Y158" s="24" t="n"/>
+      <c r="Z158" s="24" t="n"/>
+      <c r="AA158" s="24" t="n"/>
     </row>
     <row r="159">
       <c r="A159" s="24" t="n"/>
@@ -7901,6 +9491,10 @@
       <c r="U159" s="24" t="n"/>
       <c r="V159" s="24" t="n"/>
       <c r="W159" s="24" t="n"/>
+      <c r="X159" s="24" t="n"/>
+      <c r="Y159" s="24" t="n"/>
+      <c r="Z159" s="24" t="n"/>
+      <c r="AA159" s="24" t="n"/>
     </row>
     <row r="160">
       <c r="A160" s="24" t="n"/>
@@ -7926,6 +9520,10 @@
       <c r="U160" s="24" t="n"/>
       <c r="V160" s="24" t="n"/>
       <c r="W160" s="24" t="n"/>
+      <c r="X160" s="24" t="n"/>
+      <c r="Y160" s="24" t="n"/>
+      <c r="Z160" s="24" t="n"/>
+      <c r="AA160" s="24" t="n"/>
     </row>
     <row r="161">
       <c r="A161" s="24" t="n"/>
@@ -7951,6 +9549,10 @@
       <c r="U161" s="24" t="n"/>
       <c r="V161" s="24" t="n"/>
       <c r="W161" s="24" t="n"/>
+      <c r="X161" s="24" t="n"/>
+      <c r="Y161" s="24" t="n"/>
+      <c r="Z161" s="24" t="n"/>
+      <c r="AA161" s="24" t="n"/>
     </row>
     <row r="162">
       <c r="A162" s="24" t="n"/>
@@ -7976,6 +9578,10 @@
       <c r="U162" s="24" t="n"/>
       <c r="V162" s="24" t="n"/>
       <c r="W162" s="24" t="n"/>
+      <c r="X162" s="24" t="n"/>
+      <c r="Y162" s="24" t="n"/>
+      <c r="Z162" s="24" t="n"/>
+      <c r="AA162" s="24" t="n"/>
     </row>
     <row r="163">
       <c r="A163" s="24" t="n"/>
@@ -8001,6 +9607,10 @@
       <c r="U163" s="24" t="n"/>
       <c r="V163" s="24" t="n"/>
       <c r="W163" s="24" t="n"/>
+      <c r="X163" s="24" t="n"/>
+      <c r="Y163" s="24" t="n"/>
+      <c r="Z163" s="24" t="n"/>
+      <c r="AA163" s="24" t="n"/>
     </row>
     <row r="164">
       <c r="A164" s="24" t="n"/>
@@ -8026,6 +9636,10 @@
       <c r="U164" s="24" t="n"/>
       <c r="V164" s="24" t="n"/>
       <c r="W164" s="24" t="n"/>
+      <c r="X164" s="24" t="n"/>
+      <c r="Y164" s="24" t="n"/>
+      <c r="Z164" s="24" t="n"/>
+      <c r="AA164" s="24" t="n"/>
     </row>
     <row r="165">
       <c r="A165" s="24" t="n"/>
@@ -8051,6 +9665,10 @@
       <c r="U165" s="24" t="n"/>
       <c r="V165" s="24" t="n"/>
       <c r="W165" s="24" t="n"/>
+      <c r="X165" s="24" t="n"/>
+      <c r="Y165" s="24" t="n"/>
+      <c r="Z165" s="24" t="n"/>
+      <c r="AA165" s="24" t="n"/>
     </row>
     <row r="166">
       <c r="A166" s="24" t="n"/>
@@ -8076,6 +9694,10 @@
       <c r="U166" s="24" t="n"/>
       <c r="V166" s="24" t="n"/>
       <c r="W166" s="24" t="n"/>
+      <c r="X166" s="24" t="n"/>
+      <c r="Y166" s="24" t="n"/>
+      <c r="Z166" s="24" t="n"/>
+      <c r="AA166" s="24" t="n"/>
     </row>
     <row r="167">
       <c r="A167" s="24" t="n"/>
@@ -8101,6 +9723,10 @@
       <c r="U167" s="24" t="n"/>
       <c r="V167" s="24" t="n"/>
       <c r="W167" s="24" t="n"/>
+      <c r="X167" s="24" t="n"/>
+      <c r="Y167" s="24" t="n"/>
+      <c r="Z167" s="24" t="n"/>
+      <c r="AA167" s="24" t="n"/>
     </row>
     <row r="168">
       <c r="A168" s="24" t="n"/>
@@ -8126,6 +9752,10 @@
       <c r="U168" s="24" t="n"/>
       <c r="V168" s="24" t="n"/>
       <c r="W168" s="24" t="n"/>
+      <c r="X168" s="24" t="n"/>
+      <c r="Y168" s="24" t="n"/>
+      <c r="Z168" s="24" t="n"/>
+      <c r="AA168" s="24" t="n"/>
     </row>
     <row r="169">
       <c r="A169" s="24" t="n"/>
@@ -8151,6 +9781,10 @@
       <c r="U169" s="24" t="n"/>
       <c r="V169" s="24" t="n"/>
       <c r="W169" s="24" t="n"/>
+      <c r="X169" s="24" t="n"/>
+      <c r="Y169" s="24" t="n"/>
+      <c r="Z169" s="24" t="n"/>
+      <c r="AA169" s="24" t="n"/>
     </row>
     <row r="170">
       <c r="A170" s="24" t="n"/>
@@ -8176,6 +9810,10 @@
       <c r="U170" s="24" t="n"/>
       <c r="V170" s="24" t="n"/>
       <c r="W170" s="24" t="n"/>
+      <c r="X170" s="24" t="n"/>
+      <c r="Y170" s="24" t="n"/>
+      <c r="Z170" s="24" t="n"/>
+      <c r="AA170" s="24" t="n"/>
     </row>
     <row r="171">
       <c r="A171" s="24" t="n"/>
@@ -8201,6 +9839,10 @@
       <c r="U171" s="24" t="n"/>
       <c r="V171" s="24" t="n"/>
       <c r="W171" s="24" t="n"/>
+      <c r="X171" s="24" t="n"/>
+      <c r="Y171" s="24" t="n"/>
+      <c r="Z171" s="24" t="n"/>
+      <c r="AA171" s="24" t="n"/>
     </row>
     <row r="172">
       <c r="A172" s="24" t="n"/>
@@ -8226,6 +9868,10 @@
       <c r="U172" s="24" t="n"/>
       <c r="V172" s="24" t="n"/>
       <c r="W172" s="24" t="n"/>
+      <c r="X172" s="24" t="n"/>
+      <c r="Y172" s="24" t="n"/>
+      <c r="Z172" s="24" t="n"/>
+      <c r="AA172" s="24" t="n"/>
     </row>
     <row r="173">
       <c r="A173" s="24" t="n"/>
@@ -8251,6 +9897,10 @@
       <c r="U173" s="24" t="n"/>
       <c r="V173" s="24" t="n"/>
       <c r="W173" s="24" t="n"/>
+      <c r="X173" s="24" t="n"/>
+      <c r="Y173" s="24" t="n"/>
+      <c r="Z173" s="24" t="n"/>
+      <c r="AA173" s="24" t="n"/>
     </row>
     <row r="174">
       <c r="A174" s="24" t="n"/>
@@ -8276,6 +9926,10 @@
       <c r="U174" s="24" t="n"/>
       <c r="V174" s="24" t="n"/>
       <c r="W174" s="24" t="n"/>
+      <c r="X174" s="24" t="n"/>
+      <c r="Y174" s="24" t="n"/>
+      <c r="Z174" s="24" t="n"/>
+      <c r="AA174" s="24" t="n"/>
     </row>
     <row r="175">
       <c r="A175" s="24" t="n"/>
@@ -8301,6 +9955,10 @@
       <c r="U175" s="24" t="n"/>
       <c r="V175" s="24" t="n"/>
       <c r="W175" s="24" t="n"/>
+      <c r="X175" s="24" t="n"/>
+      <c r="Y175" s="24" t="n"/>
+      <c r="Z175" s="24" t="n"/>
+      <c r="AA175" s="24" t="n"/>
     </row>
     <row r="176">
       <c r="A176" s="24" t="n"/>
@@ -8326,6 +9984,10 @@
       <c r="U176" s="24" t="n"/>
       <c r="V176" s="24" t="n"/>
       <c r="W176" s="24" t="n"/>
+      <c r="X176" s="24" t="n"/>
+      <c r="Y176" s="24" t="n"/>
+      <c r="Z176" s="24" t="n"/>
+      <c r="AA176" s="24" t="n"/>
     </row>
     <row r="177">
       <c r="A177" s="24" t="n"/>
@@ -8351,6 +10013,10 @@
       <c r="U177" s="24" t="n"/>
       <c r="V177" s="24" t="n"/>
       <c r="W177" s="24" t="n"/>
+      <c r="X177" s="24" t="n"/>
+      <c r="Y177" s="24" t="n"/>
+      <c r="Z177" s="24" t="n"/>
+      <c r="AA177" s="24" t="n"/>
     </row>
     <row r="178">
       <c r="A178" s="24" t="n"/>
@@ -8376,6 +10042,10 @@
       <c r="U178" s="24" t="n"/>
       <c r="V178" s="24" t="n"/>
       <c r="W178" s="24" t="n"/>
+      <c r="X178" s="24" t="n"/>
+      <c r="Y178" s="24" t="n"/>
+      <c r="Z178" s="24" t="n"/>
+      <c r="AA178" s="24" t="n"/>
     </row>
     <row r="179">
       <c r="A179" s="24" t="n"/>
@@ -8401,6 +10071,10 @@
       <c r="U179" s="24" t="n"/>
       <c r="V179" s="24" t="n"/>
       <c r="W179" s="24" t="n"/>
+      <c r="X179" s="24" t="n"/>
+      <c r="Y179" s="24" t="n"/>
+      <c r="Z179" s="24" t="n"/>
+      <c r="AA179" s="24" t="n"/>
     </row>
     <row r="180">
       <c r="A180" s="24" t="n"/>
@@ -8426,6 +10100,10 @@
       <c r="U180" s="24" t="n"/>
       <c r="V180" s="24" t="n"/>
       <c r="W180" s="24" t="n"/>
+      <c r="X180" s="24" t="n"/>
+      <c r="Y180" s="24" t="n"/>
+      <c r="Z180" s="24" t="n"/>
+      <c r="AA180" s="24" t="n"/>
     </row>
     <row r="181">
       <c r="A181" s="24" t="n"/>
@@ -8451,6 +10129,10 @@
       <c r="U181" s="24" t="n"/>
       <c r="V181" s="24" t="n"/>
       <c r="W181" s="24" t="n"/>
+      <c r="X181" s="24" t="n"/>
+      <c r="Y181" s="24" t="n"/>
+      <c r="Z181" s="24" t="n"/>
+      <c r="AA181" s="24" t="n"/>
     </row>
     <row r="182">
       <c r="A182" s="24" t="n"/>
@@ -8476,6 +10158,10 @@
       <c r="U182" s="24" t="n"/>
       <c r="V182" s="24" t="n"/>
       <c r="W182" s="24" t="n"/>
+      <c r="X182" s="24" t="n"/>
+      <c r="Y182" s="24" t="n"/>
+      <c r="Z182" s="24" t="n"/>
+      <c r="AA182" s="24" t="n"/>
     </row>
     <row r="183">
       <c r="A183" s="24" t="n"/>
@@ -8501,6 +10187,10 @@
       <c r="U183" s="24" t="n"/>
       <c r="V183" s="24" t="n"/>
       <c r="W183" s="24" t="n"/>
+      <c r="X183" s="24" t="n"/>
+      <c r="Y183" s="24" t="n"/>
+      <c r="Z183" s="24" t="n"/>
+      <c r="AA183" s="24" t="n"/>
     </row>
     <row r="184">
       <c r="A184" s="24" t="n"/>
@@ -8526,6 +10216,10 @@
       <c r="U184" s="24" t="n"/>
       <c r="V184" s="24" t="n"/>
       <c r="W184" s="24" t="n"/>
+      <c r="X184" s="24" t="n"/>
+      <c r="Y184" s="24" t="n"/>
+      <c r="Z184" s="24" t="n"/>
+      <c r="AA184" s="24" t="n"/>
     </row>
     <row r="185">
       <c r="A185" s="24" t="n"/>
@@ -8551,6 +10245,10 @@
       <c r="U185" s="24" t="n"/>
       <c r="V185" s="24" t="n"/>
       <c r="W185" s="24" t="n"/>
+      <c r="X185" s="24" t="n"/>
+      <c r="Y185" s="24" t="n"/>
+      <c r="Z185" s="24" t="n"/>
+      <c r="AA185" s="24" t="n"/>
     </row>
     <row r="186">
       <c r="A186" s="24" t="n"/>
@@ -8576,6 +10274,10 @@
       <c r="U186" s="24" t="n"/>
       <c r="V186" s="24" t="n"/>
       <c r="W186" s="24" t="n"/>
+      <c r="X186" s="24" t="n"/>
+      <c r="Y186" s="24" t="n"/>
+      <c r="Z186" s="24" t="n"/>
+      <c r="AA186" s="24" t="n"/>
     </row>
     <row r="187">
       <c r="A187" s="24" t="n"/>
@@ -8601,6 +10303,10 @@
       <c r="U187" s="24" t="n"/>
       <c r="V187" s="24" t="n"/>
       <c r="W187" s="24" t="n"/>
+      <c r="X187" s="24" t="n"/>
+      <c r="Y187" s="24" t="n"/>
+      <c r="Z187" s="24" t="n"/>
+      <c r="AA187" s="24" t="n"/>
     </row>
     <row r="188">
       <c r="A188" s="24" t="n"/>
@@ -8626,6 +10332,10 @@
       <c r="U188" s="24" t="n"/>
       <c r="V188" s="24" t="n"/>
       <c r="W188" s="24" t="n"/>
+      <c r="X188" s="24" t="n"/>
+      <c r="Y188" s="24" t="n"/>
+      <c r="Z188" s="24" t="n"/>
+      <c r="AA188" s="24" t="n"/>
     </row>
     <row r="189">
       <c r="A189" s="24" t="n"/>
@@ -8651,6 +10361,10 @@
       <c r="U189" s="24" t="n"/>
       <c r="V189" s="24" t="n"/>
       <c r="W189" s="24" t="n"/>
+      <c r="X189" s="24" t="n"/>
+      <c r="Y189" s="24" t="n"/>
+      <c r="Z189" s="24" t="n"/>
+      <c r="AA189" s="24" t="n"/>
     </row>
     <row r="190">
       <c r="A190" s="24" t="n"/>
@@ -8676,6 +10390,10 @@
       <c r="U190" s="24" t="n"/>
       <c r="V190" s="24" t="n"/>
       <c r="W190" s="24" t="n"/>
+      <c r="X190" s="24" t="n"/>
+      <c r="Y190" s="24" t="n"/>
+      <c r="Z190" s="24" t="n"/>
+      <c r="AA190" s="24" t="n"/>
     </row>
     <row r="191">
       <c r="A191" s="24" t="n"/>
@@ -8701,6 +10419,10 @@
       <c r="U191" s="24" t="n"/>
       <c r="V191" s="24" t="n"/>
       <c r="W191" s="24" t="n"/>
+      <c r="X191" s="24" t="n"/>
+      <c r="Y191" s="24" t="n"/>
+      <c r="Z191" s="24" t="n"/>
+      <c r="AA191" s="24" t="n"/>
     </row>
     <row r="192">
       <c r="A192" s="24" t="n"/>
@@ -8726,6 +10448,10 @@
       <c r="U192" s="24" t="n"/>
       <c r="V192" s="24" t="n"/>
       <c r="W192" s="24" t="n"/>
+      <c r="X192" s="24" t="n"/>
+      <c r="Y192" s="24" t="n"/>
+      <c r="Z192" s="24" t="n"/>
+      <c r="AA192" s="24" t="n"/>
     </row>
     <row r="193">
       <c r="A193" s="24" t="n"/>
@@ -8751,6 +10477,10 @@
       <c r="U193" s="24" t="n"/>
       <c r="V193" s="24" t="n"/>
       <c r="W193" s="24" t="n"/>
+      <c r="X193" s="24" t="n"/>
+      <c r="Y193" s="24" t="n"/>
+      <c r="Z193" s="24" t="n"/>
+      <c r="AA193" s="24" t="n"/>
     </row>
     <row r="194">
       <c r="A194" s="24" t="n"/>
@@ -8776,6 +10506,10 @@
       <c r="U194" s="24" t="n"/>
       <c r="V194" s="24" t="n"/>
       <c r="W194" s="24" t="n"/>
+      <c r="X194" s="24" t="n"/>
+      <c r="Y194" s="24" t="n"/>
+      <c r="Z194" s="24" t="n"/>
+      <c r="AA194" s="24" t="n"/>
     </row>
     <row r="195">
       <c r="A195" s="24" t="n"/>
@@ -8801,6 +10535,10 @@
       <c r="U195" s="24" t="n"/>
       <c r="V195" s="24" t="n"/>
       <c r="W195" s="24" t="n"/>
+      <c r="X195" s="24" t="n"/>
+      <c r="Y195" s="24" t="n"/>
+      <c r="Z195" s="24" t="n"/>
+      <c r="AA195" s="24" t="n"/>
     </row>
     <row r="196">
       <c r="A196" s="24" t="n"/>
@@ -8826,6 +10564,10 @@
       <c r="U196" s="24" t="n"/>
       <c r="V196" s="24" t="n"/>
       <c r="W196" s="24" t="n"/>
+      <c r="X196" s="24" t="n"/>
+      <c r="Y196" s="24" t="n"/>
+      <c r="Z196" s="24" t="n"/>
+      <c r="AA196" s="24" t="n"/>
     </row>
     <row r="197">
       <c r="A197" s="24" t="n"/>
@@ -8851,6 +10593,10 @@
       <c r="U197" s="24" t="n"/>
       <c r="V197" s="24" t="n"/>
       <c r="W197" s="24" t="n"/>
+      <c r="X197" s="24" t="n"/>
+      <c r="Y197" s="24" t="n"/>
+      <c r="Z197" s="24" t="n"/>
+      <c r="AA197" s="24" t="n"/>
     </row>
     <row r="198">
       <c r="A198" s="24" t="n"/>
@@ -8876,6 +10622,10 @@
       <c r="U198" s="24" t="n"/>
       <c r="V198" s="24" t="n"/>
       <c r="W198" s="24" t="n"/>
+      <c r="X198" s="24" t="n"/>
+      <c r="Y198" s="24" t="n"/>
+      <c r="Z198" s="24" t="n"/>
+      <c r="AA198" s="24" t="n"/>
     </row>
     <row r="199">
       <c r="A199" s="24" t="n"/>
@@ -8901,6 +10651,10 @@
       <c r="U199" s="24" t="n"/>
       <c r="V199" s="24" t="n"/>
       <c r="W199" s="24" t="n"/>
+      <c r="X199" s="24" t="n"/>
+      <c r="Y199" s="24" t="n"/>
+      <c r="Z199" s="24" t="n"/>
+      <c r="AA199" s="24" t="n"/>
     </row>
     <row r="200">
       <c r="A200" s="24" t="n"/>
@@ -8926,509 +10680,594 @@
       <c r="U200" s="24" t="n"/>
       <c r="V200" s="24" t="n"/>
       <c r="W200" s="24" t="n"/>
+      <c r="X200" s="24" t="n"/>
+      <c r="Y200" s="24" t="n"/>
+      <c r="Z200" s="24" t="n"/>
+      <c r="AA200" s="24" t="n"/>
     </row>
     <row r="201">
-      <c r="A201" s="25" t="n"/>
-      <c r="B201" s="25" t="n"/>
-      <c r="C201" s="25" t="n"/>
-      <c r="D201" s="25" t="n"/>
-      <c r="E201" s="25" t="n"/>
-      <c r="F201" s="25" t="n"/>
-      <c r="G201" s="25" t="n"/>
-      <c r="H201" s="25" t="n"/>
-      <c r="I201" s="25" t="n"/>
-      <c r="J201" s="25" t="n"/>
-      <c r="K201" s="25" t="n"/>
-      <c r="L201" s="25" t="n"/>
-      <c r="M201" s="25" t="n"/>
-      <c r="N201" s="25" t="n"/>
-      <c r="O201" s="25" t="n"/>
-      <c r="P201" s="25" t="n"/>
-      <c r="Q201" s="25" t="n"/>
-      <c r="R201" s="25" t="n"/>
-      <c r="S201" s="25" t="n"/>
-      <c r="T201" s="25" t="n"/>
-      <c r="U201" s="25" t="n"/>
-      <c r="V201" s="25" t="n"/>
-      <c r="W201" s="25" t="n"/>
+      <c r="A201" s="24" t="n"/>
+      <c r="B201" s="24" t="n"/>
+      <c r="C201" s="24" t="n"/>
+      <c r="D201" s="24" t="n"/>
+      <c r="E201" s="24" t="n"/>
+      <c r="F201" s="24" t="n"/>
+      <c r="G201" s="24" t="n"/>
+      <c r="H201" s="24" t="n"/>
+      <c r="I201" s="24" t="n"/>
+      <c r="J201" s="24" t="n"/>
+      <c r="K201" s="24" t="n"/>
+      <c r="L201" s="24" t="n"/>
+      <c r="M201" s="24" t="n"/>
+      <c r="N201" s="24" t="n"/>
+      <c r="O201" s="24" t="n"/>
+      <c r="P201" s="24" t="n"/>
+      <c r="Q201" s="24" t="n"/>
+      <c r="R201" s="24" t="n"/>
+      <c r="S201" s="24" t="n"/>
+      <c r="T201" s="24" t="n"/>
+      <c r="U201" s="24" t="n"/>
+      <c r="V201" s="24" t="n"/>
+      <c r="W201" s="24" t="n"/>
+      <c r="X201" s="24" t="n"/>
+      <c r="Y201" s="24" t="n"/>
+      <c r="Z201" s="24" t="n"/>
+      <c r="AA201" s="24" t="n"/>
     </row>
     <row r="202">
-      <c r="A202" s="25" t="n"/>
-      <c r="B202" s="25" t="n"/>
-      <c r="C202" s="25" t="n"/>
-      <c r="D202" s="25" t="n"/>
-      <c r="E202" s="25" t="n"/>
-      <c r="F202" s="25" t="n"/>
-      <c r="G202" s="25" t="n"/>
-      <c r="H202" s="25" t="n"/>
-      <c r="I202" s="25" t="n"/>
-      <c r="J202" s="25" t="n"/>
-      <c r="K202" s="25" t="n"/>
-      <c r="L202" s="25" t="n"/>
-      <c r="M202" s="25" t="n"/>
-      <c r="N202" s="25" t="n"/>
-      <c r="O202" s="25" t="n"/>
-      <c r="P202" s="25" t="n"/>
-      <c r="Q202" s="25" t="n"/>
-      <c r="R202" s="25" t="n"/>
-      <c r="S202" s="25" t="n"/>
-      <c r="T202" s="25" t="n"/>
-      <c r="U202" s="25" t="n"/>
-      <c r="V202" s="25" t="n"/>
-      <c r="W202" s="25" t="n"/>
+      <c r="A202" s="24" t="n"/>
+      <c r="B202" s="24" t="n"/>
+      <c r="C202" s="24" t="n"/>
+      <c r="D202" s="24" t="n"/>
+      <c r="E202" s="24" t="n"/>
+      <c r="F202" s="24" t="n"/>
+      <c r="G202" s="24" t="n"/>
+      <c r="H202" s="24" t="n"/>
+      <c r="I202" s="24" t="n"/>
+      <c r="J202" s="24" t="n"/>
+      <c r="K202" s="24" t="n"/>
+      <c r="L202" s="24" t="n"/>
+      <c r="M202" s="24" t="n"/>
+      <c r="N202" s="24" t="n"/>
+      <c r="O202" s="24" t="n"/>
+      <c r="P202" s="24" t="n"/>
+      <c r="Q202" s="24" t="n"/>
+      <c r="R202" s="24" t="n"/>
+      <c r="S202" s="24" t="n"/>
+      <c r="T202" s="24" t="n"/>
+      <c r="U202" s="24" t="n"/>
+      <c r="V202" s="24" t="n"/>
+      <c r="W202" s="24" t="n"/>
+      <c r="X202" s="24" t="n"/>
+      <c r="Y202" s="24" t="n"/>
+      <c r="Z202" s="24" t="n"/>
+      <c r="AA202" s="24" t="n"/>
     </row>
     <row r="203">
-      <c r="A203" s="25" t="n"/>
-      <c r="B203" s="25" t="n"/>
-      <c r="C203" s="25" t="n"/>
-      <c r="D203" s="25" t="n"/>
-      <c r="E203" s="25" t="n"/>
-      <c r="F203" s="25" t="n"/>
-      <c r="G203" s="25" t="n"/>
-      <c r="H203" s="25" t="n"/>
-      <c r="I203" s="25" t="n"/>
-      <c r="J203" s="25" t="n"/>
-      <c r="K203" s="25" t="n"/>
-      <c r="L203" s="25" t="n"/>
-      <c r="M203" s="25" t="n"/>
-      <c r="N203" s="25" t="n"/>
-      <c r="O203" s="25" t="n"/>
-      <c r="P203" s="25" t="n"/>
-      <c r="Q203" s="25" t="n"/>
-      <c r="R203" s="25" t="n"/>
-      <c r="S203" s="25" t="n"/>
-      <c r="T203" s="25" t="n"/>
-      <c r="U203" s="25" t="n"/>
-      <c r="V203" s="25" t="n"/>
-      <c r="W203" s="25" t="n"/>
+      <c r="A203" s="24" t="n"/>
+      <c r="B203" s="24" t="n"/>
+      <c r="C203" s="24" t="n"/>
+      <c r="D203" s="24" t="n"/>
+      <c r="E203" s="24" t="n"/>
+      <c r="F203" s="24" t="n"/>
+      <c r="G203" s="24" t="n"/>
+      <c r="H203" s="24" t="n"/>
+      <c r="I203" s="24" t="n"/>
+      <c r="J203" s="24" t="n"/>
+      <c r="K203" s="24" t="n"/>
+      <c r="L203" s="24" t="n"/>
+      <c r="M203" s="24" t="n"/>
+      <c r="N203" s="24" t="n"/>
+      <c r="O203" s="24" t="n"/>
+      <c r="P203" s="24" t="n"/>
+      <c r="Q203" s="24" t="n"/>
+      <c r="R203" s="24" t="n"/>
+      <c r="S203" s="24" t="n"/>
+      <c r="T203" s="24" t="n"/>
+      <c r="U203" s="24" t="n"/>
+      <c r="V203" s="24" t="n"/>
+      <c r="W203" s="24" t="n"/>
+      <c r="X203" s="24" t="n"/>
+      <c r="Y203" s="24" t="n"/>
+      <c r="Z203" s="24" t="n"/>
+      <c r="AA203" s="24" t="n"/>
     </row>
     <row r="204">
-      <c r="A204" s="25" t="n"/>
-      <c r="B204" s="25" t="n"/>
-      <c r="C204" s="25" t="n"/>
-      <c r="D204" s="25" t="n"/>
-      <c r="E204" s="25" t="n"/>
-      <c r="F204" s="25" t="n"/>
-      <c r="G204" s="25" t="n"/>
-      <c r="H204" s="25" t="n"/>
-      <c r="I204" s="25" t="n"/>
-      <c r="J204" s="25" t="n"/>
-      <c r="K204" s="25" t="n"/>
-      <c r="L204" s="25" t="n"/>
-      <c r="M204" s="25" t="n"/>
-      <c r="N204" s="25" t="n"/>
-      <c r="O204" s="25" t="n"/>
-      <c r="P204" s="25" t="n"/>
-      <c r="Q204" s="25" t="n"/>
-      <c r="R204" s="25" t="n"/>
-      <c r="S204" s="25" t="n"/>
-      <c r="T204" s="25" t="n"/>
-      <c r="U204" s="25" t="n"/>
-      <c r="V204" s="25" t="n"/>
-      <c r="W204" s="25" t="n"/>
+      <c r="A204" s="24" t="n"/>
+      <c r="B204" s="24" t="n"/>
+      <c r="C204" s="24" t="n"/>
+      <c r="D204" s="24" t="n"/>
+      <c r="E204" s="24" t="n"/>
+      <c r="F204" s="24" t="n"/>
+      <c r="G204" s="24" t="n"/>
+      <c r="H204" s="24" t="n"/>
+      <c r="I204" s="24" t="n"/>
+      <c r="J204" s="24" t="n"/>
+      <c r="K204" s="24" t="n"/>
+      <c r="L204" s="24" t="n"/>
+      <c r="M204" s="24" t="n"/>
+      <c r="N204" s="24" t="n"/>
+      <c r="O204" s="24" t="n"/>
+      <c r="P204" s="24" t="n"/>
+      <c r="Q204" s="24" t="n"/>
+      <c r="R204" s="24" t="n"/>
+      <c r="S204" s="24" t="n"/>
+      <c r="T204" s="24" t="n"/>
+      <c r="U204" s="24" t="n"/>
+      <c r="V204" s="24" t="n"/>
+      <c r="W204" s="24" t="n"/>
+      <c r="X204" s="24" t="n"/>
+      <c r="Y204" s="24" t="n"/>
+      <c r="Z204" s="24" t="n"/>
+      <c r="AA204" s="24" t="n"/>
     </row>
     <row r="205">
-      <c r="A205" s="25" t="n"/>
-      <c r="B205" s="25" t="n"/>
-      <c r="C205" s="25" t="n"/>
-      <c r="D205" s="25" t="n"/>
-      <c r="E205" s="25" t="n"/>
-      <c r="F205" s="25" t="n"/>
-      <c r="G205" s="25" t="n"/>
-      <c r="H205" s="25" t="n"/>
-      <c r="I205" s="25" t="n"/>
-      <c r="J205" s="25" t="n"/>
-      <c r="K205" s="25" t="n"/>
-      <c r="L205" s="25" t="n"/>
-      <c r="M205" s="25" t="n"/>
-      <c r="N205" s="25" t="n"/>
-      <c r="O205" s="25" t="n"/>
-      <c r="P205" s="25" t="n"/>
-      <c r="Q205" s="25" t="n"/>
-      <c r="R205" s="25" t="n"/>
-      <c r="S205" s="25" t="n"/>
-      <c r="T205" s="25" t="n"/>
-      <c r="U205" s="25" t="n"/>
-      <c r="V205" s="25" t="n"/>
-      <c r="W205" s="25" t="n"/>
+      <c r="A205" s="24" t="n"/>
+      <c r="B205" s="24" t="n"/>
+      <c r="C205" s="24" t="n"/>
+      <c r="D205" s="24" t="n"/>
+      <c r="E205" s="24" t="n"/>
+      <c r="F205" s="24" t="n"/>
+      <c r="G205" s="24" t="n"/>
+      <c r="H205" s="24" t="n"/>
+      <c r="I205" s="24" t="n"/>
+      <c r="J205" s="24" t="n"/>
+      <c r="K205" s="24" t="n"/>
+      <c r="L205" s="24" t="n"/>
+      <c r="M205" s="24" t="n"/>
+      <c r="N205" s="24" t="n"/>
+      <c r="O205" s="24" t="n"/>
+      <c r="P205" s="24" t="n"/>
+      <c r="Q205" s="24" t="n"/>
+      <c r="R205" s="24" t="n"/>
+      <c r="S205" s="24" t="n"/>
+      <c r="T205" s="24" t="n"/>
+      <c r="U205" s="24" t="n"/>
+      <c r="V205" s="24" t="n"/>
+      <c r="W205" s="24" t="n"/>
+      <c r="X205" s="24" t="n"/>
+      <c r="Y205" s="24" t="n"/>
+      <c r="Z205" s="24" t="n"/>
+      <c r="AA205" s="24" t="n"/>
     </row>
     <row r="206">
-      <c r="A206" s="25" t="n"/>
-      <c r="B206" s="25" t="n"/>
-      <c r="C206" s="25" t="n"/>
-      <c r="D206" s="25" t="n"/>
-      <c r="E206" s="25" t="n"/>
-      <c r="F206" s="25" t="n"/>
-      <c r="G206" s="25" t="n"/>
-      <c r="H206" s="25" t="n"/>
-      <c r="I206" s="25" t="n"/>
-      <c r="J206" s="25" t="n"/>
-      <c r="K206" s="25" t="n"/>
-      <c r="L206" s="25" t="n"/>
-      <c r="M206" s="25" t="n"/>
-      <c r="N206" s="25" t="n"/>
-      <c r="O206" s="25" t="n"/>
-      <c r="P206" s="25" t="n"/>
-      <c r="Q206" s="25" t="n"/>
-      <c r="R206" s="25" t="n"/>
-      <c r="S206" s="25" t="n"/>
-      <c r="T206" s="25" t="n"/>
-      <c r="U206" s="25" t="n"/>
-      <c r="V206" s="25" t="n"/>
-      <c r="W206" s="25" t="n"/>
+      <c r="A206" s="24" t="n"/>
+      <c r="B206" s="24" t="n"/>
+      <c r="C206" s="24" t="n"/>
+      <c r="D206" s="24" t="n"/>
+      <c r="E206" s="24" t="n"/>
+      <c r="F206" s="24" t="n"/>
+      <c r="G206" s="24" t="n"/>
+      <c r="H206" s="24" t="n"/>
+      <c r="I206" s="24" t="n"/>
+      <c r="J206" s="24" t="n"/>
+      <c r="K206" s="24" t="n"/>
+      <c r="L206" s="24" t="n"/>
+      <c r="M206" s="24" t="n"/>
+      <c r="N206" s="24" t="n"/>
+      <c r="O206" s="24" t="n"/>
+      <c r="P206" s="24" t="n"/>
+      <c r="Q206" s="24" t="n"/>
+      <c r="R206" s="24" t="n"/>
+      <c r="S206" s="24" t="n"/>
+      <c r="T206" s="24" t="n"/>
+      <c r="U206" s="24" t="n"/>
+      <c r="V206" s="24" t="n"/>
+      <c r="W206" s="24" t="n"/>
+      <c r="X206" s="24" t="n"/>
+      <c r="Y206" s="24" t="n"/>
+      <c r="Z206" s="24" t="n"/>
+      <c r="AA206" s="24" t="n"/>
     </row>
     <row r="207">
-      <c r="A207" s="25" t="n"/>
-      <c r="B207" s="25" t="n"/>
-      <c r="C207" s="25" t="n"/>
-      <c r="D207" s="25" t="n"/>
-      <c r="E207" s="25" t="n"/>
-      <c r="F207" s="25" t="n"/>
-      <c r="G207" s="25" t="n"/>
-      <c r="H207" s="25" t="n"/>
-      <c r="I207" s="25" t="n"/>
-      <c r="J207" s="25" t="n"/>
-      <c r="K207" s="25" t="n"/>
-      <c r="L207" s="25" t="n"/>
-      <c r="M207" s="25" t="n"/>
-      <c r="N207" s="25" t="n"/>
-      <c r="O207" s="25" t="n"/>
-      <c r="P207" s="25" t="n"/>
-      <c r="Q207" s="25" t="n"/>
-      <c r="R207" s="25" t="n"/>
-      <c r="S207" s="25" t="n"/>
-      <c r="T207" s="25" t="n"/>
-      <c r="U207" s="25" t="n"/>
-      <c r="V207" s="25" t="n"/>
-      <c r="W207" s="25" t="n"/>
+      <c r="A207" s="24" t="n"/>
+      <c r="B207" s="24" t="n"/>
+      <c r="C207" s="24" t="n"/>
+      <c r="D207" s="24" t="n"/>
+      <c r="E207" s="24" t="n"/>
+      <c r="F207" s="24" t="n"/>
+      <c r="G207" s="24" t="n"/>
+      <c r="H207" s="24" t="n"/>
+      <c r="I207" s="24" t="n"/>
+      <c r="J207" s="24" t="n"/>
+      <c r="K207" s="24" t="n"/>
+      <c r="L207" s="24" t="n"/>
+      <c r="M207" s="24" t="n"/>
+      <c r="N207" s="24" t="n"/>
+      <c r="O207" s="24" t="n"/>
+      <c r="P207" s="24" t="n"/>
+      <c r="Q207" s="24" t="n"/>
+      <c r="R207" s="24" t="n"/>
+      <c r="S207" s="24" t="n"/>
+      <c r="T207" s="24" t="n"/>
+      <c r="U207" s="24" t="n"/>
+      <c r="V207" s="24" t="n"/>
+      <c r="W207" s="24" t="n"/>
+      <c r="X207" s="24" t="n"/>
+      <c r="Y207" s="24" t="n"/>
+      <c r="Z207" s="24" t="n"/>
+      <c r="AA207" s="24" t="n"/>
     </row>
     <row r="208">
-      <c r="A208" s="25" t="n"/>
-      <c r="B208" s="25" t="n"/>
-      <c r="C208" s="25" t="n"/>
-      <c r="D208" s="25" t="n"/>
-      <c r="E208" s="25" t="n"/>
-      <c r="F208" s="25" t="n"/>
-      <c r="G208" s="25" t="n"/>
-      <c r="H208" s="25" t="n"/>
-      <c r="I208" s="25" t="n"/>
-      <c r="J208" s="25" t="n"/>
-      <c r="K208" s="25" t="n"/>
-      <c r="L208" s="25" t="n"/>
-      <c r="M208" s="25" t="n"/>
-      <c r="N208" s="25" t="n"/>
-      <c r="O208" s="25" t="n"/>
-      <c r="P208" s="25" t="n"/>
-      <c r="Q208" s="25" t="n"/>
-      <c r="R208" s="25" t="n"/>
-      <c r="S208" s="25" t="n"/>
-      <c r="T208" s="25" t="n"/>
-      <c r="U208" s="25" t="n"/>
-      <c r="V208" s="25" t="n"/>
-      <c r="W208" s="25" t="n"/>
+      <c r="A208" s="24" t="n"/>
+      <c r="B208" s="24" t="n"/>
+      <c r="C208" s="24" t="n"/>
+      <c r="D208" s="24" t="n"/>
+      <c r="E208" s="24" t="n"/>
+      <c r="F208" s="24" t="n"/>
+      <c r="G208" s="24" t="n"/>
+      <c r="H208" s="24" t="n"/>
+      <c r="I208" s="24" t="n"/>
+      <c r="J208" s="24" t="n"/>
+      <c r="K208" s="24" t="n"/>
+      <c r="L208" s="24" t="n"/>
+      <c r="M208" s="24" t="n"/>
+      <c r="N208" s="24" t="n"/>
+      <c r="O208" s="24" t="n"/>
+      <c r="P208" s="24" t="n"/>
+      <c r="Q208" s="24" t="n"/>
+      <c r="R208" s="24" t="n"/>
+      <c r="S208" s="24" t="n"/>
+      <c r="T208" s="24" t="n"/>
+      <c r="U208" s="24" t="n"/>
+      <c r="V208" s="24" t="n"/>
+      <c r="W208" s="24" t="n"/>
+      <c r="X208" s="24" t="n"/>
+      <c r="Y208" s="24" t="n"/>
+      <c r="Z208" s="24" t="n"/>
+      <c r="AA208" s="24" t="n"/>
     </row>
     <row r="209">
-      <c r="A209" s="25" t="n"/>
-      <c r="B209" s="25" t="n"/>
-      <c r="C209" s="25" t="n"/>
-      <c r="D209" s="25" t="n"/>
-      <c r="E209" s="25" t="n"/>
-      <c r="F209" s="25" t="n"/>
-      <c r="G209" s="25" t="n"/>
-      <c r="H209" s="25" t="n"/>
-      <c r="I209" s="25" t="n"/>
-      <c r="J209" s="25" t="n"/>
-      <c r="K209" s="25" t="n"/>
-      <c r="L209" s="25" t="n"/>
-      <c r="M209" s="25" t="n"/>
-      <c r="N209" s="25" t="n"/>
-      <c r="O209" s="25" t="n"/>
-      <c r="P209" s="25" t="n"/>
-      <c r="Q209" s="25" t="n"/>
-      <c r="R209" s="25" t="n"/>
-      <c r="S209" s="25" t="n"/>
-      <c r="T209" s="25" t="n"/>
-      <c r="U209" s="25" t="n"/>
-      <c r="V209" s="25" t="n"/>
-      <c r="W209" s="25" t="n"/>
+      <c r="A209" s="24" t="n"/>
+      <c r="B209" s="24" t="n"/>
+      <c r="C209" s="24" t="n"/>
+      <c r="D209" s="24" t="n"/>
+      <c r="E209" s="24" t="n"/>
+      <c r="F209" s="24" t="n"/>
+      <c r="G209" s="24" t="n"/>
+      <c r="H209" s="24" t="n"/>
+      <c r="I209" s="24" t="n"/>
+      <c r="J209" s="24" t="n"/>
+      <c r="K209" s="24" t="n"/>
+      <c r="L209" s="24" t="n"/>
+      <c r="M209" s="24" t="n"/>
+      <c r="N209" s="24" t="n"/>
+      <c r="O209" s="24" t="n"/>
+      <c r="P209" s="24" t="n"/>
+      <c r="Q209" s="24" t="n"/>
+      <c r="R209" s="24" t="n"/>
+      <c r="S209" s="24" t="n"/>
+      <c r="T209" s="24" t="n"/>
+      <c r="U209" s="24" t="n"/>
+      <c r="V209" s="24" t="n"/>
+      <c r="W209" s="24" t="n"/>
+      <c r="X209" s="24" t="n"/>
+      <c r="Y209" s="24" t="n"/>
+      <c r="Z209" s="24" t="n"/>
+      <c r="AA209" s="24" t="n"/>
     </row>
     <row r="210">
-      <c r="A210" s="25" t="n"/>
-      <c r="B210" s="25" t="n"/>
-      <c r="C210" s="25" t="n"/>
-      <c r="D210" s="25" t="n"/>
-      <c r="E210" s="25" t="n"/>
-      <c r="F210" s="25" t="n"/>
-      <c r="G210" s="25" t="n"/>
-      <c r="H210" s="25" t="n"/>
-      <c r="I210" s="25" t="n"/>
-      <c r="J210" s="25" t="n"/>
-      <c r="K210" s="25" t="n"/>
-      <c r="L210" s="25" t="n"/>
-      <c r="M210" s="25" t="n"/>
-      <c r="N210" s="25" t="n"/>
-      <c r="O210" s="25" t="n"/>
-      <c r="P210" s="25" t="n"/>
-      <c r="Q210" s="25" t="n"/>
-      <c r="R210" s="25" t="n"/>
-      <c r="S210" s="25" t="n"/>
-      <c r="T210" s="25" t="n"/>
-      <c r="U210" s="25" t="n"/>
-      <c r="V210" s="25" t="n"/>
-      <c r="W210" s="25" t="n"/>
+      <c r="A210" s="24" t="n"/>
+      <c r="B210" s="24" t="n"/>
+      <c r="C210" s="24" t="n"/>
+      <c r="D210" s="24" t="n"/>
+      <c r="E210" s="24" t="n"/>
+      <c r="F210" s="24" t="n"/>
+      <c r="G210" s="24" t="n"/>
+      <c r="H210" s="24" t="n"/>
+      <c r="I210" s="24" t="n"/>
+      <c r="J210" s="24" t="n"/>
+      <c r="K210" s="24" t="n"/>
+      <c r="L210" s="24" t="n"/>
+      <c r="M210" s="24" t="n"/>
+      <c r="N210" s="24" t="n"/>
+      <c r="O210" s="24" t="n"/>
+      <c r="P210" s="24" t="n"/>
+      <c r="Q210" s="24" t="n"/>
+      <c r="R210" s="24" t="n"/>
+      <c r="S210" s="24" t="n"/>
+      <c r="T210" s="24" t="n"/>
+      <c r="U210" s="24" t="n"/>
+      <c r="V210" s="24" t="n"/>
+      <c r="W210" s="24" t="n"/>
+      <c r="X210" s="24" t="n"/>
+      <c r="Y210" s="24" t="n"/>
+      <c r="Z210" s="24" t="n"/>
+      <c r="AA210" s="24" t="n"/>
     </row>
     <row r="211">
-      <c r="A211" s="25" t="n"/>
-      <c r="B211" s="25" t="n"/>
-      <c r="C211" s="25" t="n"/>
-      <c r="D211" s="25" t="n"/>
-      <c r="E211" s="25" t="n"/>
-      <c r="F211" s="25" t="n"/>
-      <c r="G211" s="25" t="n"/>
-      <c r="H211" s="25" t="n"/>
-      <c r="I211" s="25" t="n"/>
-      <c r="J211" s="25" t="n"/>
-      <c r="K211" s="25" t="n"/>
-      <c r="L211" s="25" t="n"/>
-      <c r="M211" s="25" t="n"/>
-      <c r="N211" s="25" t="n"/>
-      <c r="O211" s="25" t="n"/>
-      <c r="P211" s="25" t="n"/>
-      <c r="Q211" s="25" t="n"/>
-      <c r="R211" s="25" t="n"/>
-      <c r="S211" s="25" t="n"/>
-      <c r="T211" s="25" t="n"/>
-      <c r="U211" s="25" t="n"/>
-      <c r="V211" s="25" t="n"/>
-      <c r="W211" s="25" t="n"/>
+      <c r="A211" s="24" t="n"/>
+      <c r="B211" s="24" t="n"/>
+      <c r="C211" s="24" t="n"/>
+      <c r="D211" s="24" t="n"/>
+      <c r="E211" s="24" t="n"/>
+      <c r="F211" s="24" t="n"/>
+      <c r="G211" s="24" t="n"/>
+      <c r="H211" s="24" t="n"/>
+      <c r="I211" s="24" t="n"/>
+      <c r="J211" s="24" t="n"/>
+      <c r="K211" s="24" t="n"/>
+      <c r="L211" s="24" t="n"/>
+      <c r="M211" s="24" t="n"/>
+      <c r="N211" s="24" t="n"/>
+      <c r="O211" s="24" t="n"/>
+      <c r="P211" s="24" t="n"/>
+      <c r="Q211" s="24" t="n"/>
+      <c r="R211" s="24" t="n"/>
+      <c r="S211" s="24" t="n"/>
+      <c r="T211" s="24" t="n"/>
+      <c r="U211" s="24" t="n"/>
+      <c r="V211" s="24" t="n"/>
+      <c r="W211" s="24" t="n"/>
+      <c r="X211" s="24" t="n"/>
+      <c r="Y211" s="24" t="n"/>
+      <c r="Z211" s="24" t="n"/>
+      <c r="AA211" s="24" t="n"/>
     </row>
     <row r="212">
-      <c r="A212" s="25" t="n"/>
-      <c r="B212" s="25" t="n"/>
-      <c r="C212" s="25" t="n"/>
-      <c r="D212" s="25" t="n"/>
-      <c r="E212" s="25" t="n"/>
-      <c r="F212" s="25" t="n"/>
-      <c r="G212" s="25" t="n"/>
-      <c r="H212" s="25" t="n"/>
-      <c r="I212" s="25" t="n"/>
-      <c r="J212" s="25" t="n"/>
-      <c r="K212" s="25" t="n"/>
-      <c r="L212" s="25" t="n"/>
-      <c r="M212" s="25" t="n"/>
-      <c r="N212" s="25" t="n"/>
-      <c r="O212" s="25" t="n"/>
-      <c r="P212" s="25" t="n"/>
-      <c r="Q212" s="25" t="n"/>
-      <c r="R212" s="25" t="n"/>
-      <c r="S212" s="25" t="n"/>
-      <c r="T212" s="25" t="n"/>
-      <c r="U212" s="25" t="n"/>
-      <c r="V212" s="25" t="n"/>
-      <c r="W212" s="25" t="n"/>
+      <c r="A212" s="24" t="n"/>
+      <c r="B212" s="24" t="n"/>
+      <c r="C212" s="24" t="n"/>
+      <c r="D212" s="24" t="n"/>
+      <c r="E212" s="24" t="n"/>
+      <c r="F212" s="24" t="n"/>
+      <c r="G212" s="24" t="n"/>
+      <c r="H212" s="24" t="n"/>
+      <c r="I212" s="24" t="n"/>
+      <c r="J212" s="24" t="n"/>
+      <c r="K212" s="24" t="n"/>
+      <c r="L212" s="24" t="n"/>
+      <c r="M212" s="24" t="n"/>
+      <c r="N212" s="24" t="n"/>
+      <c r="O212" s="24" t="n"/>
+      <c r="P212" s="24" t="n"/>
+      <c r="Q212" s="24" t="n"/>
+      <c r="R212" s="24" t="n"/>
+      <c r="S212" s="24" t="n"/>
+      <c r="T212" s="24" t="n"/>
+      <c r="U212" s="24" t="n"/>
+      <c r="V212" s="24" t="n"/>
+      <c r="W212" s="24" t="n"/>
+      <c r="X212" s="24" t="n"/>
+      <c r="Y212" s="24" t="n"/>
+      <c r="Z212" s="24" t="n"/>
+      <c r="AA212" s="24" t="n"/>
     </row>
     <row r="213">
-      <c r="A213" s="25" t="n"/>
-      <c r="B213" s="25" t="n"/>
-      <c r="C213" s="25" t="n"/>
-      <c r="D213" s="25" t="n"/>
-      <c r="E213" s="25" t="n"/>
-      <c r="F213" s="25" t="n"/>
-      <c r="G213" s="25" t="n"/>
-      <c r="H213" s="25" t="n"/>
-      <c r="I213" s="25" t="n"/>
-      <c r="J213" s="25" t="n"/>
-      <c r="K213" s="25" t="n"/>
-      <c r="L213" s="25" t="n"/>
-      <c r="M213" s="25" t="n"/>
-      <c r="N213" s="25" t="n"/>
-      <c r="O213" s="25" t="n"/>
-      <c r="P213" s="25" t="n"/>
-      <c r="Q213" s="25" t="n"/>
-      <c r="R213" s="25" t="n"/>
-      <c r="S213" s="25" t="n"/>
-      <c r="T213" s="25" t="n"/>
-      <c r="U213" s="25" t="n"/>
-      <c r="V213" s="25" t="n"/>
-      <c r="W213" s="25" t="n"/>
+      <c r="A213" s="24" t="n"/>
+      <c r="B213" s="24" t="n"/>
+      <c r="C213" s="24" t="n"/>
+      <c r="D213" s="24" t="n"/>
+      <c r="E213" s="24" t="n"/>
+      <c r="F213" s="24" t="n"/>
+      <c r="G213" s="24" t="n"/>
+      <c r="H213" s="24" t="n"/>
+      <c r="I213" s="24" t="n"/>
+      <c r="J213" s="24" t="n"/>
+      <c r="K213" s="24" t="n"/>
+      <c r="L213" s="24" t="n"/>
+      <c r="M213" s="24" t="n"/>
+      <c r="N213" s="24" t="n"/>
+      <c r="O213" s="24" t="n"/>
+      <c r="P213" s="24" t="n"/>
+      <c r="Q213" s="24" t="n"/>
+      <c r="R213" s="24" t="n"/>
+      <c r="S213" s="24" t="n"/>
+      <c r="T213" s="24" t="n"/>
+      <c r="U213" s="24" t="n"/>
+      <c r="V213" s="24" t="n"/>
+      <c r="W213" s="24" t="n"/>
+      <c r="X213" s="24" t="n"/>
+      <c r="Y213" s="24" t="n"/>
+      <c r="Z213" s="24" t="n"/>
+      <c r="AA213" s="24" t="n"/>
     </row>
     <row r="214">
-      <c r="A214" s="25" t="n"/>
-      <c r="B214" s="25" t="n"/>
-      <c r="C214" s="25" t="n"/>
-      <c r="D214" s="25" t="n"/>
-      <c r="E214" s="25" t="n"/>
-      <c r="F214" s="25" t="n"/>
-      <c r="G214" s="25" t="n"/>
-      <c r="H214" s="25" t="n"/>
-      <c r="I214" s="25" t="n"/>
-      <c r="J214" s="25" t="n"/>
-      <c r="K214" s="25" t="n"/>
-      <c r="L214" s="25" t="n"/>
-      <c r="M214" s="25" t="n"/>
-      <c r="N214" s="25" t="n"/>
-      <c r="O214" s="25" t="n"/>
-      <c r="P214" s="25" t="n"/>
-      <c r="Q214" s="25" t="n"/>
-      <c r="R214" s="25" t="n"/>
-      <c r="S214" s="25" t="n"/>
-      <c r="T214" s="25" t="n"/>
-      <c r="U214" s="25" t="n"/>
-      <c r="V214" s="25" t="n"/>
-      <c r="W214" s="25" t="n"/>
+      <c r="A214" s="24" t="n"/>
+      <c r="B214" s="24" t="n"/>
+      <c r="C214" s="24" t="n"/>
+      <c r="D214" s="24" t="n"/>
+      <c r="E214" s="24" t="n"/>
+      <c r="F214" s="24" t="n"/>
+      <c r="G214" s="24" t="n"/>
+      <c r="H214" s="24" t="n"/>
+      <c r="I214" s="24" t="n"/>
+      <c r="J214" s="24" t="n"/>
+      <c r="K214" s="24" t="n"/>
+      <c r="L214" s="24" t="n"/>
+      <c r="M214" s="24" t="n"/>
+      <c r="N214" s="24" t="n"/>
+      <c r="O214" s="24" t="n"/>
+      <c r="P214" s="24" t="n"/>
+      <c r="Q214" s="24" t="n"/>
+      <c r="R214" s="24" t="n"/>
+      <c r="S214" s="24" t="n"/>
+      <c r="T214" s="24" t="n"/>
+      <c r="U214" s="24" t="n"/>
+      <c r="V214" s="24" t="n"/>
+      <c r="W214" s="24" t="n"/>
+      <c r="X214" s="24" t="n"/>
+      <c r="Y214" s="24" t="n"/>
+      <c r="Z214" s="24" t="n"/>
+      <c r="AA214" s="24" t="n"/>
     </row>
     <row r="215">
-      <c r="A215" s="25" t="n"/>
-      <c r="B215" s="25" t="n"/>
-      <c r="C215" s="25" t="n"/>
-      <c r="D215" s="25" t="n"/>
-      <c r="E215" s="25" t="n"/>
-      <c r="F215" s="25" t="n"/>
-      <c r="G215" s="25" t="n"/>
-      <c r="H215" s="25" t="n"/>
-      <c r="I215" s="25" t="n"/>
-      <c r="J215" s="25" t="n"/>
-      <c r="K215" s="25" t="n"/>
-      <c r="L215" s="25" t="n"/>
-      <c r="M215" s="25" t="n"/>
-      <c r="N215" s="25" t="n"/>
-      <c r="O215" s="25" t="n"/>
-      <c r="P215" s="25" t="n"/>
-      <c r="Q215" s="25" t="n"/>
-      <c r="R215" s="25" t="n"/>
-      <c r="S215" s="25" t="n"/>
-      <c r="T215" s="25" t="n"/>
-      <c r="U215" s="25" t="n"/>
-      <c r="V215" s="25" t="n"/>
-      <c r="W215" s="25" t="n"/>
+      <c r="A215" s="24" t="n"/>
+      <c r="B215" s="24" t="n"/>
+      <c r="C215" s="24" t="n"/>
+      <c r="D215" s="24" t="n"/>
+      <c r="E215" s="24" t="n"/>
+      <c r="F215" s="24" t="n"/>
+      <c r="G215" s="24" t="n"/>
+      <c r="H215" s="24" t="n"/>
+      <c r="I215" s="24" t="n"/>
+      <c r="J215" s="24" t="n"/>
+      <c r="K215" s="24" t="n"/>
+      <c r="L215" s="24" t="n"/>
+      <c r="M215" s="24" t="n"/>
+      <c r="N215" s="24" t="n"/>
+      <c r="O215" s="24" t="n"/>
+      <c r="P215" s="24" t="n"/>
+      <c r="Q215" s="24" t="n"/>
+      <c r="R215" s="24" t="n"/>
+      <c r="S215" s="24" t="n"/>
+      <c r="T215" s="24" t="n"/>
+      <c r="U215" s="24" t="n"/>
+      <c r="V215" s="24" t="n"/>
+      <c r="W215" s="24" t="n"/>
+      <c r="X215" s="24" t="n"/>
+      <c r="Y215" s="24" t="n"/>
+      <c r="Z215" s="24" t="n"/>
+      <c r="AA215" s="24" t="n"/>
     </row>
     <row r="216">
-      <c r="A216" s="25" t="n"/>
-      <c r="B216" s="25" t="n"/>
-      <c r="C216" s="25" t="n"/>
-      <c r="D216" s="25" t="n"/>
-      <c r="E216" s="25" t="n"/>
-      <c r="F216" s="25" t="n"/>
-      <c r="G216" s="25" t="n"/>
-      <c r="H216" s="25" t="n"/>
-      <c r="I216" s="25" t="n"/>
-      <c r="J216" s="25" t="n"/>
-      <c r="K216" s="25" t="n"/>
-      <c r="L216" s="25" t="n"/>
-      <c r="M216" s="25" t="n"/>
-      <c r="N216" s="25" t="n"/>
-      <c r="O216" s="25" t="n"/>
-      <c r="P216" s="25" t="n"/>
-      <c r="Q216" s="25" t="n"/>
-      <c r="R216" s="25" t="n"/>
-      <c r="S216" s="25" t="n"/>
-      <c r="T216" s="25" t="n"/>
-      <c r="U216" s="25" t="n"/>
-      <c r="V216" s="25" t="n"/>
-      <c r="W216" s="25" t="n"/>
+      <c r="A216" s="24" t="n"/>
+      <c r="B216" s="24" t="n"/>
+      <c r="C216" s="24" t="n"/>
+      <c r="D216" s="24" t="n"/>
+      <c r="E216" s="24" t="n"/>
+      <c r="F216" s="24" t="n"/>
+      <c r="G216" s="24" t="n"/>
+      <c r="H216" s="24" t="n"/>
+      <c r="I216" s="24" t="n"/>
+      <c r="J216" s="24" t="n"/>
+      <c r="K216" s="24" t="n"/>
+      <c r="L216" s="24" t="n"/>
+      <c r="M216" s="24" t="n"/>
+      <c r="N216" s="24" t="n"/>
+      <c r="O216" s="24" t="n"/>
+      <c r="P216" s="24" t="n"/>
+      <c r="Q216" s="24" t="n"/>
+      <c r="R216" s="24" t="n"/>
+      <c r="S216" s="24" t="n"/>
+      <c r="T216" s="24" t="n"/>
+      <c r="U216" s="24" t="n"/>
+      <c r="V216" s="24" t="n"/>
+      <c r="W216" s="24" t="n"/>
+      <c r="X216" s="24" t="n"/>
+      <c r="Y216" s="24" t="n"/>
+      <c r="Z216" s="24" t="n"/>
+      <c r="AA216" s="24" t="n"/>
     </row>
     <row r="217">
-      <c r="A217" s="25" t="n"/>
-      <c r="B217" s="25" t="n"/>
-      <c r="C217" s="25" t="n"/>
-      <c r="D217" s="25" t="n"/>
-      <c r="E217" s="25" t="n"/>
-      <c r="F217" s="25" t="n"/>
-      <c r="G217" s="25" t="n"/>
-      <c r="H217" s="25" t="n"/>
-      <c r="I217" s="25" t="n"/>
-      <c r="J217" s="25" t="n"/>
-      <c r="K217" s="25" t="n"/>
-      <c r="L217" s="25" t="n"/>
-      <c r="M217" s="25" t="n"/>
-      <c r="N217" s="25" t="n"/>
-      <c r="O217" s="25" t="n"/>
-      <c r="P217" s="25" t="n"/>
-      <c r="Q217" s="25" t="n"/>
-      <c r="R217" s="25" t="n"/>
-      <c r="S217" s="25" t="n"/>
-      <c r="T217" s="25" t="n"/>
-      <c r="U217" s="25" t="n"/>
-      <c r="V217" s="25" t="n"/>
-      <c r="W217" s="25" t="n"/>
+      <c r="A217" s="24" t="n"/>
+      <c r="B217" s="24" t="n"/>
+      <c r="C217" s="24" t="n"/>
+      <c r="D217" s="24" t="n"/>
+      <c r="E217" s="24" t="n"/>
+      <c r="F217" s="24" t="n"/>
+      <c r="G217" s="24" t="n"/>
+      <c r="H217" s="24" t="n"/>
+      <c r="I217" s="24" t="n"/>
+      <c r="J217" s="24" t="n"/>
+      <c r="K217" s="24" t="n"/>
+      <c r="L217" s="24" t="n"/>
+      <c r="M217" s="24" t="n"/>
+      <c r="N217" s="24" t="n"/>
+      <c r="O217" s="24" t="n"/>
+      <c r="P217" s="24" t="n"/>
+      <c r="Q217" s="24" t="n"/>
+      <c r="R217" s="24" t="n"/>
+      <c r="S217" s="24" t="n"/>
+      <c r="T217" s="24" t="n"/>
+      <c r="U217" s="24" t="n"/>
+      <c r="V217" s="24" t="n"/>
+      <c r="W217" s="24" t="n"/>
+      <c r="X217" s="24" t="n"/>
+      <c r="Y217" s="24" t="n"/>
+      <c r="Z217" s="24" t="n"/>
+      <c r="AA217" s="24" t="n"/>
     </row>
     <row r="218">
-      <c r="A218" s="25" t="n"/>
-      <c r="B218" s="25" t="n"/>
-      <c r="C218" s="25" t="n"/>
-      <c r="D218" s="25" t="n"/>
-      <c r="E218" s="25" t="n"/>
-      <c r="F218" s="25" t="n"/>
-      <c r="G218" s="25" t="n"/>
-      <c r="H218" s="25" t="n"/>
-      <c r="I218" s="25" t="n"/>
-      <c r="J218" s="25" t="n"/>
-      <c r="K218" s="25" t="n"/>
-      <c r="L218" s="25" t="n"/>
-      <c r="M218" s="25" t="n"/>
-      <c r="N218" s="25" t="n"/>
-      <c r="O218" s="25" t="n"/>
-      <c r="P218" s="25" t="n"/>
-      <c r="Q218" s="25" t="n"/>
-      <c r="R218" s="25" t="n"/>
-      <c r="S218" s="25" t="n"/>
-      <c r="T218" s="25" t="n"/>
-      <c r="U218" s="25" t="n"/>
-      <c r="V218" s="25" t="n"/>
-      <c r="W218" s="25" t="n"/>
+      <c r="A218" s="24" t="n"/>
+      <c r="B218" s="24" t="n"/>
+      <c r="C218" s="24" t="n"/>
+      <c r="D218" s="24" t="n"/>
+      <c r="E218" s="24" t="n"/>
+      <c r="F218" s="24" t="n"/>
+      <c r="G218" s="24" t="n"/>
+      <c r="H218" s="24" t="n"/>
+      <c r="I218" s="24" t="n"/>
+      <c r="J218" s="24" t="n"/>
+      <c r="K218" s="24" t="n"/>
+      <c r="L218" s="24" t="n"/>
+      <c r="M218" s="24" t="n"/>
+      <c r="N218" s="24" t="n"/>
+      <c r="O218" s="24" t="n"/>
+      <c r="P218" s="24" t="n"/>
+      <c r="Q218" s="24" t="n"/>
+      <c r="R218" s="24" t="n"/>
+      <c r="S218" s="24" t="n"/>
+      <c r="T218" s="24" t="n"/>
+      <c r="U218" s="24" t="n"/>
+      <c r="V218" s="24" t="n"/>
+      <c r="W218" s="24" t="n"/>
+      <c r="X218" s="24" t="n"/>
+      <c r="Y218" s="24" t="n"/>
+      <c r="Z218" s="24" t="n"/>
+      <c r="AA218" s="24" t="n"/>
     </row>
     <row r="219">
-      <c r="A219" s="25" t="n"/>
-      <c r="B219" s="25" t="n"/>
-      <c r="C219" s="25" t="n"/>
-      <c r="D219" s="25" t="n"/>
-      <c r="E219" s="25" t="n"/>
-      <c r="F219" s="25" t="n"/>
-      <c r="G219" s="25" t="n"/>
-      <c r="H219" s="25" t="n"/>
-      <c r="I219" s="25" t="n"/>
-      <c r="J219" s="25" t="n"/>
-      <c r="K219" s="25" t="n"/>
-      <c r="L219" s="25" t="n"/>
-      <c r="M219" s="25" t="n"/>
-      <c r="N219" s="25" t="n"/>
-      <c r="O219" s="25" t="n"/>
-      <c r="P219" s="25" t="n"/>
-      <c r="Q219" s="25" t="n"/>
-      <c r="R219" s="25" t="n"/>
-      <c r="S219" s="25" t="n"/>
-      <c r="T219" s="25" t="n"/>
-      <c r="U219" s="25" t="n"/>
-      <c r="V219" s="25" t="n"/>
-      <c r="W219" s="25" t="n"/>
+      <c r="A219" s="24" t="n"/>
+      <c r="B219" s="24" t="n"/>
+      <c r="C219" s="24" t="n"/>
+      <c r="D219" s="24" t="n"/>
+      <c r="E219" s="24" t="n"/>
+      <c r="F219" s="24" t="n"/>
+      <c r="G219" s="24" t="n"/>
+      <c r="H219" s="24" t="n"/>
+      <c r="I219" s="24" t="n"/>
+      <c r="J219" s="24" t="n"/>
+      <c r="K219" s="24" t="n"/>
+      <c r="L219" s="24" t="n"/>
+      <c r="M219" s="24" t="n"/>
+      <c r="N219" s="24" t="n"/>
+      <c r="O219" s="24" t="n"/>
+      <c r="P219" s="24" t="n"/>
+      <c r="Q219" s="24" t="n"/>
+      <c r="R219" s="24" t="n"/>
+      <c r="S219" s="24" t="n"/>
+      <c r="T219" s="24" t="n"/>
+      <c r="U219" s="24" t="n"/>
+      <c r="V219" s="24" t="n"/>
+      <c r="W219" s="24" t="n"/>
+      <c r="X219" s="24" t="n"/>
+      <c r="Y219" s="24" t="n"/>
+      <c r="Z219" s="24" t="n"/>
+      <c r="AA219" s="24" t="n"/>
     </row>
     <row r="220">
-      <c r="A220" s="25" t="n"/>
-      <c r="B220" s="25" t="n"/>
-      <c r="C220" s="25" t="n"/>
-      <c r="D220" s="25" t="n"/>
-      <c r="E220" s="25" t="n"/>
-      <c r="F220" s="25" t="n"/>
-      <c r="G220" s="25" t="n"/>
-      <c r="H220" s="25" t="n"/>
-      <c r="I220" s="25" t="n"/>
-      <c r="J220" s="25" t="n"/>
-      <c r="K220" s="25" t="n"/>
-      <c r="L220" s="25" t="n"/>
-      <c r="M220" s="25" t="n"/>
-      <c r="N220" s="25" t="n"/>
-      <c r="O220" s="25" t="n"/>
-      <c r="P220" s="25" t="n"/>
-      <c r="Q220" s="25" t="n"/>
-      <c r="R220" s="25" t="n"/>
-      <c r="S220" s="25" t="n"/>
-      <c r="T220" s="25" t="n"/>
-      <c r="U220" s="25" t="n"/>
-      <c r="V220" s="25" t="n"/>
-      <c r="W220" s="25" t="n"/>
+      <c r="A220" s="24" t="n"/>
+      <c r="B220" s="24" t="n"/>
+      <c r="C220" s="24" t="n"/>
+      <c r="D220" s="24" t="n"/>
+      <c r="E220" s="24" t="n"/>
+      <c r="F220" s="24" t="n"/>
+      <c r="G220" s="24" t="n"/>
+      <c r="H220" s="24" t="n"/>
+      <c r="I220" s="24" t="n"/>
+      <c r="J220" s="24" t="n"/>
+      <c r="K220" s="24" t="n"/>
+      <c r="L220" s="24" t="n"/>
+      <c r="M220" s="24" t="n"/>
+      <c r="N220" s="24" t="n"/>
+      <c r="O220" s="24" t="n"/>
+      <c r="P220" s="24" t="n"/>
+      <c r="Q220" s="24" t="n"/>
+      <c r="R220" s="24" t="n"/>
+      <c r="S220" s="24" t="n"/>
+      <c r="T220" s="24" t="n"/>
+      <c r="U220" s="24" t="n"/>
+      <c r="V220" s="24" t="n"/>
+      <c r="W220" s="24" t="n"/>
+      <c r="X220" s="24" t="n"/>
+      <c r="Y220" s="24" t="n"/>
+      <c r="Z220" s="24" t="n"/>
+      <c r="AA220" s="24" t="n"/>
     </row>
   </sheetData>
-  <dataValidations count="3">
+  <autoFilter ref="A1:AA220"/>
+  <dataValidations count="15">
     <dataValidation sqref="C2:C200" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"客户金融场景,SA-AI内化场景"</formula1>
     </dataValidation>
@@ -9438,12 +11277,48 @@
     <dataValidation sqref="M2:M200" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"catalog,skill,demo"</formula1>
     </dataValidation>
+    <dataValidation sqref="C3:C500" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"客户金融场景,SA-AI内化场景"</formula1>
+    </dataValidation>
+    <dataValidation sqref="K3:K500" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"独立 Skill,主 Skill + L1,Agent 编排,L1 候选,L3 专项候选"</formula1>
+    </dataValidation>
+    <dataValidation sqref="L3:L500" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"规则型,LLM生成型,RAG知识检索型,数据分析型,工具调用型,Agent编排型,混合型"</formula1>
+    </dataValidation>
+    <dataValidation sqref="M3:M500" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"目录规划,仅Demo,真实SKILL.md,真实Skill包,真实Skill包+Demo"</formula1>
+    </dataValidation>
+    <dataValidation sqref="Q3:Q500" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"catalog,skill,demo"</formula1>
+    </dataValidation>
+    <dataValidation sqref="C2:C500" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"客户金融场景,SA-AI内化场景"</formula1>
+    </dataValidation>
+    <dataValidation sqref="J2:J500" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"风控,财富管理,投研,团队管理,投标,方案写作,技术评估,资料检索,合规,车险,客服,办公,科技,需求调研"</formula1>
+    </dataValidation>
+    <dataValidation sqref="K2:K500" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"独立 Skill,主 Skill + L1,Agent 编排,L1 候选,L3 专项候选"</formula1>
+    </dataValidation>
+    <dataValidation sqref="L2:L500" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"规则型,LLM生成型,RAG知识检索型,数据分析型,工具调用型,Agent编排型,混合型"</formula1>
+    </dataValidation>
+    <dataValidation sqref="M2:M500" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"目录规划,仅Demo,真实SKILL.md,真实Skill包,真实Skill包+Demo"</formula1>
+    </dataValidation>
+    <dataValidation sqref="P2:P500" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"规划,已制作,已开发"</formula1>
+    </dataValidation>
+    <dataValidation sqref="Q2:Q500" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"catalog,skill,demo"</formula1>
+    </dataValidation>
   </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>

--- a/shared-templates/team_skill_register.xlsx
+++ b/shared-templates/team_skill_register.xlsx
@@ -8,9 +8,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="已制作Skill登记" sheetId="3" state="visible" r:id="rId3"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="同事填写说明" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
-  <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'已制作Skill登记'!$A$1:$AA$220</definedName>
-  </definedNames>
+  <definedNames/>
 </workbook>
 </file>
 
@@ -189,16 +187,16 @@
     </font>
     <font>
       <b val="1"/>
-      <color rgb="00FFFFFF"/>
+      <color rgb="FFFFFFFF"/>
     </font>
     <font>
       <b val="1"/>
-      <color rgb="00FFFFFF"/>
+      <color rgb="FFFFFFFF"/>
       <sz val="16"/>
     </font>
     <font>
       <b val="1"/>
-      <color rgb="004C1D95"/>
+      <color rgb="FF4C1D95"/>
     </font>
   </fonts>
   <fills count="41">
@@ -385,22 +383,22 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="001F4E78"/>
+        <fgColor rgb="FF1F4E78"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="004C1D95"/>
+        <fgColor rgb="FF4C1D95"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="006D28D9"/>
+        <fgColor rgb="FF6D28D9"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00334155"/>
+        <fgColor rgb="FF334155"/>
       </patternFill>
     </fill>
   </fills>
@@ -501,62 +499,62 @@
     </border>
     <border>
       <left style="thin">
-        <color rgb="00D9E2F3"/>
+        <color rgb="FFD9E2F3"/>
       </left>
       <right style="thin">
-        <color rgb="00D9E2F3"/>
+        <color rgb="FFD9E2F3"/>
       </right>
       <top style="thin">
-        <color rgb="00D9E2F3"/>
+        <color rgb="FFD9E2F3"/>
       </top>
       <bottom style="thin">
-        <color rgb="00D9E2F3"/>
+        <color rgb="FFD9E2F3"/>
       </bottom>
     </border>
     <border>
       <left style="thin">
-        <color rgb="00D9E2EC"/>
+        <color rgb="FFD9E2EC"/>
       </left>
       <right style="thin">
-        <color rgb="00D9E2EC"/>
+        <color rgb="FFD9E2EC"/>
       </right>
       <top style="thin">
-        <color rgb="00D9E2EC"/>
+        <color rgb="FFD9E2EC"/>
       </top>
       <bottom style="thin">
-        <color rgb="00D9E2EC"/>
+        <color rgb="FFD9E2EC"/>
       </bottom>
     </border>
     <border>
       <top style="thin">
-        <color rgb="00D9E2EC"/>
+        <color rgb="FFD9E2EC"/>
       </top>
     </border>
     <border>
       <right style="thin">
-        <color rgb="00D9E2EC"/>
+        <color rgb="FFD9E2EC"/>
       </right>
       <top style="thin">
-        <color rgb="00D9E2EC"/>
+        <color rgb="FFD9E2EC"/>
       </top>
     </border>
     <border>
       <top style="thin">
-        <color rgb="00D9E2EC"/>
+        <color rgb="FFD9E2EC"/>
       </top>
       <bottom style="thin">
-        <color rgb="00D9E2EC"/>
+        <color rgb="FFD9E2EC"/>
       </bottom>
     </border>
     <border>
       <right style="thin">
-        <color rgb="00D9E2EC"/>
+        <color rgb="FFD9E2EC"/>
       </right>
       <top style="thin">
-        <color rgb="00D9E2EC"/>
+        <color rgb="FFD9E2EC"/>
       </top>
       <bottom style="thin">
-        <color rgb="00D9E2EC"/>
+        <color rgb="FFD9E2EC"/>
       </bottom>
     </border>
   </borders>
@@ -1166,9 +1164,9 @@
     </a:clrScheme>
     <a:fontScheme name="Office">
       <a:majorFont>
-        <a:latin typeface="Calibri"/>
-        <a:ea typeface="Calibri"/>
-        <a:cs typeface="Calibri"/>
+        <a:latin typeface="Calibri Light"/>
+        <a:ea typeface="Calibri Light"/>
+        <a:cs typeface="Calibri Light"/>
       </a:majorFont>
       <a:minorFont>
         <a:latin typeface="Calibri"/>
@@ -2571,17 +2569,17 @@
       </c>
       <c r="C6" s="37" t="inlineStr">
         <is>
-          <t>风控 / 财富管理 / 投研 / 团队管理 / 投标 / 方案写作 / 技术评估 / 资料检索 / 合规 / 车险 / 客服 / 办公 / 科技</t>
+          <t>AI信贷 / 信贷 / 贷前 / 贷中 / 贷后 / 风控 / 财富管理 / 投研 / 营销 / 客服 / 合规 / 团队管理 / 投标 / 方案写作 / 技术评估 / 资料检索 / 车险 / 办公 / 科技</t>
         </is>
       </c>
       <c r="D6" s="37" t="inlineStr">
         <is>
-          <t>用业务语言，不用技术语言。不要填“混合型”“Agent”“RAG”；这些属于实现模式。</t>
+          <t>用业务语言，不用技术语言。业务分类填最主要的业务入口；如果一个场景可被多个入口命中，在标签中补充相关业务词。面向客户专项演示时，可使用 AI信贷 这类演示集合标签。不要填“混合型”“Agent”“RAG”；这些属于实现模式。</t>
         </is>
       </c>
       <c r="E6" s="37" t="inlineStr">
         <is>
-          <t>授信走访=风控；个股研究=投研；日报汇总=团队管理；招标红线=投标</t>
+          <t>信贷尽调=业务分类填信贷，标签补 AI信贷、风控、贷前、尽调；授信走访=AI信贷/风控/信贷；贷后监测=AI信贷/贷后/风控</t>
         </is>
       </c>
     </row>
@@ -2778,8 +2776,16 @@
       <c r="A14" s="37" t="inlineStr"/>
       <c r="B14" s="37" t="inlineStr"/>
       <c r="C14" s="37" t="inlineStr"/>
-      <c r="D14" s="37" t="inlineStr"/>
-      <c r="E14" s="37" t="inlineStr"/>
+      <c r="D14" s="37" t="inlineStr">
+        <is>
+          <t>放不适合作为稳定主分类的关键词、产品名、平台名、项目名、指标名，也可补充辅助筛选的业务词或演示集合标签。</t>
+        </is>
+      </c>
+      <c r="E14" s="37" t="inlineStr">
+        <is>
+          <t>AI信贷,信贷,风控,贷前,尽调,P800,净值走势,日报,信创,投顾</t>
+        </is>
+      </c>
     </row>
     <row r="15" ht="42" customHeight="1" s="29">
       <c r="A15" s="37" t="inlineStr">
@@ -2861,7 +2867,7 @@
     <mergeCell ref="A1:E1"/>
     <mergeCell ref="B2:E2"/>
   </mergeCells>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
@@ -5495,33 +5501,129 @@
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="24" t="n"/>
-      <c r="B22" s="24" t="n"/>
-      <c r="C22" s="24" t="n"/>
-      <c r="D22" s="24" t="n"/>
-      <c r="E22" s="24" t="n"/>
-      <c r="F22" s="24" t="n"/>
-      <c r="G22" s="24" t="n"/>
-      <c r="H22" s="24" t="n"/>
-      <c r="I22" s="24" t="n"/>
-      <c r="J22" s="24" t="n"/>
-      <c r="K22" s="24" t="n"/>
-      <c r="L22" s="24" t="n"/>
-      <c r="M22" s="24" t="n"/>
-      <c r="N22" s="24" t="n"/>
-      <c r="O22" s="24" t="n"/>
-      <c r="P22" s="24" t="n"/>
-      <c r="Q22" s="24" t="n"/>
-      <c r="R22" s="24" t="n"/>
-      <c r="S22" s="24" t="n"/>
-      <c r="T22" s="24" t="n"/>
-      <c r="U22" s="24" t="n"/>
-      <c r="V22" s="24" t="n"/>
-      <c r="W22" s="24" t="n"/>
-      <c r="X22" s="24" t="n"/>
-      <c r="Y22" s="24" t="n"/>
-      <c r="Z22" s="24" t="n"/>
-      <c r="AA22" s="24" t="n"/>
+      <c r="A22" s="24" t="inlineStr">
+        <is>
+          <t>credit-due-diligence-report</t>
+        </is>
+      </c>
+      <c r="B22" s="24" t="inlineStr">
+        <is>
+          <t>信贷尽调调查与分析报告生成</t>
+        </is>
+      </c>
+      <c r="C22" s="24" t="inlineStr">
+        <is>
+          <t>客户金融场景</t>
+        </is>
+      </c>
+      <c r="D22" s="24" t="inlineStr">
+        <is>
+          <t>银行</t>
+        </is>
+      </c>
+      <c r="E22" s="24" t="inlineStr">
+        <is>
+          <t>中台</t>
+        </is>
+      </c>
+      <c r="F22" s="24" t="inlineStr">
+        <is>
+          <t>信贷</t>
+        </is>
+      </c>
+      <c r="G22" s="24" t="inlineStr">
+        <is>
+          <t>贷前尽调</t>
+        </is>
+      </c>
+      <c r="H22" s="24" t="inlineStr">
+        <is>
+          <t>面向客户经理和授信审查人员，围绕贷前尽调场景整合企业基本信息、经营现场、财务报表、流水税票、征信、司法舆情、关联方和担保圈等信息，自动生成尽调分析报告草稿、风险问题清单、补充材料清单和授信建议。</t>
+        </is>
+      </c>
+      <c r="I22" s="24" t="inlineStr">
+        <is>
+          <t>混合型 Skill（数据核验+规则+LLM报告生成+人工复核）</t>
+        </is>
+      </c>
+      <c r="J22" s="24" t="inlineStr">
+        <is>
+          <t>信贷</t>
+        </is>
+      </c>
+      <c r="K22" s="24" t="inlineStr">
+        <is>
+          <t>主 Skill + L1</t>
+        </is>
+      </c>
+      <c r="L22" s="24" t="inlineStr">
+        <is>
+          <t>混合型</t>
+        </is>
+      </c>
+      <c r="M22" s="24" t="inlineStr">
+        <is>
+          <t>仅Demo</t>
+        </is>
+      </c>
+      <c r="N22" s="24" t="inlineStr">
+        <is>
+          <t>企业工商信息、授信申请、财务报表、银行流水、税票、征信报告、司法舆情、合同/发票/年报/章程、现场走访记录、关联方与担保信息</t>
+        </is>
+      </c>
+      <c r="O22" s="24" t="inlineStr">
+        <is>
+          <t>信贷尽调分析报告草稿、风险评级/关注等级、风险问题清单、待补充材料清单、授信额度/期限/担保条件建议、后续跟踪要求</t>
+        </is>
+      </c>
+      <c r="P22" s="24" t="inlineStr">
+        <is>
+          <t>已制作</t>
+        </is>
+      </c>
+      <c r="Q22" s="24" t="inlineStr">
+        <is>
+          <t>demo</t>
+        </is>
+      </c>
+      <c r="R22" s="24" t="inlineStr">
+        <is>
+          <t>FDE共创/模拟Demo</t>
+        </is>
+      </c>
+      <c r="S22" s="24" t="inlineStr">
+        <is>
+          <t>通用</t>
+        </is>
+      </c>
+      <c r="T22" s="24" t="inlineStr">
+        <is>
+          <t>当前为售前演示 Demo，未伪造真实 SKILL.md；后续拿到真实业务规则、数据接口和脚本后，可补齐 Skill 包并升级为真实Skill包+Demo。</t>
+        </is>
+      </c>
+      <c r="U22" s="24" t="str"/>
+      <c r="V22" s="24" t="inlineStr">
+        <is>
+          <t>presales-skill-matrix/credit-due-diligence-report/credit-due-diligence-report-demo.html</t>
+        </is>
+      </c>
+      <c r="W22" s="24" t="str"/>
+      <c r="X22" s="24" t="str"/>
+      <c r="Y22" s="24" t="inlineStr">
+        <is>
+          <t>0.1.0</t>
+        </is>
+      </c>
+      <c r="Z22" s="24" t="inlineStr">
+        <is>
+          <t>AI信贷,信贷,风控,贷前,尽调,尽调报告,授信审批,企业信用分析,财务分析,征信核查,关联担保,报告生成,仅Demo</t>
+        </is>
+      </c>
+      <c r="AA22" s="24" t="inlineStr">
+        <is>
+          <t>2026-07-09 新增信贷尽调调查场景；Demo 使用脱敏模拟数据展示左侧业务工作台、中间 Skill 链路、右侧模拟数据区。</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" s="24" t="n"/>
@@ -11266,7 +11368,6 @@
       <c r="AA220" s="24" t="n"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:AA220"/>
   <dataValidations count="15">
     <dataValidation sqref="C2:C200" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"客户金融场景,SA-AI内化场景"</formula1>
